--- a/research/traditional_assets/database/data/turkey/turkey_precious_metals.xlsx
+++ b/research/traditional_assets/database/data/turkey/turkey_precious_metals.xlsx
@@ -588,115 +588,118 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.293</v>
+        <v>0.421</v>
       </c>
       <c r="E2">
-        <v>0.605</v>
+        <v>0.483</v>
       </c>
       <c r="G2">
-        <v>0.6654978962131837</v>
+        <v>0.5299199999999999</v>
       </c>
       <c r="H2">
-        <v>0.6028517999064983</v>
+        <v>0.48448</v>
       </c>
       <c r="I2">
-        <v>0.437120149602618</v>
+        <v>0.41664</v>
       </c>
       <c r="J2">
-        <v>0.3301078783916312</v>
+        <v>0.329319379524302</v>
       </c>
       <c r="K2">
-        <v>251.1</v>
+        <v>229.3</v>
       </c>
       <c r="L2">
-        <v>0.5869565217391304</v>
+        <v>0.7337600000000001</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>140.8</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.03057878162666957</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>0.6140427387701701</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>140.8</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.03057878162666957</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.6140427387701701</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
-        <v>857.6</v>
+        <v>30.5</v>
       </c>
       <c r="V2">
-        <v>0.6417240347201436</v>
+        <v>0.006623954826799869</v>
       </c>
       <c r="W2">
-        <v>0.2691029900332226</v>
+        <v>0.2159337037385818</v>
       </c>
       <c r="X2">
-        <v>0.1087197605490591</v>
+        <v>0.2279254616545791</v>
       </c>
       <c r="Y2">
-        <v>0.1603832294841635</v>
+        <v>-0.01199175791599727</v>
       </c>
       <c r="Z2">
-        <v>2.009110975437937</v>
+        <v>1.498800959232613</v>
       </c>
       <c r="AA2">
-        <v>0.6632233615551583</v>
+        <v>0.4935842019249128</v>
       </c>
       <c r="AB2">
-        <v>0.1085208319612028</v>
+        <v>0.2278790317670524</v>
       </c>
       <c r="AC2">
-        <v>0.5547025295939554</v>
+        <v>0.2657051701578603</v>
       </c>
       <c r="AD2">
-        <v>5.46</v>
+        <v>1.72</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>5.46</v>
+        <v>1.72</v>
       </c>
       <c r="AG2">
-        <v>-852.14</v>
+        <v>-28.78</v>
       </c>
       <c r="AH2">
-        <v>0.004068978880062003</v>
+        <v>0.0003734081307449492</v>
       </c>
       <c r="AI2">
-        <v>0.005115424973767051</v>
+        <v>0.002894063804011307</v>
       </c>
       <c r="AJ2">
-        <v>-1.75967455499112</v>
+        <v>-0.00628972052485729</v>
       </c>
       <c r="AK2">
-        <v>-4.062452326468343</v>
+        <v>-0.05104465964314852</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-144.9</v>
+        <v>-146.4</v>
       </c>
       <c r="AN2">
-        <v>0.02655642023346303</v>
+        <v>0.01176470588235294</v>
       </c>
       <c r="AP2">
-        <v>-4.144649805447471</v>
+        <v>-0.1968536251709987</v>
       </c>
       <c r="AQ2">
-        <v>-1.290545203588682</v>
+        <v>-0.8893442622950819</v>
       </c>
     </row>
     <row r="3">
@@ -716,115 +719,118 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.293</v>
+        <v>0.421</v>
       </c>
       <c r="E3">
-        <v>0.605</v>
+        <v>0.483</v>
       </c>
       <c r="G3">
-        <v>0.6654978962131837</v>
+        <v>0.5299199999999999</v>
       </c>
       <c r="H3">
-        <v>0.6028517999064983</v>
+        <v>0.48448</v>
       </c>
       <c r="I3">
-        <v>0.437120149602618</v>
+        <v>0.41664</v>
       </c>
       <c r="J3">
-        <v>0.3301078783916312</v>
+        <v>0.329319379524302</v>
       </c>
       <c r="K3">
-        <v>251.1</v>
+        <v>229.3</v>
       </c>
       <c r="L3">
-        <v>0.5869565217391304</v>
+        <v>0.7337600000000001</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>140.8</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.03057878162666957</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.6140427387701701</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>140.8</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.03057878162666957</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.6140427387701701</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>857.6</v>
+        <v>30.5</v>
       </c>
       <c r="V3">
-        <v>0.6417240347201436</v>
+        <v>0.006623954826799869</v>
       </c>
       <c r="W3">
-        <v>0.2691029900332226</v>
+        <v>0.2159337037385818</v>
       </c>
       <c r="X3">
-        <v>0.1087197605490591</v>
+        <v>0.2279254616545791</v>
       </c>
       <c r="Y3">
-        <v>0.1603832294841635</v>
+        <v>-0.01199175791599727</v>
       </c>
       <c r="Z3">
-        <v>2.009110975437937</v>
+        <v>1.498800959232613</v>
       </c>
       <c r="AA3">
-        <v>0.6632233615551583</v>
+        <v>0.4935842019249128</v>
       </c>
       <c r="AB3">
-        <v>0.1085208319612028</v>
+        <v>0.2278790317670524</v>
       </c>
       <c r="AC3">
-        <v>0.5547025295939554</v>
+        <v>0.2657051701578603</v>
       </c>
       <c r="AD3">
-        <v>5.46</v>
+        <v>1.72</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>5.46</v>
+        <v>1.72</v>
       </c>
       <c r="AG3">
-        <v>-852.14</v>
+        <v>-28.78</v>
       </c>
       <c r="AH3">
-        <v>0.004068978880062003</v>
+        <v>0.0003734081307449492</v>
       </c>
       <c r="AI3">
-        <v>0.005115424973767051</v>
+        <v>0.002894063804011307</v>
       </c>
       <c r="AJ3">
-        <v>-1.75967455499112</v>
+        <v>-0.00628972052485729</v>
       </c>
       <c r="AK3">
-        <v>-4.062452326468343</v>
+        <v>-0.05104465964314852</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-144.9</v>
+        <v>-146.4</v>
       </c>
       <c r="AN3">
-        <v>0.02655642023346303</v>
+        <v>0.01176470588235294</v>
       </c>
       <c r="AP3">
-        <v>-4.144649805447471</v>
+        <v>-0.1968536251709987</v>
       </c>
       <c r="AQ3">
-        <v>-1.290545203588682</v>
+        <v>-0.8893442622950819</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/turkey/turkey_precious_metals.xlsx
+++ b/research/traditional_assets/database/data/turkey/turkey_precious_metals.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="ibse_kozal" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,118 +590,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.421</v>
+        <v>0.358</v>
       </c>
       <c r="E2">
-        <v>0.483</v>
+        <v>0.373</v>
       </c>
       <c r="G2">
-        <v>0.5299199999999999</v>
+        <v>0.6877767936226749</v>
       </c>
       <c r="H2">
-        <v>0.48448</v>
+        <v>0.6138175376439327</v>
       </c>
       <c r="I2">
-        <v>0.41664</v>
+        <v>0.2714791851195748</v>
       </c>
       <c r="J2">
-        <v>0.329319379524302</v>
+        <v>0.2465270541343198</v>
       </c>
       <c r="K2">
-        <v>229.3</v>
+        <v>197.6</v>
       </c>
       <c r="L2">
-        <v>0.7337600000000001</v>
+        <v>0.8751107174490699</v>
       </c>
       <c r="M2">
-        <v>140.8</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="N2">
-        <v>0.03057878162666957</v>
+        <v>0.03835059346479406</v>
       </c>
       <c r="O2">
-        <v>0.6140427387701701</v>
+        <v>0.4104251012145749</v>
       </c>
       <c r="P2">
-        <v>140.8</v>
+        <v>44.8</v>
       </c>
       <c r="Q2">
-        <v>0.03057878162666957</v>
+        <v>0.02118503806686528</v>
       </c>
       <c r="R2">
-        <v>0.6140427387701701</v>
+        <v>0.2267206477732794</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>36.3</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.4475955610357583</v>
       </c>
       <c r="U2">
-        <v>30.5</v>
+        <v>6.26</v>
       </c>
       <c r="V2">
-        <v>0.006623954826799869</v>
+        <v>0.002960230765593228</v>
       </c>
       <c r="W2">
-        <v>0.2159337037385818</v>
+        <v>0.3334458319271009</v>
       </c>
       <c r="X2">
-        <v>0.2279254616545791</v>
+        <v>0.18556980102639</v>
       </c>
       <c r="Y2">
-        <v>-0.01199175791599727</v>
+        <v>0.1478760309007109</v>
       </c>
       <c r="Z2">
-        <v>1.498800959232613</v>
+        <v>0.4009133295692223</v>
       </c>
       <c r="AA2">
-        <v>0.4935842019249128</v>
+        <v>0.09883598210188206</v>
       </c>
       <c r="AB2">
-        <v>0.2278790317670524</v>
+        <v>0.1849318614608096</v>
       </c>
       <c r="AC2">
-        <v>0.2657051701578603</v>
+        <v>-0.08609587935892758</v>
       </c>
       <c r="AD2">
-        <v>1.72</v>
+        <v>14.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.72</v>
+        <v>14.4</v>
       </c>
       <c r="AG2">
-        <v>-28.78</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="AH2">
-        <v>0.0003734081307449492</v>
+        <v>0.006763421163872059</v>
       </c>
       <c r="AI2">
-        <v>0.002894063804011307</v>
+        <v>0.02726756296156031</v>
       </c>
       <c r="AJ2">
-        <v>-0.00628972052485729</v>
+        <v>0.003834485877409509</v>
       </c>
       <c r="AK2">
-        <v>-0.05104465964314852</v>
+        <v>0.01559865092748735</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AM2">
-        <v>-146.4</v>
+        <v>-174.38</v>
       </c>
       <c r="AN2">
-        <v>0.01176470588235294</v>
+        <v>0.2051282051282051</v>
+      </c>
+      <c r="AO2">
+        <v>60.09803921568627</v>
       </c>
       <c r="AP2">
-        <v>-0.1968536251709987</v>
+        <v>0.115954415954416</v>
       </c>
       <c r="AQ2">
-        <v>-0.8893442622950819</v>
+        <v>-0.3515311388920748</v>
       </c>
     </row>
     <row r="3">
@@ -719,118 +724,8893 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.421</v>
+        <v>0.358</v>
       </c>
       <c r="E3">
-        <v>0.483</v>
+        <v>0.373</v>
       </c>
       <c r="G3">
-        <v>0.5299199999999999</v>
+        <v>0.6877767936226749</v>
       </c>
       <c r="H3">
-        <v>0.48448</v>
+        <v>0.6138175376439327</v>
       </c>
       <c r="I3">
-        <v>0.41664</v>
+        <v>0.2714791851195748</v>
       </c>
       <c r="J3">
-        <v>0.329319379524302</v>
+        <v>0.2465270541343198</v>
       </c>
       <c r="K3">
-        <v>229.3</v>
+        <v>197.6</v>
       </c>
       <c r="L3">
-        <v>0.7337600000000001</v>
+        <v>0.8751107174490699</v>
       </c>
       <c r="M3">
-        <v>140.8</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="N3">
-        <v>0.03057878162666957</v>
+        <v>0.03835059346479406</v>
       </c>
       <c r="O3">
-        <v>0.6140427387701701</v>
+        <v>0.4104251012145749</v>
       </c>
       <c r="P3">
-        <v>140.8</v>
+        <v>44.8</v>
       </c>
       <c r="Q3">
-        <v>0.03057878162666957</v>
+        <v>0.02118503806686528</v>
       </c>
       <c r="R3">
-        <v>0.6140427387701701</v>
+        <v>0.2267206477732794</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>36.3</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.4475955610357583</v>
       </c>
       <c r="U3">
-        <v>30.5</v>
+        <v>6.26</v>
       </c>
       <c r="V3">
-        <v>0.006623954826799869</v>
+        <v>0.002960230765593228</v>
       </c>
       <c r="W3">
-        <v>0.2159337037385818</v>
+        <v>0.3334458319271009</v>
       </c>
       <c r="X3">
-        <v>0.2279254616545791</v>
+        <v>0.18556980102639</v>
       </c>
       <c r="Y3">
-        <v>-0.01199175791599727</v>
+        <v>0.1478760309007109</v>
       </c>
       <c r="Z3">
-        <v>1.498800959232613</v>
+        <v>0.4009133295692223</v>
       </c>
       <c r="AA3">
-        <v>0.4935842019249128</v>
+        <v>0.09883598210188206</v>
       </c>
       <c r="AB3">
-        <v>0.2278790317670524</v>
+        <v>0.1849318614608096</v>
       </c>
       <c r="AC3">
-        <v>0.2657051701578603</v>
+        <v>-0.08609587935892758</v>
       </c>
       <c r="AD3">
-        <v>1.72</v>
+        <v>14.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.72</v>
+        <v>14.4</v>
       </c>
       <c r="AG3">
-        <v>-28.78</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.0003734081307449492</v>
+        <v>0.006763421163872059</v>
       </c>
       <c r="AI3">
-        <v>0.002894063804011307</v>
+        <v>0.02726756296156031</v>
       </c>
       <c r="AJ3">
-        <v>-0.00628972052485729</v>
+        <v>0.003834485877409509</v>
       </c>
       <c r="AK3">
-        <v>-0.05104465964314852</v>
+        <v>0.01559865092748735</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AM3">
-        <v>-146.4</v>
+        <v>-174.38</v>
       </c>
       <c r="AN3">
-        <v>0.01176470588235294</v>
+        <v>0.2051282051282051</v>
+      </c>
+      <c r="AO3">
+        <v>60.09803921568627</v>
       </c>
       <c r="AP3">
-        <v>-0.1968536251709987</v>
+        <v>0.115954415954416</v>
       </c>
       <c r="AQ3">
-        <v>-0.8893442622950819</v>
+        <v>-0.3515311388920748</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Koza Altin Isletmeleri A.S. (IBSE:KOZAL)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>IBSE:KOZAL</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Precious Metals</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>60.0980392156863</v>
+      </c>
+      <c r="F2">
+        <v>3.65931725330238</v>
+      </c>
+      <c r="G2">
+        <v>0.205128205128205</v>
+      </c>
+      <c r="H2">
+        <v>4.24606837606838</v>
+      </c>
+      <c r="I2">
+        <v>0.00676342116387206</v>
+      </c>
+      <c r="J2">
+        <v>0.14</v>
+      </c>
+      <c r="K2">
+        <v>2114.7</v>
+      </c>
+      <c r="L2">
+        <v>1902.34171867896</v>
+      </c>
+      <c r="M2">
+        <v>2122.84</v>
+      </c>
+      <c r="N2">
+        <v>2194.15571867896</v>
+      </c>
+      <c r="O2">
+        <v>14.4</v>
+      </c>
+      <c r="P2">
+        <v>298.074</v>
+      </c>
+      <c r="Q2">
+        <v>0.18493186146081</v>
+      </c>
+      <c r="R2">
+        <v>0.180182199149583</v>
+      </c>
+      <c r="S2">
+        <v>0.091247778173816</v>
+      </c>
+      <c r="T2">
+        <v>0.04215</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.18556980102639</v>
+      </c>
+      <c r="X2">
+        <v>0.202652557150678</v>
+      </c>
+      <c r="Y2">
+        <v>1.04050431641724</v>
+      </c>
+      <c r="Z2">
+        <v>1.16161016625367</v>
+      </c>
+      <c r="AA2">
+        <v>14.4</v>
+      </c>
+      <c r="AB2">
+        <v>0.1216637042317547</v>
+      </c>
+      <c r="AC2">
+        <v>60.09803921568627</v>
+      </c>
+      <c r="AD2">
+        <v>14.4</v>
+      </c>
+      <c r="AE2">
+        <v>1.02</v>
+      </c>
+      <c r="AF2">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="AG2">
+        <v>70.2</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>2114.7</v>
+      </c>
+      <c r="AK2">
+        <v>0.1410564076579343</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.25</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>37.50000000000001</v>
+      </c>
+      <c r="AR2">
+        <v>1.02</v>
+      </c>
+      <c r="AS2">
+        <v>14.4</v>
+      </c>
+      <c r="AT2">
+        <v>6.26</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1848240405695163</v>
+      </c>
+      <c r="C2">
+        <v>2130.667457659578</v>
+      </c>
+      <c r="D2">
+        <v>2124.407457659578</v>
+      </c>
+      <c r="E2">
+        <v>-14.4</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>6.26</v>
+      </c>
+      <c r="H2">
+        <v>2114.7</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>70.2</v>
+      </c>
+      <c r="K2">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L2">
+        <v>61.3</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>61.3</v>
+      </c>
+      <c r="O2">
+        <v>15.325</v>
+      </c>
+      <c r="P2">
+        <v>45.97499999999999</v>
+      </c>
+      <c r="Q2">
+        <v>54.875</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1848240405695163</v>
+      </c>
+      <c r="T2">
+        <v>1.035217350236429</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.25</v>
+      </c>
+      <c r="W2">
+        <v>0.033525</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1844062304680925</v>
+      </c>
+      <c r="C3">
+        <v>2115.472343065695</v>
+      </c>
+      <c r="D3">
+        <v>2130.503343065694</v>
+      </c>
+      <c r="E3">
+        <v>6.891000000000002</v>
+      </c>
+      <c r="F3">
+        <v>21.291</v>
+      </c>
+      <c r="G3">
+        <v>6.26</v>
+      </c>
+      <c r="H3">
+        <v>2114.7</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>70.2</v>
+      </c>
+      <c r="K3">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L3">
+        <v>61.3</v>
+      </c>
+      <c r="M3">
+        <v>0.9517077</v>
+      </c>
+      <c r="N3">
+        <v>60.3482923</v>
+      </c>
+      <c r="O3">
+        <v>15.087073075</v>
+      </c>
+      <c r="P3">
+        <v>45.261219225</v>
+      </c>
+      <c r="Q3">
+        <v>54.161219225</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1859302833011035</v>
+      </c>
+      <c r="T3">
+        <v>1.043059905920038</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0.25</v>
+      </c>
+      <c r="W3">
+        <v>0.033525</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>64.41053277177436</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1839884203666687</v>
+      </c>
+      <c r="C4">
+        <v>2100.312312846908</v>
+      </c>
+      <c r="D4">
+        <v>2136.634312846908</v>
+      </c>
+      <c r="E4">
+        <v>28.182</v>
+      </c>
+      <c r="F4">
+        <v>42.582</v>
+      </c>
+      <c r="G4">
+        <v>6.26</v>
+      </c>
+      <c r="H4">
+        <v>2114.7</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>70.2</v>
+      </c>
+      <c r="K4">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L4">
+        <v>61.3</v>
+      </c>
+      <c r="M4">
+        <v>1.9034154</v>
+      </c>
+      <c r="N4">
+        <v>59.3965846</v>
+      </c>
+      <c r="O4">
+        <v>14.84914615</v>
+      </c>
+      <c r="P4">
+        <v>44.54743845</v>
+      </c>
+      <c r="Q4">
+        <v>53.44743845000001</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1870591024149681</v>
+      </c>
+      <c r="T4">
+        <v>1.051062513760456</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.25</v>
+      </c>
+      <c r="W4">
+        <v>0.033525</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>32.20526638588718</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1835706102652449</v>
+      </c>
+      <c r="C5">
+        <v>2085.187670765276</v>
+      </c>
+      <c r="D5">
+        <v>2142.800670765276</v>
+      </c>
+      <c r="E5">
+        <v>49.473</v>
+      </c>
+      <c r="F5">
+        <v>63.873</v>
+      </c>
+      <c r="G5">
+        <v>6.26</v>
+      </c>
+      <c r="H5">
+        <v>2114.7</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>70.2</v>
+      </c>
+      <c r="K5">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L5">
+        <v>61.3</v>
+      </c>
+      <c r="M5">
+        <v>2.8551231</v>
+      </c>
+      <c r="N5">
+        <v>58.4448769</v>
+      </c>
+      <c r="O5">
+        <v>14.611219225</v>
+      </c>
+      <c r="P5">
+        <v>43.833657675</v>
+      </c>
+      <c r="Q5">
+        <v>52.733657675</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.188211196149737</v>
+      </c>
+      <c r="T5">
+        <v>1.059230123824387</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.25</v>
+      </c>
+      <c r="W5">
+        <v>0.033525</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>21.47017759059145</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1831528001638211</v>
+      </c>
+      <c r="C6">
+        <v>2070.098724099657</v>
+      </c>
+      <c r="D6">
+        <v>2149.002724099657</v>
+      </c>
+      <c r="E6">
+        <v>70.76400000000001</v>
+      </c>
+      <c r="F6">
+        <v>85.164</v>
+      </c>
+      <c r="G6">
+        <v>6.26</v>
+      </c>
+      <c r="H6">
+        <v>2114.7</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>70.2</v>
+      </c>
+      <c r="K6">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L6">
+        <v>61.3</v>
+      </c>
+      <c r="M6">
+        <v>3.8068308</v>
+      </c>
+      <c r="N6">
+        <v>57.4931692</v>
+      </c>
+      <c r="O6">
+        <v>14.3732923</v>
+      </c>
+      <c r="P6">
+        <v>43.11987689999999</v>
+      </c>
+      <c r="Q6">
+        <v>52.0198769</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1893872918373137</v>
+      </c>
+      <c r="T6">
+        <v>1.067567892431317</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.25</v>
+      </c>
+      <c r="W6">
+        <v>0.033525</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>16.10263319294359</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1827349900623973</v>
+      </c>
+      <c r="C7">
+        <v>2055.04578369675</v>
+      </c>
+      <c r="D7">
+        <v>2155.24078369675</v>
+      </c>
+      <c r="E7">
+        <v>92.05500000000001</v>
+      </c>
+      <c r="F7">
+        <v>106.455</v>
+      </c>
+      <c r="G7">
+        <v>6.26</v>
+      </c>
+      <c r="H7">
+        <v>2114.7</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>70.2</v>
+      </c>
+      <c r="K7">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L7">
+        <v>61.3</v>
+      </c>
+      <c r="M7">
+        <v>4.7585385</v>
+      </c>
+      <c r="N7">
+        <v>56.5414615</v>
+      </c>
+      <c r="O7">
+        <v>14.135365375</v>
+      </c>
+      <c r="P7">
+        <v>42.406096125</v>
+      </c>
+      <c r="Q7">
+        <v>51.306096125</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1905881474341025</v>
+      </c>
+      <c r="T7">
+        <v>1.07608119300892</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.25</v>
+      </c>
+      <c r="W7">
+        <v>0.033525</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>12.88210655435487</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1823666799609736</v>
+      </c>
+      <c r="C8">
+        <v>2039.283900563225</v>
+      </c>
+      <c r="D8">
+        <v>2160.769900563224</v>
+      </c>
+      <c r="E8">
+        <v>113.346</v>
+      </c>
+      <c r="F8">
+        <v>127.746</v>
+      </c>
+      <c r="G8">
+        <v>6.26</v>
+      </c>
+      <c r="H8">
+        <v>2114.7</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>70.2</v>
+      </c>
+      <c r="K8">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L8">
+        <v>61.3</v>
+      </c>
+      <c r="M8">
+        <v>5.8507668</v>
+      </c>
+      <c r="N8">
+        <v>55.44923319999999</v>
+      </c>
+      <c r="O8">
+        <v>13.8623083</v>
+      </c>
+      <c r="P8">
+        <v>41.5869249</v>
+      </c>
+      <c r="Q8">
+        <v>50.48692490000001</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1918145531499719</v>
+      </c>
+      <c r="T8">
+        <v>1.084775627641364</v>
+      </c>
+      <c r="U8">
+        <v>0.0458</v>
+      </c>
+      <c r="V8">
+        <v>0.25</v>
+      </c>
+      <c r="W8">
+        <v>0.03435</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>10.47725915174059</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1820726198595497</v>
+      </c>
+      <c r="C9">
+        <v>2022.427775954881</v>
+      </c>
+      <c r="D9">
+        <v>2165.20477595488</v>
+      </c>
+      <c r="E9">
+        <v>134.637</v>
+      </c>
+      <c r="F9">
+        <v>149.037</v>
+      </c>
+      <c r="G9">
+        <v>6.26</v>
+      </c>
+      <c r="H9">
+        <v>2114.7</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>70.2</v>
+      </c>
+      <c r="K9">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L9">
+        <v>61.3</v>
+      </c>
+      <c r="M9">
+        <v>7.153776000000001</v>
+      </c>
+      <c r="N9">
+        <v>54.146224</v>
+      </c>
+      <c r="O9">
+        <v>13.536556</v>
+      </c>
+      <c r="P9">
+        <v>40.609668</v>
+      </c>
+      <c r="Q9">
+        <v>49.509668</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1930673331823116</v>
+      </c>
+      <c r="T9">
+        <v>1.093657039362679</v>
+      </c>
+      <c r="U9">
+        <v>0.048</v>
+      </c>
+      <c r="V9">
+        <v>0.25</v>
+      </c>
+      <c r="W9">
+        <v>0.036</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>8.568901234816408</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.181769559758126</v>
+      </c>
+      <c r="C10">
+        <v>2005.726474490108</v>
+      </c>
+      <c r="D10">
+        <v>2169.794474490108</v>
+      </c>
+      <c r="E10">
+        <v>155.928</v>
+      </c>
+      <c r="F10">
+        <v>170.328</v>
+      </c>
+      <c r="G10">
+        <v>6.26</v>
+      </c>
+      <c r="H10">
+        <v>2114.7</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>70.2</v>
+      </c>
+      <c r="K10">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L10">
+        <v>61.3</v>
+      </c>
+      <c r="M10">
+        <v>8.431236</v>
+      </c>
+      <c r="N10">
+        <v>52.868764</v>
+      </c>
+      <c r="O10">
+        <v>13.217191</v>
+      </c>
+      <c r="P10">
+        <v>39.651573</v>
+      </c>
+      <c r="Q10">
+        <v>48.551573</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1943473475631804</v>
+      </c>
+      <c r="T10">
+        <v>1.102731525251848</v>
+      </c>
+      <c r="U10">
+        <v>0.0495</v>
+      </c>
+      <c r="V10">
+        <v>0.25</v>
+      </c>
+      <c r="W10">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>7.270582865904832</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1813877496567022</v>
+      </c>
+      <c r="C11">
+        <v>1990.245577043578</v>
+      </c>
+      <c r="D11">
+        <v>2175.604577043578</v>
+      </c>
+      <c r="E11">
+        <v>177.219</v>
+      </c>
+      <c r="F11">
+        <v>191.619</v>
+      </c>
+      <c r="G11">
+        <v>6.26</v>
+      </c>
+      <c r="H11">
+        <v>2114.7</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>70.2</v>
+      </c>
+      <c r="K11">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L11">
+        <v>61.3</v>
+      </c>
+      <c r="M11">
+        <v>9.485140499999998</v>
+      </c>
+      <c r="N11">
+        <v>51.8148595</v>
+      </c>
+      <c r="O11">
+        <v>12.953714875</v>
+      </c>
+      <c r="P11">
+        <v>38.86114462499999</v>
+      </c>
+      <c r="Q11">
+        <v>47.761144625</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1956554941282442</v>
+      </c>
+      <c r="T11">
+        <v>1.112005450391329</v>
+      </c>
+      <c r="U11">
+        <v>0.0495</v>
+      </c>
+      <c r="V11">
+        <v>0.25</v>
+      </c>
+      <c r="W11">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>6.462740325248741</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1811109395552784</v>
+      </c>
+      <c r="C12">
+        <v>1973.186362214216</v>
+      </c>
+      <c r="D12">
+        <v>2179.836362214216</v>
+      </c>
+      <c r="E12">
+        <v>198.51</v>
+      </c>
+      <c r="F12">
+        <v>212.91</v>
+      </c>
+      <c r="G12">
+        <v>6.26</v>
+      </c>
+      <c r="H12">
+        <v>2114.7</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>70.2</v>
+      </c>
+      <c r="K12">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L12">
+        <v>61.3</v>
+      </c>
+      <c r="M12">
+        <v>10.837119</v>
+      </c>
+      <c r="N12">
+        <v>50.462881</v>
+      </c>
+      <c r="O12">
+        <v>12.61572025</v>
+      </c>
+      <c r="P12">
+        <v>37.84716075</v>
+      </c>
+      <c r="Q12">
+        <v>46.74716075000001</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.196992710616976</v>
+      </c>
+      <c r="T12">
+        <v>1.121485462756131</v>
+      </c>
+      <c r="U12">
+        <v>0.0509</v>
+      </c>
+      <c r="V12">
+        <v>0.25</v>
+      </c>
+      <c r="W12">
+        <v>0.038175</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>5.656484901568397</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1807396294538546</v>
+      </c>
+      <c r="C13">
+        <v>1957.597753180398</v>
+      </c>
+      <c r="D13">
+        <v>2185.538753180398</v>
+      </c>
+      <c r="E13">
+        <v>219.801</v>
+      </c>
+      <c r="F13">
+        <v>234.201</v>
+      </c>
+      <c r="G13">
+        <v>6.26</v>
+      </c>
+      <c r="H13">
+        <v>2114.7</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>70.2</v>
+      </c>
+      <c r="K13">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L13">
+        <v>61.3</v>
+      </c>
+      <c r="M13">
+        <v>11.9208309</v>
+      </c>
+      <c r="N13">
+        <v>49.3791691</v>
+      </c>
+      <c r="O13">
+        <v>12.344792275</v>
+      </c>
+      <c r="P13">
+        <v>37.034376825</v>
+      </c>
+      <c r="Q13">
+        <v>45.934376825</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1983599769144434</v>
+      </c>
+      <c r="T13">
+        <v>1.13117850910666</v>
+      </c>
+      <c r="U13">
+        <v>0.0509</v>
+      </c>
+      <c r="V13">
+        <v>0.25</v>
+      </c>
+      <c r="W13">
+        <v>0.038175</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>5.142259001425815</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1803683193524308</v>
+      </c>
+      <c r="C14">
+        <v>1942.039056988349</v>
+      </c>
+      <c r="D14">
+        <v>2191.271056988348</v>
+      </c>
+      <c r="E14">
+        <v>241.092</v>
+      </c>
+      <c r="F14">
+        <v>255.492</v>
+      </c>
+      <c r="G14">
+        <v>6.26</v>
+      </c>
+      <c r="H14">
+        <v>2114.7</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>70.2</v>
+      </c>
+      <c r="K14">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L14">
+        <v>61.3</v>
+      </c>
+      <c r="M14">
+        <v>13.0045428</v>
+      </c>
+      <c r="N14">
+        <v>48.2954572</v>
+      </c>
+      <c r="O14">
+        <v>12.0738643</v>
+      </c>
+      <c r="P14">
+        <v>36.2215929</v>
+      </c>
+      <c r="Q14">
+        <v>45.12159290000001</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1997583174459441</v>
+      </c>
+      <c r="T14">
+        <v>1.141091851965155</v>
+      </c>
+      <c r="U14">
+        <v>0.0509</v>
+      </c>
+      <c r="V14">
+        <v>0.25</v>
+      </c>
+      <c r="W14">
+        <v>0.038175</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>4.713737417973665</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.180250509251007</v>
+      </c>
+      <c r="C15">
+        <v>1922.573104256384</v>
+      </c>
+      <c r="D15">
+        <v>2193.096104256384</v>
+      </c>
+      <c r="E15">
+        <v>262.383</v>
+      </c>
+      <c r="F15">
+        <v>276.783</v>
+      </c>
+      <c r="G15">
+        <v>6.26</v>
+      </c>
+      <c r="H15">
+        <v>2114.7</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>70.2</v>
+      </c>
+      <c r="K15">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L15">
+        <v>61.3</v>
+      </c>
+      <c r="M15">
+        <v>14.8078905</v>
+      </c>
+      <c r="N15">
+        <v>46.4921095</v>
+      </c>
+      <c r="O15">
+        <v>11.623027375</v>
+      </c>
+      <c r="P15">
+        <v>34.869082125</v>
+      </c>
+      <c r="Q15">
+        <v>43.769082125</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.2011888037367897</v>
+      </c>
+      <c r="T15">
+        <v>1.151233087762925</v>
+      </c>
+      <c r="U15">
+        <v>0.0535</v>
+      </c>
+      <c r="V15">
+        <v>0.25</v>
+      </c>
+      <c r="W15">
+        <v>0.040125</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>4.139684852477805</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1801821991495832</v>
+      </c>
+      <c r="C16">
+        <v>1902.341718678957</v>
+      </c>
+      <c r="D16">
+        <v>2194.155718678956</v>
+      </c>
+      <c r="E16">
+        <v>283.674</v>
+      </c>
+      <c r="F16">
+        <v>298.074</v>
+      </c>
+      <c r="G16">
+        <v>6.26</v>
+      </c>
+      <c r="H16">
+        <v>2114.7</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>70.2</v>
+      </c>
+      <c r="K16">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L16">
+        <v>61.3</v>
+      </c>
+      <c r="M16">
+        <v>16.7517588</v>
+      </c>
+      <c r="N16">
+        <v>44.54824119999999</v>
+      </c>
+      <c r="O16">
+        <v>11.1370603</v>
+      </c>
+      <c r="P16">
+        <v>33.41118089999999</v>
+      </c>
+      <c r="Q16">
+        <v>42.3111809</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.2026525571506782</v>
+      </c>
+      <c r="T16">
+        <v>1.161610166253668</v>
+      </c>
+      <c r="U16">
+        <v>0.0562</v>
+      </c>
+      <c r="V16">
+        <v>0.25</v>
+      </c>
+      <c r="W16">
+        <v>0.04215</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>3.659317253302381</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1803793890481594</v>
+      </c>
+      <c r="C17">
+        <v>1877.994727644276</v>
+      </c>
+      <c r="D17">
+        <v>2191.099727644276</v>
+      </c>
+      <c r="E17">
+        <v>304.965</v>
+      </c>
+      <c r="F17">
+        <v>319.365</v>
+      </c>
+      <c r="G17">
+        <v>6.26</v>
+      </c>
+      <c r="H17">
+        <v>2114.7</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>70.2</v>
+      </c>
+      <c r="K17">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L17">
+        <v>61.3</v>
+      </c>
+      <c r="M17">
+        <v>19.4493285</v>
+      </c>
+      <c r="N17">
+        <v>41.8506715</v>
+      </c>
+      <c r="O17">
+        <v>10.462667875</v>
+      </c>
+      <c r="P17">
+        <v>31.388003625</v>
+      </c>
+      <c r="Q17">
+        <v>40.28800362500001</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.204150751821364</v>
+      </c>
+      <c r="T17">
+        <v>1.172231411297133</v>
+      </c>
+      <c r="U17">
+        <v>0.0609</v>
+      </c>
+      <c r="V17">
+        <v>0.25</v>
+      </c>
+      <c r="W17">
+        <v>0.045675</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>3.151779764530175</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1811990789467356</v>
+      </c>
+      <c r="C18">
+        <v>1844.091129818451</v>
+      </c>
+      <c r="D18">
+        <v>2178.487129818451</v>
+      </c>
+      <c r="E18">
+        <v>326.256</v>
+      </c>
+      <c r="F18">
+        <v>340.656</v>
+      </c>
+      <c r="G18">
+        <v>6.26</v>
+      </c>
+      <c r="H18">
+        <v>2114.7</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>70.2</v>
+      </c>
+      <c r="K18">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L18">
+        <v>61.3</v>
+      </c>
+      <c r="M18">
+        <v>23.9140512</v>
+      </c>
+      <c r="N18">
+        <v>37.38594879999999</v>
+      </c>
+      <c r="O18">
+        <v>9.346487199999999</v>
+      </c>
+      <c r="P18">
+        <v>28.0394616</v>
+      </c>
+      <c r="Q18">
+        <v>36.9394616</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.2056846177937329</v>
+      </c>
+      <c r="T18">
+        <v>1.183105543127347</v>
+      </c>
+      <c r="U18">
+        <v>0.0702</v>
+      </c>
+      <c r="V18">
+        <v>0.25</v>
+      </c>
+      <c r="W18">
+        <v>0.05265</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>2.563346523235678</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1815717688453118</v>
+      </c>
+      <c r="C19">
+        <v>1817.113430311763</v>
+      </c>
+      <c r="D19">
+        <v>2172.800430311763</v>
+      </c>
+      <c r="E19">
+        <v>347.547</v>
+      </c>
+      <c r="F19">
+        <v>361.947</v>
+      </c>
+      <c r="G19">
+        <v>6.26</v>
+      </c>
+      <c r="H19">
+        <v>2114.7</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>70.2</v>
+      </c>
+      <c r="K19">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L19">
+        <v>61.3</v>
+      </c>
+      <c r="M19">
+        <v>27.1098303</v>
+      </c>
+      <c r="N19">
+        <v>34.1901697</v>
+      </c>
+      <c r="O19">
+        <v>8.547542425</v>
+      </c>
+      <c r="P19">
+        <v>25.642627275</v>
+      </c>
+      <c r="Q19">
+        <v>34.542627275</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.207255444391942</v>
+      </c>
+      <c r="T19">
+        <v>1.194241702230579</v>
+      </c>
+      <c r="U19">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V19">
+        <v>0.25</v>
+      </c>
+      <c r="W19">
+        <v>0.056175</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>2.261172398412246</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1813804587438881</v>
+      </c>
+      <c r="C20">
+        <v>1798.73782751527</v>
+      </c>
+      <c r="D20">
+        <v>2175.715827515269</v>
+      </c>
+      <c r="E20">
+        <v>368.838</v>
+      </c>
+      <c r="F20">
+        <v>383.2379999999999</v>
+      </c>
+      <c r="G20">
+        <v>6.26</v>
+      </c>
+      <c r="H20">
+        <v>2114.7</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>70.2</v>
+      </c>
+      <c r="K20">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L20">
+        <v>61.3</v>
+      </c>
+      <c r="M20">
+        <v>28.70452619999999</v>
+      </c>
+      <c r="N20">
+        <v>32.59547380000001</v>
+      </c>
+      <c r="O20">
+        <v>8.148868450000002</v>
+      </c>
+      <c r="P20">
+        <v>24.44660535000001</v>
+      </c>
+      <c r="Q20">
+        <v>33.34660535000001</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.2088645838340098</v>
+      </c>
+      <c r="T20">
+        <v>1.205649474970475</v>
+      </c>
+      <c r="U20">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V20">
+        <v>0.25</v>
+      </c>
+      <c r="W20">
+        <v>0.056175</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>2.135551709611567</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1811891486424643</v>
+      </c>
+      <c r="C21">
+        <v>1780.370058812033</v>
+      </c>
+      <c r="D21">
+        <v>2178.639058812033</v>
+      </c>
+      <c r="E21">
+        <v>390.129</v>
+      </c>
+      <c r="F21">
+        <v>404.529</v>
+      </c>
+      <c r="G21">
+        <v>6.26</v>
+      </c>
+      <c r="H21">
+        <v>2114.7</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>70.2</v>
+      </c>
+      <c r="K21">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L21">
+        <v>61.3</v>
+      </c>
+      <c r="M21">
+        <v>30.2992221</v>
+      </c>
+      <c r="N21">
+        <v>31.0007779</v>
+      </c>
+      <c r="O21">
+        <v>7.750194475</v>
+      </c>
+      <c r="P21">
+        <v>23.250583425</v>
+      </c>
+      <c r="Q21">
+        <v>32.15058342500001</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.2105134551141535</v>
+      </c>
+      <c r="T21">
+        <v>1.217338921111357</v>
+      </c>
+      <c r="U21">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V21">
+        <v>0.25</v>
+      </c>
+      <c r="W21">
+        <v>0.056175</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>2.023154251210958</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1834428385410405</v>
+      </c>
+      <c r="C22">
+        <v>1725.133535556175</v>
+      </c>
+      <c r="D22">
+        <v>2144.693535556175</v>
+      </c>
+      <c r="E22">
+        <v>411.42</v>
+      </c>
+      <c r="F22">
+        <v>425.82</v>
+      </c>
+      <c r="G22">
+        <v>6.26</v>
+      </c>
+      <c r="H22">
+        <v>2114.7</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>70.2</v>
+      </c>
+      <c r="K22">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L22">
+        <v>61.3</v>
+      </c>
+      <c r="M22">
+        <v>38.834784</v>
+      </c>
+      <c r="N22">
+        <v>22.465216</v>
+      </c>
+      <c r="O22">
+        <v>5.616304</v>
+      </c>
+      <c r="P22">
+        <v>16.848912</v>
+      </c>
+      <c r="Q22">
+        <v>25.748912</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.2122035481763006</v>
+      </c>
+      <c r="T22">
+        <v>1.22932060340576</v>
+      </c>
+      <c r="U22">
+        <v>0.0912</v>
+      </c>
+      <c r="V22">
+        <v>0.25</v>
+      </c>
+      <c r="W22">
+        <v>0.0684</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>1.578481806413549</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1833737784396167</v>
+      </c>
+      <c r="C23">
+        <v>1704.867014231957</v>
+      </c>
+      <c r="D23">
+        <v>2145.718014231956</v>
+      </c>
+      <c r="E23">
+        <v>432.711</v>
+      </c>
+      <c r="F23">
+        <v>447.111</v>
+      </c>
+      <c r="G23">
+        <v>6.26</v>
+      </c>
+      <c r="H23">
+        <v>2114.7</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>70.2</v>
+      </c>
+      <c r="K23">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L23">
+        <v>61.3</v>
+      </c>
+      <c r="M23">
+        <v>40.7765232</v>
+      </c>
+      <c r="N23">
+        <v>20.5234768</v>
+      </c>
+      <c r="O23">
+        <v>5.130869199999999</v>
+      </c>
+      <c r="P23">
+        <v>15.3926076</v>
+      </c>
+      <c r="Q23">
+        <v>24.2926076</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.2139364284045781</v>
+      </c>
+      <c r="T23">
+        <v>1.241605619429135</v>
+      </c>
+      <c r="U23">
+        <v>0.0912</v>
+      </c>
+      <c r="V23">
+        <v>0.25</v>
+      </c>
+      <c r="W23">
+        <v>0.0684</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>1.503316006108142</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1968303941293257</v>
+      </c>
+      <c r="C24">
+        <v>1500.86367680416</v>
+      </c>
+      <c r="D24">
+        <v>1963.00567680416</v>
+      </c>
+      <c r="E24">
+        <v>454.002</v>
+      </c>
+      <c r="F24">
+        <v>468.402</v>
+      </c>
+      <c r="G24">
+        <v>6.26</v>
+      </c>
+      <c r="H24">
+        <v>2114.7</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>70.2</v>
+      </c>
+      <c r="K24">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L24">
+        <v>61.3</v>
+      </c>
+      <c r="M24">
+        <v>73.3517532</v>
+      </c>
+      <c r="N24">
+        <v>-12.05175320000001</v>
+      </c>
+      <c r="O24">
+        <v>-3.012938300000002</v>
+      </c>
+      <c r="P24">
+        <v>-9.038814900000006</v>
+      </c>
+      <c r="Q24">
+        <v>-0.1388148999999999</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.2174054758545788</v>
+      </c>
+      <c r="T24">
+        <v>1.266198954163798</v>
+      </c>
+      <c r="U24">
+        <v>0.1566</v>
+      </c>
+      <c r="V24">
+        <v>0.2089247949972653</v>
+      </c>
+      <c r="W24">
+        <v>0.1238823771034283</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>0.8356991799890612</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.2116923364800619</v>
+      </c>
+      <c r="C25">
+        <v>1310.83137920364</v>
+      </c>
+      <c r="D25">
+        <v>1794.26437920364</v>
+      </c>
+      <c r="E25">
+        <v>475.293</v>
+      </c>
+      <c r="F25">
+        <v>489.693</v>
+      </c>
+      <c r="G25">
+        <v>6.26</v>
+      </c>
+      <c r="H25">
+        <v>2114.7</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>70.2</v>
+      </c>
+      <c r="K25">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L25">
+        <v>61.3</v>
+      </c>
+      <c r="M25">
+        <v>102.2478984</v>
+      </c>
+      <c r="N25">
+        <v>-40.9478984</v>
+      </c>
+      <c r="O25">
+        <v>-10.2369746</v>
+      </c>
+      <c r="P25">
+        <v>-30.7109238</v>
+      </c>
+      <c r="Q25">
+        <v>-21.81092379999999</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.2219041733991008</v>
+      </c>
+      <c r="T25">
+        <v>1.298091851616791</v>
+      </c>
+      <c r="U25">
+        <v>0.2088</v>
+      </c>
+      <c r="V25">
+        <v>0.1498808311936903</v>
+      </c>
+      <c r="W25">
+        <v>0.1775048824467575</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>0.5995233247747613</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.2133923364800619</v>
+      </c>
+      <c r="C26">
+        <v>1272.06968429147</v>
+      </c>
+      <c r="D26">
+        <v>1776.79368429147</v>
+      </c>
+      <c r="E26">
+        <v>496.584</v>
+      </c>
+      <c r="F26">
+        <v>510.984</v>
+      </c>
+      <c r="G26">
+        <v>6.26</v>
+      </c>
+      <c r="H26">
+        <v>2114.7</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>70.2</v>
+      </c>
+      <c r="K26">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L26">
+        <v>61.3</v>
+      </c>
+      <c r="M26">
+        <v>106.6934592</v>
+      </c>
+      <c r="N26">
+        <v>-45.39345920000001</v>
+      </c>
+      <c r="O26">
+        <v>-11.3483648</v>
+      </c>
+      <c r="P26">
+        <v>-34.04509440000001</v>
+      </c>
+      <c r="Q26">
+        <v>-25.1450944</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.2243134388385627</v>
+      </c>
+      <c r="T26">
+        <v>1.315172007559117</v>
+      </c>
+      <c r="U26">
+        <v>0.2088</v>
+      </c>
+      <c r="V26">
+        <v>0.1436357965606199</v>
+      </c>
+      <c r="W26">
+        <v>0.1788088456781426</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>0.5745431862424796</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.2150923364800618</v>
+      </c>
+      <c r="C27">
+        <v>1233.64493177786</v>
+      </c>
+      <c r="D27">
+        <v>1759.65993177786</v>
+      </c>
+      <c r="E27">
+        <v>517.875</v>
+      </c>
+      <c r="F27">
+        <v>532.275</v>
+      </c>
+      <c r="G27">
+        <v>6.26</v>
+      </c>
+      <c r="H27">
+        <v>2114.7</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>70.2</v>
+      </c>
+      <c r="K27">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L27">
+        <v>61.3</v>
+      </c>
+      <c r="M27">
+        <v>111.13902</v>
+      </c>
+      <c r="N27">
+        <v>-49.83902</v>
+      </c>
+      <c r="O27">
+        <v>-12.459755</v>
+      </c>
+      <c r="P27">
+        <v>-37.379265</v>
+      </c>
+      <c r="Q27">
+        <v>-28.479265</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.2267869513564102</v>
+      </c>
+      <c r="T27">
+        <v>1.332707634326572</v>
+      </c>
+      <c r="U27">
+        <v>0.2088</v>
+      </c>
+      <c r="V27">
+        <v>0.1378903646981951</v>
+      </c>
+      <c r="W27">
+        <v>0.1800084918510169</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>0.5515614587927804</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.2167923364800619</v>
+      </c>
+      <c r="C28">
+        <v>1195.547467279555</v>
+      </c>
+      <c r="D28">
+        <v>1742.853467279555</v>
+      </c>
+      <c r="E28">
+        <v>539.1660000000001</v>
+      </c>
+      <c r="F28">
+        <v>553.566</v>
+      </c>
+      <c r="G28">
+        <v>6.26</v>
+      </c>
+      <c r="H28">
+        <v>2114.7</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>70.2</v>
+      </c>
+      <c r="K28">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L28">
+        <v>61.3</v>
+      </c>
+      <c r="M28">
+        <v>115.5845808</v>
+      </c>
+      <c r="N28">
+        <v>-54.28458080000001</v>
+      </c>
+      <c r="O28">
+        <v>-13.5711452</v>
+      </c>
+      <c r="P28">
+        <v>-40.71343560000001</v>
+      </c>
+      <c r="Q28">
+        <v>-31.81343560000001</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.2293273155639292</v>
+      </c>
+      <c r="T28">
+        <v>1.350717196952607</v>
+      </c>
+      <c r="U28">
+        <v>0.2088</v>
+      </c>
+      <c r="V28">
+        <v>0.1325868891328799</v>
+      </c>
+      <c r="W28">
+        <v>0.1811158575490547</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.5303475565315195</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.2184923364800619</v>
+      </c>
+      <c r="C29">
+        <v>1157.768001758913</v>
+      </c>
+      <c r="D29">
+        <v>1726.365001758913</v>
+      </c>
+      <c r="E29">
+        <v>560.457</v>
+      </c>
+      <c r="F29">
+        <v>574.857</v>
+      </c>
+      <c r="G29">
+        <v>6.26</v>
+      </c>
+      <c r="H29">
+        <v>2114.7</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>70.2</v>
+      </c>
+      <c r="K29">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L29">
+        <v>61.3</v>
+      </c>
+      <c r="M29">
+        <v>120.0301416</v>
+      </c>
+      <c r="N29">
+        <v>-58.73014160000001</v>
+      </c>
+      <c r="O29">
+        <v>-14.6825354</v>
+      </c>
+      <c r="P29">
+        <v>-44.0476062</v>
+      </c>
+      <c r="Q29">
+        <v>-35.1476062</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.2319372787908324</v>
+      </c>
+      <c r="T29">
+        <v>1.369220172253327</v>
+      </c>
+      <c r="U29">
+        <v>0.2088</v>
+      </c>
+      <c r="V29">
+        <v>0.1276762636094399</v>
+      </c>
+      <c r="W29">
+        <v>0.182141196158349</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.5107050544377596</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.2292247268132539</v>
+      </c>
+      <c r="C30">
+        <v>1039.178592216708</v>
+      </c>
+      <c r="D30">
+        <v>1629.066592216708</v>
+      </c>
+      <c r="E30">
+        <v>581.748</v>
+      </c>
+      <c r="F30">
+        <v>596.148</v>
+      </c>
+      <c r="G30">
+        <v>6.26</v>
+      </c>
+      <c r="H30">
+        <v>2114.7</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>70.2</v>
+      </c>
+      <c r="K30">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L30">
+        <v>61.3</v>
+      </c>
+      <c r="M30">
+        <v>142.3601424</v>
+      </c>
+      <c r="N30">
+        <v>-81.0601424</v>
+      </c>
+      <c r="O30">
+        <v>-20.2650356</v>
+      </c>
+      <c r="P30">
+        <v>-60.7951068</v>
+      </c>
+      <c r="Q30">
+        <v>-51.89510679999999</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.2354980609034718</v>
+      </c>
+      <c r="T30">
+        <v>1.394463847260807</v>
+      </c>
+      <c r="U30">
+        <v>0.2388</v>
+      </c>
+      <c r="V30">
+        <v>0.1076495130002062</v>
+      </c>
+      <c r="W30">
+        <v>0.2130932962955508</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.4305980520008246</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.2312247268132539</v>
+      </c>
+      <c r="C31">
+        <v>1000.955604117302</v>
+      </c>
+      <c r="D31">
+        <v>1612.134604117302</v>
+      </c>
+      <c r="E31">
+        <v>603.039</v>
+      </c>
+      <c r="F31">
+        <v>617.439</v>
+      </c>
+      <c r="G31">
+        <v>6.26</v>
+      </c>
+      <c r="H31">
+        <v>2114.7</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>70.2</v>
+      </c>
+      <c r="K31">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L31">
+        <v>61.3</v>
+      </c>
+      <c r="M31">
+        <v>147.4444332</v>
+      </c>
+      <c r="N31">
+        <v>-86.14443319999999</v>
+      </c>
+      <c r="O31">
+        <v>-21.5361083</v>
+      </c>
+      <c r="P31">
+        <v>-64.6083249</v>
+      </c>
+      <c r="Q31">
+        <v>-55.70832489999999</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.2382684561274643</v>
+      </c>
+      <c r="T31">
+        <v>1.414104183137719</v>
+      </c>
+      <c r="U31">
+        <v>0.2388</v>
+      </c>
+      <c r="V31">
+        <v>0.1039374608277853</v>
+      </c>
+      <c r="W31">
+        <v>0.2139797343543249</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.4157498433111411</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.2332247268132539</v>
+      </c>
+      <c r="C32">
+        <v>963.0809665261251</v>
+      </c>
+      <c r="D32">
+        <v>1595.550966526125</v>
+      </c>
+      <c r="E32">
+        <v>624.3299999999999</v>
+      </c>
+      <c r="F32">
+        <v>638.7299999999999</v>
+      </c>
+      <c r="G32">
+        <v>6.26</v>
+      </c>
+      <c r="H32">
+        <v>2114.7</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>70.2</v>
+      </c>
+      <c r="K32">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L32">
+        <v>61.3</v>
+      </c>
+      <c r="M32">
+        <v>152.528724</v>
+      </c>
+      <c r="N32">
+        <v>-91.22872399999999</v>
+      </c>
+      <c r="O32">
+        <v>-22.807181</v>
+      </c>
+      <c r="P32">
+        <v>-68.42154299999999</v>
+      </c>
+      <c r="Q32">
+        <v>-59.52154299999998</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.2411180055007139</v>
+      </c>
+      <c r="T32">
+        <v>1.434305671468258</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>0.1004728788001924</v>
+      </c>
+      <c r="W32">
+        <v>0.2148070765425141</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.4018915152007697</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.2352247268132539</v>
+      </c>
+      <c r="C33">
+        <v>925.5440387102951</v>
+      </c>
+      <c r="D33">
+        <v>1579.305038710295</v>
+      </c>
+      <c r="E33">
+        <v>645.621</v>
+      </c>
+      <c r="F33">
+        <v>660.021</v>
+      </c>
+      <c r="G33">
+        <v>6.26</v>
+      </c>
+      <c r="H33">
+        <v>2114.7</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>70.2</v>
+      </c>
+      <c r="K33">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L33">
+        <v>61.3</v>
+      </c>
+      <c r="M33">
+        <v>157.6130148</v>
+      </c>
+      <c r="N33">
+        <v>-96.3130148</v>
+      </c>
+      <c r="O33">
+        <v>-24.0782537</v>
+      </c>
+      <c r="P33">
+        <v>-72.2347611</v>
+      </c>
+      <c r="Q33">
+        <v>-63.33476109999999</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.2440501505079705</v>
+      </c>
+      <c r="T33">
+        <v>1.455092710185189</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>0.0972318181937346</v>
+      </c>
+      <c r="W33">
+        <v>0.2155810418153362</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.3889272727749383</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.2372247268132539</v>
+      </c>
+      <c r="C34">
+        <v>888.3346089452724</v>
+      </c>
+      <c r="D34">
+        <v>1563.386608945272</v>
+      </c>
+      <c r="E34">
+        <v>666.912</v>
+      </c>
+      <c r="F34">
+        <v>681.312</v>
+      </c>
+      <c r="G34">
+        <v>6.26</v>
+      </c>
+      <c r="H34">
+        <v>2114.7</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>70.2</v>
+      </c>
+      <c r="K34">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L34">
+        <v>61.3</v>
+      </c>
+      <c r="M34">
+        <v>162.6973056</v>
+      </c>
+      <c r="N34">
+        <v>-101.3973056</v>
+      </c>
+      <c r="O34">
+        <v>-25.34932640000001</v>
+      </c>
+      <c r="P34">
+        <v>-76.04797920000001</v>
+      </c>
+      <c r="Q34">
+        <v>-67.14797920000001</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.2470685350742642</v>
+      </c>
+      <c r="T34">
+        <v>1.476491132393795</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>0.09419332387518037</v>
+      </c>
+      <c r="W34">
+        <v>0.2163066342586069</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.3767732955007215</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.2392247268132539</v>
+      </c>
+      <c r="C35">
+        <v>851.4428731098989</v>
+      </c>
+      <c r="D35">
+        <v>1547.785873109899</v>
+      </c>
+      <c r="E35">
+        <v>688.203</v>
+      </c>
+      <c r="F35">
+        <v>702.603</v>
+      </c>
+      <c r="G35">
+        <v>6.26</v>
+      </c>
+      <c r="H35">
+        <v>2114.7</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>70.2</v>
+      </c>
+      <c r="K35">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L35">
+        <v>61.3</v>
+      </c>
+      <c r="M35">
+        <v>167.7815964</v>
+      </c>
+      <c r="N35">
+        <v>-106.4815964</v>
+      </c>
+      <c r="O35">
+        <v>-26.6203991</v>
+      </c>
+      <c r="P35">
+        <v>-79.86119729999999</v>
+      </c>
+      <c r="Q35">
+        <v>-70.96119729999998</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.2501770206723876</v>
+      </c>
+      <c r="T35">
+        <v>1.4985283134743</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>0.09133898072744766</v>
+      </c>
+      <c r="W35">
+        <v>0.2169882514022855</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.3653559229097906</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.2412247268132539</v>
+      </c>
+      <c r="C36">
+        <v>814.8594145503491</v>
+      </c>
+      <c r="D36">
+        <v>1532.493414550349</v>
+      </c>
+      <c r="E36">
+        <v>709.494</v>
+      </c>
+      <c r="F36">
+        <v>723.894</v>
+      </c>
+      <c r="G36">
+        <v>6.26</v>
+      </c>
+      <c r="H36">
+        <v>2114.7</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>70.2</v>
+      </c>
+      <c r="K36">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L36">
+        <v>61.3</v>
+      </c>
+      <c r="M36">
+        <v>172.8658872</v>
+      </c>
+      <c r="N36">
+        <v>-111.5658872</v>
+      </c>
+      <c r="O36">
+        <v>-27.8914718</v>
+      </c>
+      <c r="P36">
+        <v>-83.6744154</v>
+      </c>
+      <c r="Q36">
+        <v>-74.7744154</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.2533797028037874</v>
+      </c>
+      <c r="T36">
+        <v>1.52123328792088</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>0.08865254011781683</v>
+      </c>
+      <c r="W36">
+        <v>0.2176297734198653</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.3546101604712674</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.2432247268132539</v>
+      </c>
+      <c r="C37">
+        <v>778.5751851260994</v>
+      </c>
+      <c r="D37">
+        <v>1517.500185126099</v>
+      </c>
+      <c r="E37">
+        <v>730.7850000000001</v>
+      </c>
+      <c r="F37">
+        <v>745.1850000000001</v>
+      </c>
+      <c r="G37">
+        <v>6.26</v>
+      </c>
+      <c r="H37">
+        <v>2114.7</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>70.2</v>
+      </c>
+      <c r="K37">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L37">
+        <v>61.3</v>
+      </c>
+      <c r="M37">
+        <v>177.950178</v>
+      </c>
+      <c r="N37">
+        <v>-116.650178</v>
+      </c>
+      <c r="O37">
+        <v>-29.16254450000001</v>
+      </c>
+      <c r="P37">
+        <v>-87.48763350000002</v>
+      </c>
+      <c r="Q37">
+        <v>-78.58763350000001</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.2566809290007688</v>
+      </c>
+      <c r="T37">
+        <v>1.544636876965817</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>0.08611961040016491</v>
+      </c>
+      <c r="W37">
+        <v>0.2182346370364406</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.3444784416006597</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.2452247268132539</v>
+      </c>
+      <c r="C38">
+        <v>742.5814873577367</v>
+      </c>
+      <c r="D38">
+        <v>1502.797487357737</v>
+      </c>
+      <c r="E38">
+        <v>752.0759999999999</v>
+      </c>
+      <c r="F38">
+        <v>766.4759999999999</v>
+      </c>
+      <c r="G38">
+        <v>6.26</v>
+      </c>
+      <c r="H38">
+        <v>2114.7</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>70.2</v>
+      </c>
+      <c r="K38">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L38">
+        <v>61.3</v>
+      </c>
+      <c r="M38">
+        <v>183.0344688</v>
+      </c>
+      <c r="N38">
+        <v>-121.7344688</v>
+      </c>
+      <c r="O38">
+        <v>-30.4336172</v>
+      </c>
+      <c r="P38">
+        <v>-91.30085159999999</v>
+      </c>
+      <c r="Q38">
+        <v>-82.40085159999998</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.2600853185164057</v>
+      </c>
+      <c r="T38">
+        <v>1.568771828168407</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>0.08372739900016035</v>
+      </c>
+      <c r="W38">
+        <v>0.2188058971187617</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.3349095960006414</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.2472247268132539</v>
+      </c>
+      <c r="C39">
+        <v>706.8699576026057</v>
+      </c>
+      <c r="D39">
+        <v>1488.376957602606</v>
+      </c>
+      <c r="E39">
+        <v>773.367</v>
+      </c>
+      <c r="F39">
+        <v>787.7669999999999</v>
+      </c>
+      <c r="G39">
+        <v>6.26</v>
+      </c>
+      <c r="H39">
+        <v>2114.7</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>70.2</v>
+      </c>
+      <c r="K39">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L39">
+        <v>61.3</v>
+      </c>
+      <c r="M39">
+        <v>188.1187596</v>
+      </c>
+      <c r="N39">
+        <v>-126.8187596</v>
+      </c>
+      <c r="O39">
+        <v>-31.7046899</v>
+      </c>
+      <c r="P39">
+        <v>-95.1140697</v>
+      </c>
+      <c r="Q39">
+        <v>-86.2140697</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.263597783889682</v>
+      </c>
+      <c r="T39">
+        <v>1.593672968298065</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>0.08146449632448033</v>
+      </c>
+      <c r="W39">
+        <v>0.2193462782777141</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.3258579852979213</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.2492247268132539</v>
+      </c>
+      <c r="C40">
+        <v>671.4325501899118</v>
+      </c>
+      <c r="D40">
+        <v>1474.230550189912</v>
+      </c>
+      <c r="E40">
+        <v>794.658</v>
+      </c>
+      <c r="F40">
+        <v>809.058</v>
+      </c>
+      <c r="G40">
+        <v>6.26</v>
+      </c>
+      <c r="H40">
+        <v>2114.7</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>70.2</v>
+      </c>
+      <c r="K40">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L40">
+        <v>61.3</v>
+      </c>
+      <c r="M40">
+        <v>193.2030504</v>
+      </c>
+      <c r="N40">
+        <v>-131.9030504</v>
+      </c>
+      <c r="O40">
+        <v>-32.9757626</v>
+      </c>
+      <c r="P40">
+        <v>-98.92728779999999</v>
+      </c>
+      <c r="Q40">
+        <v>-90.02728779999998</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.2672235545975801</v>
+      </c>
+      <c r="T40">
+        <v>1.619377371012549</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>0.07932069378962558</v>
+      </c>
+      <c r="W40">
+        <v>0.2198582183230374</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.3172827751585025</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.2512247268132539</v>
+      </c>
+      <c r="C41">
+        <v>636.2615224520297</v>
+      </c>
+      <c r="D41">
+        <v>1460.35052245203</v>
+      </c>
+      <c r="E41">
+        <v>815.9490000000001</v>
+      </c>
+      <c r="F41">
+        <v>830.349</v>
+      </c>
+      <c r="G41">
+        <v>6.26</v>
+      </c>
+      <c r="H41">
+        <v>2114.7</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>70.2</v>
+      </c>
+      <c r="K41">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L41">
+        <v>61.3</v>
+      </c>
+      <c r="M41">
+        <v>198.2873412</v>
+      </c>
+      <c r="N41">
+        <v>-136.9873412</v>
+      </c>
+      <c r="O41">
+        <v>-34.2468353</v>
+      </c>
+      <c r="P41">
+        <v>-102.7405059</v>
+      </c>
+      <c r="Q41">
+        <v>-93.8405059</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.2709682030336061</v>
+      </c>
+      <c r="T41">
+        <v>1.645924541029149</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>0.07728682984630185</v>
+      </c>
+      <c r="W41">
+        <v>0.2203439050327031</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.3091473193852075</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.2532247268132539</v>
+      </c>
+      <c r="C42">
+        <v>601.3494205935314</v>
+      </c>
+      <c r="D42">
+        <v>1446.729420593531</v>
+      </c>
+      <c r="E42">
+        <v>837.24</v>
+      </c>
+      <c r="F42">
+        <v>851.64</v>
+      </c>
+      <c r="G42">
+        <v>6.26</v>
+      </c>
+      <c r="H42">
+        <v>2114.7</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>70.2</v>
+      </c>
+      <c r="K42">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L42">
+        <v>61.3</v>
+      </c>
+      <c r="M42">
+        <v>203.371632</v>
+      </c>
+      <c r="N42">
+        <v>-142.071632</v>
+      </c>
+      <c r="O42">
+        <v>-35.51790800000001</v>
+      </c>
+      <c r="P42">
+        <v>-106.553724</v>
+      </c>
+      <c r="Q42">
+        <v>-97.65372400000001</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.2748376730841662</v>
+      </c>
+      <c r="T42">
+        <v>1.673356616712968</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0.0753546591001443</v>
+      </c>
+      <c r="W42">
+        <v>0.2208053074068856</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.3014186364005772</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.2552247268132539</v>
+      </c>
+      <c r="C43">
+        <v>566.6890663437107</v>
+      </c>
+      <c r="D43">
+        <v>1433.360066343711</v>
+      </c>
+      <c r="E43">
+        <v>858.5310000000001</v>
+      </c>
+      <c r="F43">
+        <v>872.931</v>
+      </c>
+      <c r="G43">
+        <v>6.26</v>
+      </c>
+      <c r="H43">
+        <v>2114.7</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>70.2</v>
+      </c>
+      <c r="K43">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L43">
+        <v>61.3</v>
+      </c>
+      <c r="M43">
+        <v>208.4559228</v>
+      </c>
+      <c r="N43">
+        <v>-147.1559228</v>
+      </c>
+      <c r="O43">
+        <v>-36.78898070000001</v>
+      </c>
+      <c r="P43">
+        <v>-110.3669421</v>
+      </c>
+      <c r="Q43">
+        <v>-101.4669421</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.2788383116110164</v>
+      </c>
+      <c r="T43">
+        <v>1.701718593267425</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0.07351674058550663</v>
+      </c>
+      <c r="W43">
+        <v>0.221244202348181</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.2940669623420265</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.2572247268132539</v>
+      </c>
+      <c r="C44">
+        <v>532.2735443424156</v>
+      </c>
+      <c r="D44">
+        <v>1420.235544342416</v>
+      </c>
+      <c r="E44">
+        <v>879.822</v>
+      </c>
+      <c r="F44">
+        <v>894.222</v>
+      </c>
+      <c r="G44">
+        <v>6.26</v>
+      </c>
+      <c r="H44">
+        <v>2114.7</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>70.2</v>
+      </c>
+      <c r="K44">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L44">
+        <v>61.3</v>
+      </c>
+      <c r="M44">
+        <v>213.5402136</v>
+      </c>
+      <c r="N44">
+        <v>-152.2402136</v>
+      </c>
+      <c r="O44">
+        <v>-38.0600534</v>
+      </c>
+      <c r="P44">
+        <v>-114.1801602</v>
+      </c>
+      <c r="Q44">
+        <v>-105.2801602</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.2829769031905167</v>
+      </c>
+      <c r="T44">
+        <v>1.731058569013415</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0.07176634200013743</v>
+      </c>
+      <c r="W44">
+        <v>0.2216621975303672</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.2870653680005498</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.2592247268132539</v>
+      </c>
+      <c r="C45">
+        <v>498.0961902125939</v>
+      </c>
+      <c r="D45">
+        <v>1407.349190212594</v>
+      </c>
+      <c r="E45">
+        <v>901.1129999999999</v>
+      </c>
+      <c r="F45">
+        <v>915.5129999999999</v>
+      </c>
+      <c r="G45">
+        <v>6.26</v>
+      </c>
+      <c r="H45">
+        <v>2114.7</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>70.2</v>
+      </c>
+      <c r="K45">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L45">
+        <v>61.3</v>
+      </c>
+      <c r="M45">
+        <v>218.6245044</v>
+      </c>
+      <c r="N45">
+        <v>-157.3245044</v>
+      </c>
+      <c r="O45">
+        <v>-39.33112609999999</v>
+      </c>
+      <c r="P45">
+        <v>-117.9933783</v>
+      </c>
+      <c r="Q45">
+        <v>-109.0933783</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.2872607085096486</v>
+      </c>
+      <c r="T45">
+        <v>1.761428017592598</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.07009735730245983</v>
+      </c>
+      <c r="W45">
+        <v>0.2220607510761726</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.2803894292098393</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.2612247268132539</v>
+      </c>
+      <c r="C46">
+        <v>464.1505792763356</v>
+      </c>
+      <c r="D46">
+        <v>1394.694579276336</v>
+      </c>
+      <c r="E46">
+        <v>922.404</v>
+      </c>
+      <c r="F46">
+        <v>936.804</v>
+      </c>
+      <c r="G46">
+        <v>6.26</v>
+      </c>
+      <c r="H46">
+        <v>2114.7</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>70.2</v>
+      </c>
+      <c r="K46">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L46">
+        <v>61.3</v>
+      </c>
+      <c r="M46">
+        <v>223.7087952</v>
+      </c>
+      <c r="N46">
+        <v>-162.4087952</v>
+      </c>
+      <c r="O46">
+        <v>-40.6021988</v>
+      </c>
+      <c r="P46">
+        <v>-121.8065964</v>
+      </c>
+      <c r="Q46">
+        <v>-112.9065964</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.2916975068758922</v>
+      </c>
+      <c r="T46">
+        <v>1.792882089335323</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.06850423554558574</v>
+      </c>
+      <c r="W46">
+        <v>0.2224411885517141</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.274016942182343</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.2632247268132539</v>
+      </c>
+      <c r="C47">
+        <v>430.4305158742723</v>
+      </c>
+      <c r="D47">
+        <v>1382.265515874272</v>
+      </c>
+      <c r="E47">
+        <v>943.6950000000001</v>
+      </c>
+      <c r="F47">
+        <v>958.095</v>
+      </c>
+      <c r="G47">
+        <v>6.26</v>
+      </c>
+      <c r="H47">
+        <v>2114.7</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>70.2</v>
+      </c>
+      <c r="K47">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L47">
+        <v>61.3</v>
+      </c>
+      <c r="M47">
+        <v>228.793086</v>
+      </c>
+      <c r="N47">
+        <v>-167.493086</v>
+      </c>
+      <c r="O47">
+        <v>-41.8732715</v>
+      </c>
+      <c r="P47">
+        <v>-125.6198145</v>
+      </c>
+      <c r="Q47">
+        <v>-116.7198145</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.2962956433645448</v>
+      </c>
+      <c r="T47">
+        <v>1.825479945505056</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.06698191920012826</v>
+      </c>
+      <c r="W47">
+        <v>0.2228047176950094</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.2679276768005131</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.2652247268132539</v>
+      </c>
+      <c r="C48">
+        <v>396.9300232510193</v>
+      </c>
+      <c r="D48">
+        <v>1370.056023251019</v>
+      </c>
+      <c r="E48">
+        <v>964.986</v>
+      </c>
+      <c r="F48">
+        <v>979.386</v>
+      </c>
+      <c r="G48">
+        <v>6.26</v>
+      </c>
+      <c r="H48">
+        <v>2114.7</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>70.2</v>
+      </c>
+      <c r="K48">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L48">
+        <v>61.3</v>
+      </c>
+      <c r="M48">
+        <v>233.8773768</v>
+      </c>
+      <c r="N48">
+        <v>-172.5773768</v>
+      </c>
+      <c r="O48">
+        <v>-43.14434420000001</v>
+      </c>
+      <c r="P48">
+        <v>-129.4330326</v>
+      </c>
+      <c r="Q48">
+        <v>-120.5330326</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.301064081204629</v>
+      </c>
+      <c r="T48">
+        <v>1.859285129681075</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.06552579052186461</v>
+      </c>
+      <c r="W48">
+        <v>0.2231524412233787</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.2621031620874584</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.2672247268132539</v>
+      </c>
+      <c r="C49">
+        <v>363.6433339719766</v>
+      </c>
+      <c r="D49">
+        <v>1358.060333971977</v>
+      </c>
+      <c r="E49">
+        <v>986.277</v>
+      </c>
+      <c r="F49">
+        <v>1000.677</v>
+      </c>
+      <c r="G49">
+        <v>6.26</v>
+      </c>
+      <c r="H49">
+        <v>2114.7</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>70.2</v>
+      </c>
+      <c r="K49">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L49">
+        <v>61.3</v>
+      </c>
+      <c r="M49">
+        <v>238.9616676</v>
+      </c>
+      <c r="N49">
+        <v>-177.6616676</v>
+      </c>
+      <c r="O49">
+        <v>-44.41541690000001</v>
+      </c>
+      <c r="P49">
+        <v>-133.2462507</v>
+      </c>
+      <c r="Q49">
+        <v>-124.3462507</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.3060124600952824</v>
+      </c>
+      <c r="T49">
+        <v>1.894365981184492</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.06413162476608025</v>
+      </c>
+      <c r="W49">
+        <v>0.2234853680058601</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.256526499064321</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.2692247268132539</v>
+      </c>
+      <c r="C50">
+        <v>330.5648808392003</v>
+      </c>
+      <c r="D50">
+        <v>1346.2728808392</v>
+      </c>
+      <c r="E50">
+        <v>1007.568</v>
+      </c>
+      <c r="F50">
+        <v>1021.968</v>
+      </c>
+      <c r="G50">
+        <v>6.26</v>
+      </c>
+      <c r="H50">
+        <v>2114.7</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>70.2</v>
+      </c>
+      <c r="K50">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L50">
+        <v>61.3</v>
+      </c>
+      <c r="M50">
+        <v>244.0459584</v>
+      </c>
+      <c r="N50">
+        <v>-182.7459584</v>
+      </c>
+      <c r="O50">
+        <v>-45.6864896</v>
+      </c>
+      <c r="P50">
+        <v>-137.0594688</v>
+      </c>
+      <c r="Q50">
+        <v>-128.1594688</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.3111511612509609</v>
+      </c>
+      <c r="T50">
+        <v>1.930796096207271</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.06279554925012026</v>
+      </c>
+      <c r="W50">
+        <v>0.2238044228390713</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.2511821970004809</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.2712247268132539</v>
+      </c>
+      <c r="C51">
+        <v>297.6892882762854</v>
+      </c>
+      <c r="D51">
+        <v>1334.688288276285</v>
+      </c>
+      <c r="E51">
+        <v>1028.859</v>
+      </c>
+      <c r="F51">
+        <v>1043.259</v>
+      </c>
+      <c r="G51">
+        <v>6.26</v>
+      </c>
+      <c r="H51">
+        <v>2114.7</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>70.2</v>
+      </c>
+      <c r="K51">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L51">
+        <v>61.3</v>
+      </c>
+      <c r="M51">
+        <v>249.1302492</v>
+      </c>
+      <c r="N51">
+        <v>-187.8302492</v>
+      </c>
+      <c r="O51">
+        <v>-46.95756230000001</v>
+      </c>
+      <c r="P51">
+        <v>-140.8726869</v>
+      </c>
+      <c r="Q51">
+        <v>-131.9726869</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.3164913800990189</v>
+      </c>
+      <c r="T51">
+        <v>1.968654843191727</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.06151400742868923</v>
+      </c>
+      <c r="W51">
+        <v>0.224110455026029</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.2460560297147568</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.2732247268132539</v>
+      </c>
+      <c r="C52">
+        <v>265.0113641542448</v>
+      </c>
+      <c r="D52">
+        <v>1323.301364154245</v>
+      </c>
+      <c r="E52">
+        <v>1050.15</v>
+      </c>
+      <c r="F52">
+        <v>1064.55</v>
+      </c>
+      <c r="G52">
+        <v>6.26</v>
+      </c>
+      <c r="H52">
+        <v>2114.7</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>70.2</v>
+      </c>
+      <c r="K52">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L52">
+        <v>61.3</v>
+      </c>
+      <c r="M52">
+        <v>254.21454</v>
+      </c>
+      <c r="N52">
+        <v>-192.91454</v>
+      </c>
+      <c r="O52">
+        <v>-48.228635</v>
+      </c>
+      <c r="P52">
+        <v>-144.685905</v>
+      </c>
+      <c r="Q52">
+        <v>-135.785905</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.3220452077009994</v>
+      </c>
+      <c r="T52">
+        <v>2.008027940055562</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.06028372728011545</v>
+      </c>
+      <c r="W52">
+        <v>0.2244042459255084</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.2411349091204619</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.2752247268132539</v>
+      </c>
+      <c r="C53">
+        <v>232.526092032281</v>
+      </c>
+      <c r="D53">
+        <v>1312.107092032281</v>
+      </c>
+      <c r="E53">
+        <v>1071.441</v>
+      </c>
+      <c r="F53">
+        <v>1085.841</v>
+      </c>
+      <c r="G53">
+        <v>6.26</v>
+      </c>
+      <c r="H53">
+        <v>2114.7</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>70.2</v>
+      </c>
+      <c r="K53">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L53">
+        <v>61.3</v>
+      </c>
+      <c r="M53">
+        <v>259.2988308</v>
+      </c>
+      <c r="N53">
+        <v>-197.9988308</v>
+      </c>
+      <c r="O53">
+        <v>-49.49970769999999</v>
+      </c>
+      <c r="P53">
+        <v>-148.4991231</v>
+      </c>
+      <c r="Q53">
+        <v>-139.5991231</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.327825722143877</v>
+      </c>
+      <c r="T53">
+        <v>2.049008102097512</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.0591016934118779</v>
+      </c>
+      <c r="W53">
+        <v>0.2246865156132436</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.2364067736475116</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2772247268132539</v>
+      </c>
+      <c r="C54">
+        <v>200.2286237890773</v>
+      </c>
+      <c r="D54">
+        <v>1301.100623789077</v>
+      </c>
+      <c r="E54">
+        <v>1092.732</v>
+      </c>
+      <c r="F54">
+        <v>1107.132</v>
+      </c>
+      <c r="G54">
+        <v>6.26</v>
+      </c>
+      <c r="H54">
+        <v>2114.7</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>70.2</v>
+      </c>
+      <c r="K54">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L54">
+        <v>61.3</v>
+      </c>
+      <c r="M54">
+        <v>264.3831216</v>
+      </c>
+      <c r="N54">
+        <v>-203.0831216</v>
+      </c>
+      <c r="O54">
+        <v>-50.77078040000001</v>
+      </c>
+      <c r="P54">
+        <v>-152.3123412</v>
+      </c>
+      <c r="Q54">
+        <v>-143.4123412</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.3338470913552077</v>
+      </c>
+      <c r="T54">
+        <v>2.09169577089121</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.05796512238472638</v>
+      </c>
+      <c r="W54">
+        <v>0.2249579287745274</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.2318604895389056</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2792247268132539</v>
+      </c>
+      <c r="C55">
+        <v>168.1142726218768</v>
+      </c>
+      <c r="D55">
+        <v>1290.277272621877</v>
+      </c>
+      <c r="E55">
+        <v>1114.023</v>
+      </c>
+      <c r="F55">
+        <v>1128.423</v>
+      </c>
+      <c r="G55">
+        <v>6.26</v>
+      </c>
+      <c r="H55">
+        <v>2114.7</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>70.2</v>
+      </c>
+      <c r="K55">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L55">
+        <v>61.3</v>
+      </c>
+      <c r="M55">
+        <v>269.4674124</v>
+      </c>
+      <c r="N55">
+        <v>-208.1674124</v>
+      </c>
+      <c r="O55">
+        <v>-52.0418531</v>
+      </c>
+      <c r="P55">
+        <v>-156.1255593</v>
+      </c>
+      <c r="Q55">
+        <v>-147.2255593</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.3401246890436164</v>
+      </c>
+      <c r="T55">
+        <v>2.136199936229321</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.05687144083029759</v>
+      </c>
+      <c r="W55">
+        <v>0.2252190999297249</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.2274857633211904</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2812247268132539</v>
+      </c>
+      <c r="C56">
+        <v>136.1785063921038</v>
+      </c>
+      <c r="D56">
+        <v>1279.632506392104</v>
+      </c>
+      <c r="E56">
+        <v>1135.314</v>
+      </c>
+      <c r="F56">
+        <v>1149.714</v>
+      </c>
+      <c r="G56">
+        <v>6.26</v>
+      </c>
+      <c r="H56">
+        <v>2114.7</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>70.2</v>
+      </c>
+      <c r="K56">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L56">
+        <v>61.3</v>
+      </c>
+      <c r="M56">
+        <v>274.5517032</v>
+      </c>
+      <c r="N56">
+        <v>-213.2517032</v>
+      </c>
+      <c r="O56">
+        <v>-53.3129258</v>
+      </c>
+      <c r="P56">
+        <v>-159.9387774</v>
+      </c>
+      <c r="Q56">
+        <v>-151.0387774</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.3466752257619558</v>
+      </c>
+      <c r="T56">
+        <v>2.182639065277784</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.05581826600010689</v>
+      </c>
+      <c r="W56">
+        <v>0.2254705980791745</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.2232730640004276</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2832247268132539</v>
+      </c>
+      <c r="C57">
+        <v>104.4169412976823</v>
+      </c>
+      <c r="D57">
+        <v>1269.161941297682</v>
+      </c>
+      <c r="E57">
+        <v>1156.605</v>
+      </c>
+      <c r="F57">
+        <v>1171.005</v>
+      </c>
+      <c r="G57">
+        <v>6.26</v>
+      </c>
+      <c r="H57">
+        <v>2114.7</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>70.2</v>
+      </c>
+      <c r="K57">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L57">
+        <v>61.3</v>
+      </c>
+      <c r="M57">
+        <v>279.635994</v>
+      </c>
+      <c r="N57">
+        <v>-218.335994</v>
+      </c>
+      <c r="O57">
+        <v>-54.58399850000001</v>
+      </c>
+      <c r="P57">
+        <v>-163.7519955</v>
+      </c>
+      <c r="Q57">
+        <v>-154.8519955</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.353516897445555</v>
+      </c>
+      <c r="T57">
+        <v>2.231142155617291</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.05480338843646858</v>
+      </c>
+      <c r="W57">
+        <v>0.2257129508413713</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.2192135537458744</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2852247268132538</v>
+      </c>
+      <c r="C58">
+        <v>72.82533585349415</v>
+      </c>
+      <c r="D58">
+        <v>1258.861335853494</v>
+      </c>
+      <c r="E58">
+        <v>1177.896</v>
+      </c>
+      <c r="F58">
+        <v>1192.296</v>
+      </c>
+      <c r="G58">
+        <v>6.26</v>
+      </c>
+      <c r="H58">
+        <v>2114.7</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>70.2</v>
+      </c>
+      <c r="K58">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L58">
+        <v>61.3</v>
+      </c>
+      <c r="M58">
+        <v>284.7202848</v>
+      </c>
+      <c r="N58">
+        <v>-223.4202848</v>
+      </c>
+      <c r="O58">
+        <v>-55.8550712</v>
+      </c>
+      <c r="P58">
+        <v>-167.5652136</v>
+      </c>
+      <c r="Q58">
+        <v>-158.6652136</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.360669554205681</v>
+      </c>
+      <c r="T58">
+        <v>2.281849931881319</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.05382475650010308</v>
+      </c>
+      <c r="W58">
+        <v>0.2259466481477754</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.2152990260004124</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2872247268132539</v>
+      </c>
+      <c r="C59">
+        <v>41.3995851625948</v>
+      </c>
+      <c r="D59">
+        <v>1248.726585162595</v>
+      </c>
+      <c r="E59">
+        <v>1199.187</v>
+      </c>
+      <c r="F59">
+        <v>1213.587</v>
+      </c>
+      <c r="G59">
+        <v>6.26</v>
+      </c>
+      <c r="H59">
+        <v>2114.7</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>70.2</v>
+      </c>
+      <c r="K59">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L59">
+        <v>61.3</v>
+      </c>
+      <c r="M59">
+        <v>289.8045756</v>
+      </c>
+      <c r="N59">
+        <v>-228.5045756</v>
+      </c>
+      <c r="O59">
+        <v>-57.1261439</v>
+      </c>
+      <c r="P59">
+        <v>-171.3784317</v>
+      </c>
+      <c r="Q59">
+        <v>-162.4784317</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.3681548926755807</v>
+      </c>
+      <c r="T59">
+        <v>2.334916209366932</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.05288046252641705</v>
+      </c>
+      <c r="W59">
+        <v>0.2261721455486916</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.2115218501056683</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2892247268132539</v>
+      </c>
+      <c r="C60">
+        <v>10.13571546196204</v>
+      </c>
+      <c r="D60">
+        <v>1238.753715461962</v>
+      </c>
+      <c r="E60">
+        <v>1220.478</v>
+      </c>
+      <c r="F60">
+        <v>1234.878</v>
+      </c>
+      <c r="G60">
+        <v>6.26</v>
+      </c>
+      <c r="H60">
+        <v>2114.7</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>70.2</v>
+      </c>
+      <c r="K60">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L60">
+        <v>61.3</v>
+      </c>
+      <c r="M60">
+        <v>294.8888664</v>
+      </c>
+      <c r="N60">
+        <v>-233.5888664</v>
+      </c>
+      <c r="O60">
+        <v>-58.39721659999999</v>
+      </c>
+      <c r="P60">
+        <v>-175.1916498</v>
+      </c>
+      <c r="Q60">
+        <v>-166.2916498</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.3759966758345231</v>
+      </c>
+      <c r="T60">
+        <v>2.390509452447097</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.05196873041389263</v>
+      </c>
+      <c r="W60">
+        <v>0.2263898671771624</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.2078749216555705</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2912247268132539</v>
+      </c>
+      <c r="C61">
+        <v>-20.97012107248247</v>
+      </c>
+      <c r="D61">
+        <v>1228.938878927517</v>
+      </c>
+      <c r="E61">
+        <v>1241.769</v>
+      </c>
+      <c r="F61">
+        <v>1256.169</v>
+      </c>
+      <c r="G61">
+        <v>6.26</v>
+      </c>
+      <c r="H61">
+        <v>2114.7</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>70.2</v>
+      </c>
+      <c r="K61">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L61">
+        <v>61.3</v>
+      </c>
+      <c r="M61">
+        <v>299.9731572</v>
+      </c>
+      <c r="N61">
+        <v>-238.6731572</v>
+      </c>
+      <c r="O61">
+        <v>-59.6682893</v>
+      </c>
+      <c r="P61">
+        <v>-179.0048679</v>
+      </c>
+      <c r="Q61">
+        <v>-170.1048679</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.3842209850012187</v>
+      </c>
+      <c r="T61">
+        <v>2.448814561043367</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.05108790447467411</v>
+      </c>
+      <c r="W61">
+        <v>0.2266002084114478</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.2043516178986965</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2932247268132538</v>
+      </c>
+      <c r="C62">
+        <v>-51.92165127581848</v>
+      </c>
+      <c r="D62">
+        <v>1219.278348724181</v>
+      </c>
+      <c r="E62">
+        <v>1263.06</v>
+      </c>
+      <c r="F62">
+        <v>1277.46</v>
+      </c>
+      <c r="G62">
+        <v>6.26</v>
+      </c>
+      <c r="H62">
+        <v>2114.7</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>70.2</v>
+      </c>
+      <c r="K62">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L62">
+        <v>61.3</v>
+      </c>
+      <c r="M62">
+        <v>305.057448</v>
+      </c>
+      <c r="N62">
+        <v>-243.757448</v>
+      </c>
+      <c r="O62">
+        <v>-60.93936199999999</v>
+      </c>
+      <c r="P62">
+        <v>-182.818086</v>
+      </c>
+      <c r="Q62">
+        <v>-173.918086</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.3928565096262491</v>
+      </c>
+      <c r="T62">
+        <v>2.510034925069451</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.05023643940009621</v>
+      </c>
+      <c r="W62">
+        <v>0.226803538271257</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.2009457576003849</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.295224726813254</v>
+      </c>
+      <c r="C63">
+        <v>-82.72248571243426</v>
+      </c>
+      <c r="D63">
+        <v>1209.768514287566</v>
+      </c>
+      <c r="E63">
+        <v>1284.351</v>
+      </c>
+      <c r="F63">
+        <v>1298.751</v>
+      </c>
+      <c r="G63">
+        <v>6.26</v>
+      </c>
+      <c r="H63">
+        <v>2114.7</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>70.2</v>
+      </c>
+      <c r="K63">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L63">
+        <v>61.3</v>
+      </c>
+      <c r="M63">
+        <v>310.1417388</v>
+      </c>
+      <c r="N63">
+        <v>-248.8417388</v>
+      </c>
+      <c r="O63">
+        <v>-62.21043469999999</v>
+      </c>
+      <c r="P63">
+        <v>-186.6313041</v>
+      </c>
+      <c r="Q63">
+        <v>-177.7313041</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.4019348816679479</v>
+      </c>
+      <c r="T63">
+        <v>2.574394794943027</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.04941289121320938</v>
+      </c>
+      <c r="W63">
+        <v>0.2270002015782856</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.1976515648528376</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2972247268132539</v>
+      </c>
+      <c r="C64">
+        <v>-113.3761231752321</v>
+      </c>
+      <c r="D64">
+        <v>1200.405876824768</v>
+      </c>
+      <c r="E64">
+        <v>1305.642</v>
+      </c>
+      <c r="F64">
+        <v>1320.042</v>
+      </c>
+      <c r="G64">
+        <v>6.26</v>
+      </c>
+      <c r="H64">
+        <v>2114.7</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>70.2</v>
+      </c>
+      <c r="K64">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L64">
+        <v>61.3</v>
+      </c>
+      <c r="M64">
+        <v>315.2260296</v>
+      </c>
+      <c r="N64">
+        <v>-253.9260296</v>
+      </c>
+      <c r="O64">
+        <v>-63.4815074</v>
+      </c>
+      <c r="P64">
+        <v>-190.4445222</v>
+      </c>
+      <c r="Q64">
+        <v>-181.5445222</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.4114910627644728</v>
+      </c>
+      <c r="T64">
+        <v>2.642142026388897</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.0486159090968673</v>
+      </c>
+      <c r="W64">
+        <v>0.2271905209076681</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.1944636363874692</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2992247268132539</v>
+      </c>
+      <c r="C65">
+        <v>-143.8859549775252</v>
+      </c>
+      <c r="D65">
+        <v>1191.187045022475</v>
+      </c>
+      <c r="E65">
+        <v>1326.933</v>
+      </c>
+      <c r="F65">
+        <v>1341.333</v>
+      </c>
+      <c r="G65">
+        <v>6.26</v>
+      </c>
+      <c r="H65">
+        <v>2114.7</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>70.2</v>
+      </c>
+      <c r="K65">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L65">
+        <v>61.3</v>
+      </c>
+      <c r="M65">
+        <v>320.3103204</v>
+      </c>
+      <c r="N65">
+        <v>-259.0103204</v>
+      </c>
+      <c r="O65">
+        <v>-64.75258009999999</v>
+      </c>
+      <c r="P65">
+        <v>-194.2577403</v>
+      </c>
+      <c r="Q65">
+        <v>-185.3577403</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.4215637941905397</v>
+      </c>
+      <c r="T65">
+        <v>2.713551270345353</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.04784422800009163</v>
+      </c>
+      <c r="W65">
+        <v>0.2273747983535781</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.1913769120003666</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.3012247268132539</v>
+      </c>
+      <c r="C66">
+        <v>-174.2552690486696</v>
+      </c>
+      <c r="D66">
+        <v>1182.10873095133</v>
+      </c>
+      <c r="E66">
+        <v>1348.224</v>
+      </c>
+      <c r="F66">
+        <v>1362.624</v>
+      </c>
+      <c r="G66">
+        <v>6.26</v>
+      </c>
+      <c r="H66">
+        <v>2114.7</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>70.2</v>
+      </c>
+      <c r="K66">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L66">
+        <v>61.3</v>
+      </c>
+      <c r="M66">
+        <v>325.3946112</v>
+      </c>
+      <c r="N66">
+        <v>-264.0946112</v>
+      </c>
+      <c r="O66">
+        <v>-66.02365280000001</v>
+      </c>
+      <c r="P66">
+        <v>-198.0709584</v>
+      </c>
+      <c r="Q66">
+        <v>-189.1709584</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.4321961218069436</v>
+      </c>
+      <c r="T66">
+        <v>2.788927694521613</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.04709666193759018</v>
+      </c>
+      <c r="W66">
+        <v>0.2275533171293035</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.1883866477503607</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.303224726813254</v>
+      </c>
+      <c r="C67">
+        <v>-204.4872538438337</v>
+      </c>
+      <c r="D67">
+        <v>1173.167746156166</v>
+      </c>
+      <c r="E67">
+        <v>1369.515</v>
+      </c>
+      <c r="F67">
+        <v>1383.915</v>
+      </c>
+      <c r="G67">
+        <v>6.26</v>
+      </c>
+      <c r="H67">
+        <v>2114.7</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>70.2</v>
+      </c>
+      <c r="K67">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L67">
+        <v>61.3</v>
+      </c>
+      <c r="M67">
+        <v>330.478902</v>
+      </c>
+      <c r="N67">
+        <v>-269.178902</v>
+      </c>
+      <c r="O67">
+        <v>-67.2947255</v>
+      </c>
+      <c r="P67">
+        <v>-201.8841765</v>
+      </c>
+      <c r="Q67">
+        <v>-192.9841765</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.4434360110014277</v>
+      </c>
+      <c r="T67">
+        <v>2.868611342936517</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.04637209790778112</v>
+      </c>
+      <c r="W67">
+        <v>0.2277263430196219</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.1854883916311245</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.3052247268132539</v>
+      </c>
+      <c r="C68">
+        <v>-234.5850020776675</v>
+      </c>
+      <c r="D68">
+        <v>1164.360997922332</v>
+      </c>
+      <c r="E68">
+        <v>1390.806</v>
+      </c>
+      <c r="F68">
+        <v>1405.206</v>
+      </c>
+      <c r="G68">
+        <v>6.26</v>
+      </c>
+      <c r="H68">
+        <v>2114.7</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>70.2</v>
+      </c>
+      <c r="K68">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L68">
+        <v>61.3</v>
+      </c>
+      <c r="M68">
+        <v>335.5631928</v>
+      </c>
+      <c r="N68">
+        <v>-274.2631928</v>
+      </c>
+      <c r="O68">
+        <v>-68.56579819999999</v>
+      </c>
+      <c r="P68">
+        <v>-205.6973946</v>
+      </c>
+      <c r="Q68">
+        <v>-196.7973946</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.4553370701485285</v>
+      </c>
+      <c r="T68">
+        <v>2.952982264787591</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.04566949036372383</v>
+      </c>
+      <c r="W68">
+        <v>0.2278941257011428</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.1826779614548953</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.3072247268132539</v>
+      </c>
+      <c r="C69">
+        <v>-264.5515142910592</v>
+      </c>
+      <c r="D69">
+        <v>1155.685485708941</v>
+      </c>
+      <c r="E69">
+        <v>1412.097</v>
+      </c>
+      <c r="F69">
+        <v>1426.497</v>
+      </c>
+      <c r="G69">
+        <v>6.26</v>
+      </c>
+      <c r="H69">
+        <v>2114.7</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>70.2</v>
+      </c>
+      <c r="K69">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L69">
+        <v>61.3</v>
+      </c>
+      <c r="M69">
+        <v>340.6474836</v>
+      </c>
+      <c r="N69">
+        <v>-279.3474836</v>
+      </c>
+      <c r="O69">
+        <v>-69.83687090000001</v>
+      </c>
+      <c r="P69">
+        <v>-209.5106127</v>
+      </c>
+      <c r="Q69">
+        <v>-200.6106127</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.4679594056075749</v>
+      </c>
+      <c r="T69">
+        <v>3.04246657584176</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.04498785617919063</v>
+      </c>
+      <c r="W69">
+        <v>0.2280568999444093</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.1799514247167625</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.3092247268132539</v>
+      </c>
+      <c r="C70">
+        <v>-294.3897022596138</v>
+      </c>
+      <c r="D70">
+        <v>1147.138297740386</v>
+      </c>
+      <c r="E70">
+        <v>1433.388</v>
+      </c>
+      <c r="F70">
+        <v>1447.788</v>
+      </c>
+      <c r="G70">
+        <v>6.26</v>
+      </c>
+      <c r="H70">
+        <v>2114.7</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>70.2</v>
+      </c>
+      <c r="K70">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L70">
+        <v>61.3</v>
+      </c>
+      <c r="M70">
+        <v>345.7317744</v>
+      </c>
+      <c r="N70">
+        <v>-284.4317744</v>
+      </c>
+      <c r="O70">
+        <v>-71.1079436</v>
+      </c>
+      <c r="P70">
+        <v>-213.3238308</v>
+      </c>
+      <c r="Q70">
+        <v>-204.4238308</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.4813706370328116</v>
+      </c>
+      <c r="T70">
+        <v>3.137543656336815</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.04432627005890841</v>
+      </c>
+      <c r="W70">
+        <v>0.2282148867099327</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.1773050802356337</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.311224726813254</v>
+      </c>
+      <c r="C71">
+        <v>-324.1023922519967</v>
+      </c>
+      <c r="D71">
+        <v>1138.716607748003</v>
+      </c>
+      <c r="E71">
+        <v>1454.679</v>
+      </c>
+      <c r="F71">
+        <v>1469.079</v>
+      </c>
+      <c r="G71">
+        <v>6.26</v>
+      </c>
+      <c r="H71">
+        <v>2114.7</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>70.2</v>
+      </c>
+      <c r="K71">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L71">
+        <v>61.3</v>
+      </c>
+      <c r="M71">
+        <v>350.8160652</v>
+      </c>
+      <c r="N71">
+        <v>-289.5160652</v>
+      </c>
+      <c r="O71">
+        <v>-72.3790163</v>
+      </c>
+      <c r="P71">
+        <v>-217.1370489</v>
+      </c>
+      <c r="Q71">
+        <v>-208.2370489</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.4956471091951604</v>
+      </c>
+      <c r="T71">
+        <v>3.2387547420251</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.04368386034790974</v>
+      </c>
+      <c r="W71">
+        <v>0.2283682941489192</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.174735441391639</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.313224726813254</v>
+      </c>
+      <c r="C72">
+        <v>-353.6923281457939</v>
+      </c>
+      <c r="D72">
+        <v>1130.417671854206</v>
+      </c>
+      <c r="E72">
+        <v>1475.97</v>
+      </c>
+      <c r="F72">
+        <v>1490.37</v>
+      </c>
+      <c r="G72">
+        <v>6.26</v>
+      </c>
+      <c r="H72">
+        <v>2114.7</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>70.2</v>
+      </c>
+      <c r="K72">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L72">
+        <v>61.3</v>
+      </c>
+      <c r="M72">
+        <v>355.900356</v>
+      </c>
+      <c r="N72">
+        <v>-294.600356</v>
+      </c>
+      <c r="O72">
+        <v>-73.65008900000001</v>
+      </c>
+      <c r="P72">
+        <v>-220.950267</v>
+      </c>
+      <c r="Q72">
+        <v>-212.050267</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.5108753461683324</v>
+      </c>
+      <c r="T72">
+        <v>3.346713233425936</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.04305980520008246</v>
+      </c>
+      <c r="W72">
+        <v>0.2285173185182203</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.1722392208003298</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.3152247268132539</v>
+      </c>
+      <c r="C73">
+        <v>-383.1621744081099</v>
+      </c>
+      <c r="D73">
+        <v>1122.23882559189</v>
+      </c>
+      <c r="E73">
+        <v>1497.261</v>
+      </c>
+      <c r="F73">
+        <v>1511.661</v>
+      </c>
+      <c r="G73">
+        <v>6.26</v>
+      </c>
+      <c r="H73">
+        <v>2114.7</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>70.2</v>
+      </c>
+      <c r="K73">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L73">
+        <v>61.3</v>
+      </c>
+      <c r="M73">
+        <v>360.9846468</v>
+      </c>
+      <c r="N73">
+        <v>-299.6846467999999</v>
+      </c>
+      <c r="O73">
+        <v>-74.92116169999998</v>
+      </c>
+      <c r="P73">
+        <v>-224.7634851</v>
+      </c>
+      <c r="Q73">
+        <v>-215.8634851</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.5271538063810334</v>
+      </c>
+      <c r="T73">
+        <v>3.46211713802683</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.04245332907050384</v>
+      </c>
+      <c r="W73">
+        <v>0.2286621450179637</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.1698133162820155</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.3172247268132539</v>
+      </c>
+      <c r="C74">
+        <v>-412.514518947703</v>
+      </c>
+      <c r="D74">
+        <v>1114.177481052297</v>
+      </c>
+      <c r="E74">
+        <v>1518.552</v>
+      </c>
+      <c r="F74">
+        <v>1532.952</v>
+      </c>
+      <c r="G74">
+        <v>6.26</v>
+      </c>
+      <c r="H74">
+        <v>2114.7</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>70.2</v>
+      </c>
+      <c r="K74">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L74">
+        <v>61.3</v>
+      </c>
+      <c r="M74">
+        <v>366.0689376</v>
+      </c>
+      <c r="N74">
+        <v>-304.7689376</v>
+      </c>
+      <c r="O74">
+        <v>-76.19223439999999</v>
+      </c>
+      <c r="P74">
+        <v>-228.5767032</v>
+      </c>
+      <c r="Q74">
+        <v>-219.6767032</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.5445950137517845</v>
+      </c>
+      <c r="T74">
+        <v>3.585764178670645</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.04186369950008018</v>
+      </c>
+      <c r="W74">
+        <v>0.2288029485593809</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.1674547980003207</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.3192247268132539</v>
+      </c>
+      <c r="C75">
+        <v>-441.7518758450697</v>
+      </c>
+      <c r="D75">
+        <v>1106.23112415493</v>
+      </c>
+      <c r="E75">
+        <v>1539.843</v>
+      </c>
+      <c r="F75">
+        <v>1554.243</v>
+      </c>
+      <c r="G75">
+        <v>6.26</v>
+      </c>
+      <c r="H75">
+        <v>2114.7</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>70.2</v>
+      </c>
+      <c r="K75">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L75">
+        <v>61.3</v>
+      </c>
+      <c r="M75">
+        <v>371.1532284</v>
+      </c>
+      <c r="N75">
+        <v>-309.8532284</v>
+      </c>
+      <c r="O75">
+        <v>-77.46330709999999</v>
+      </c>
+      <c r="P75">
+        <v>-232.3899213</v>
+      </c>
+      <c r="Q75">
+        <v>-223.4899213</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.5633281624092581</v>
+      </c>
+      <c r="T75">
+        <v>3.718570259362151</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.04129022416446264</v>
+      </c>
+      <c r="W75">
+        <v>0.2289398944695263</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.1651608966578506</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.3212247268132539</v>
+      </c>
+      <c r="C76">
+        <v>-470.87668796653</v>
+      </c>
+      <c r="D76">
+        <v>1098.39731203347</v>
+      </c>
+      <c r="E76">
+        <v>1561.134</v>
+      </c>
+      <c r="F76">
+        <v>1575.534</v>
+      </c>
+      <c r="G76">
+        <v>6.26</v>
+      </c>
+      <c r="H76">
+        <v>2114.7</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>70.2</v>
+      </c>
+      <c r="K76">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L76">
+        <v>61.3</v>
+      </c>
+      <c r="M76">
+        <v>376.2375192</v>
+      </c>
+      <c r="N76">
+        <v>-314.9375192</v>
+      </c>
+      <c r="O76">
+        <v>-78.7343798</v>
+      </c>
+      <c r="P76">
+        <v>-236.2031394</v>
+      </c>
+      <c r="Q76">
+        <v>-227.3031394</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.5835023225019218</v>
+      </c>
+      <c r="T76">
+        <v>3.861592192414541</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.04073224816224016</v>
+      </c>
+      <c r="W76">
+        <v>0.229073139138857</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.1629289926489607</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.3232247268132539</v>
+      </c>
+      <c r="C77">
+        <v>-499.8913294680274</v>
+      </c>
+      <c r="D77">
+        <v>1090.673670531972</v>
+      </c>
+      <c r="E77">
+        <v>1582.425</v>
+      </c>
+      <c r="F77">
+        <v>1596.825</v>
+      </c>
+      <c r="G77">
+        <v>6.26</v>
+      </c>
+      <c r="H77">
+        <v>2114.7</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>70.2</v>
+      </c>
+      <c r="K77">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L77">
+        <v>61.3</v>
+      </c>
+      <c r="M77">
+        <v>381.32181</v>
+      </c>
+      <c r="N77">
+        <v>-320.02181</v>
+      </c>
+      <c r="O77">
+        <v>-80.00545249999999</v>
+      </c>
+      <c r="P77">
+        <v>-240.0163575</v>
+      </c>
+      <c r="Q77">
+        <v>-231.1163575</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.6052904154019987</v>
+      </c>
+      <c r="T77">
+        <v>4.016055880111123</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.04018915152007697</v>
+      </c>
+      <c r="W77">
+        <v>0.2292028306170056</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.160756606080308</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.3252247268132539</v>
+      </c>
+      <c r="C78">
+        <v>-528.798108194025</v>
+      </c>
+      <c r="D78">
+        <v>1083.057891805975</v>
+      </c>
+      <c r="E78">
+        <v>1603.716</v>
+      </c>
+      <c r="F78">
+        <v>1618.116</v>
+      </c>
+      <c r="G78">
+        <v>6.26</v>
+      </c>
+      <c r="H78">
+        <v>2114.7</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>70.2</v>
+      </c>
+      <c r="K78">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L78">
+        <v>61.3</v>
+      </c>
+      <c r="M78">
+        <v>386.4061008</v>
+      </c>
+      <c r="N78">
+        <v>-325.1061008</v>
+      </c>
+      <c r="O78">
+        <v>-81.27652519999999</v>
+      </c>
+      <c r="P78">
+        <v>-243.8295756</v>
+      </c>
+      <c r="Q78">
+        <v>-234.9295756</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.6288941827104153</v>
+      </c>
+      <c r="T78">
+        <v>4.18339154178242</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.03966034689481279</v>
+      </c>
+      <c r="W78">
+        <v>0.2293291091615187</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.1586413875792512</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.3272247268132539</v>
+      </c>
+      <c r="C79">
+        <v>-557.5992679765961</v>
+      </c>
+      <c r="D79">
+        <v>1075.547732023404</v>
+      </c>
+      <c r="E79">
+        <v>1625.007</v>
+      </c>
+      <c r="F79">
+        <v>1639.407</v>
+      </c>
+      <c r="G79">
+        <v>6.26</v>
+      </c>
+      <c r="H79">
+        <v>2114.7</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>70.2</v>
+      </c>
+      <c r="K79">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L79">
+        <v>61.3</v>
+      </c>
+      <c r="M79">
+        <v>391.4903916</v>
+      </c>
+      <c r="N79">
+        <v>-330.1903916</v>
+      </c>
+      <c r="O79">
+        <v>-82.5475979</v>
+      </c>
+      <c r="P79">
+        <v>-247.6427937</v>
+      </c>
+      <c r="Q79">
+        <v>-238.7427937</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.6545504515239118</v>
+      </c>
+      <c r="T79">
+        <v>4.365278130555569</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.03914527745462042</v>
+      </c>
+      <c r="W79">
+        <v>0.2294521077438367</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.1565811098184817</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.3292247268132539</v>
+      </c>
+      <c r="C80">
+        <v>-586.2969908395223</v>
+      </c>
+      <c r="D80">
+        <v>1068.141009160478</v>
+      </c>
+      <c r="E80">
+        <v>1646.298</v>
+      </c>
+      <c r="F80">
+        <v>1660.698</v>
+      </c>
+      <c r="G80">
+        <v>6.26</v>
+      </c>
+      <c r="H80">
+        <v>2114.7</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>70.2</v>
+      </c>
+      <c r="K80">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L80">
+        <v>61.3</v>
+      </c>
+      <c r="M80">
+        <v>396.5746824</v>
+      </c>
+      <c r="N80">
+        <v>-335.2746824</v>
+      </c>
+      <c r="O80">
+        <v>-83.8186706</v>
+      </c>
+      <c r="P80">
+        <v>-251.4560118</v>
+      </c>
+      <c r="Q80">
+        <v>-242.5560118</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.6825391084113621</v>
+      </c>
+      <c r="T80">
+        <v>4.563699863762639</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.03864341492315092</v>
+      </c>
+      <c r="W80">
+        <v>0.2295719525163516</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.1545736596926037</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.3312247268132539</v>
+      </c>
+      <c r="C81">
+        <v>-614.8933991119397</v>
+      </c>
+      <c r="D81">
+        <v>1060.83560088806</v>
+      </c>
+      <c r="E81">
+        <v>1667.589</v>
+      </c>
+      <c r="F81">
+        <v>1681.989</v>
+      </c>
+      <c r="G81">
+        <v>6.26</v>
+      </c>
+      <c r="H81">
+        <v>2114.7</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>70.2</v>
+      </c>
+      <c r="K81">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L81">
+        <v>61.3</v>
+      </c>
+      <c r="M81">
+        <v>401.6589732</v>
+      </c>
+      <c r="N81">
+        <v>-340.3589732</v>
+      </c>
+      <c r="O81">
+        <v>-85.08974330000001</v>
+      </c>
+      <c r="P81">
+        <v>-255.2692299</v>
+      </c>
+      <c r="Q81">
+        <v>-246.3692299</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.7131933516690463</v>
+      </c>
+      <c r="T81">
+        <v>4.781018904894195</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.03815425777222496</v>
+      </c>
+      <c r="W81">
+        <v>0.2296887632439927</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.1526170310888999</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.3332247268132539</v>
+      </c>
+      <c r="C82">
+        <v>-643.3905574558407</v>
+      </c>
+      <c r="D82">
+        <v>1053.629442544159</v>
+      </c>
+      <c r="E82">
+        <v>1688.88</v>
+      </c>
+      <c r="F82">
+        <v>1703.28</v>
+      </c>
+      <c r="G82">
+        <v>6.26</v>
+      </c>
+      <c r="H82">
+        <v>2114.7</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>70.2</v>
+      </c>
+      <c r="K82">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L82">
+        <v>61.3</v>
+      </c>
+      <c r="M82">
+        <v>406.743264</v>
+      </c>
+      <c r="N82">
+        <v>-345.443264</v>
+      </c>
+      <c r="O82">
+        <v>-86.360816</v>
+      </c>
+      <c r="P82">
+        <v>-259.082448</v>
+      </c>
+      <c r="Q82">
+        <v>-250.182448</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.7469130192524984</v>
+      </c>
+      <c r="T82">
+        <v>5.020069850138904</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.03767732955007215</v>
+      </c>
+      <c r="W82">
+        <v>0.2298026537034428</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.1507093182002887</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.3352247268132539</v>
+      </c>
+      <c r="C83">
+        <v>-671.7904748114968</v>
+      </c>
+      <c r="D83">
+        <v>1046.520525188503</v>
+      </c>
+      <c r="E83">
+        <v>1710.171</v>
+      </c>
+      <c r="F83">
+        <v>1724.571</v>
+      </c>
+      <c r="G83">
+        <v>6.26</v>
+      </c>
+      <c r="H83">
+        <v>2114.7</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>70.2</v>
+      </c>
+      <c r="K83">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L83">
+        <v>61.3</v>
+      </c>
+      <c r="M83">
+        <v>411.8275548</v>
+      </c>
+      <c r="N83">
+        <v>-350.5275548</v>
+      </c>
+      <c r="O83">
+        <v>-87.6318887</v>
+      </c>
+      <c r="P83">
+        <v>-262.8956661</v>
+      </c>
+      <c r="Q83">
+        <v>-253.9956661</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.7841821255289458</v>
+      </c>
+      <c r="T83">
+        <v>5.284284052777794</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.03721217733340459</v>
+      </c>
+      <c r="W83">
+        <v>0.229913732052783</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.1488487093336184</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.3372247268132539</v>
+      </c>
+      <c r="C84">
+        <v>-700.0951062646529</v>
+      </c>
+      <c r="D84">
+        <v>1039.506893735347</v>
+      </c>
+      <c r="E84">
+        <v>1731.462</v>
+      </c>
+      <c r="F84">
+        <v>1745.862</v>
+      </c>
+      <c r="G84">
+        <v>6.26</v>
+      </c>
+      <c r="H84">
+        <v>2114.7</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>70.2</v>
+      </c>
+      <c r="K84">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L84">
+        <v>61.3</v>
+      </c>
+      <c r="M84">
+        <v>416.9118456</v>
+      </c>
+      <c r="N84">
+        <v>-355.6118456</v>
+      </c>
+      <c r="O84">
+        <v>-88.90296140000001</v>
+      </c>
+      <c r="P84">
+        <v>-266.7088842000001</v>
+      </c>
+      <c r="Q84">
+        <v>-257.8088842000001</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.8255922436138874</v>
+      </c>
+      <c r="T84">
+        <v>5.577855389043228</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.03675837029275331</v>
+      </c>
+      <c r="W84">
+        <v>0.2300221011740905</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.1470334811710133</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.3392247268132539</v>
+      </c>
+      <c r="C85">
+        <v>-728.3063548391422</v>
+      </c>
+      <c r="D85">
+        <v>1032.586645160858</v>
+      </c>
+      <c r="E85">
+        <v>1752.753</v>
+      </c>
+      <c r="F85">
+        <v>1767.153</v>
+      </c>
+      <c r="G85">
+        <v>6.26</v>
+      </c>
+      <c r="H85">
+        <v>2114.7</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>70.2</v>
+      </c>
+      <c r="K85">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L85">
+        <v>61.3</v>
+      </c>
+      <c r="M85">
+        <v>421.9961364</v>
+      </c>
+      <c r="N85">
+        <v>-360.6961364</v>
+      </c>
+      <c r="O85">
+        <v>-90.1740341</v>
+      </c>
+      <c r="P85">
+        <v>-270.5221023</v>
+      </c>
+      <c r="Q85">
+        <v>-261.6221023000001</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.8718741402970573</v>
+      </c>
+      <c r="T85">
+        <v>5.905964529575183</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.03631549836151533</v>
+      </c>
+      <c r="W85">
+        <v>0.2301278589912701</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.1452619934460614</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.3412247268132539</v>
+      </c>
+      <c r="C86">
+        <v>-756.4260732183668</v>
+      </c>
+      <c r="D86">
+        <v>1025.757926781633</v>
+      </c>
+      <c r="E86">
+        <v>1774.044</v>
+      </c>
+      <c r="F86">
+        <v>1788.444</v>
+      </c>
+      <c r="G86">
+        <v>6.26</v>
+      </c>
+      <c r="H86">
+        <v>2114.7</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>70.2</v>
+      </c>
+      <c r="K86">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L86">
+        <v>61.3</v>
+      </c>
+      <c r="M86">
+        <v>427.0804272</v>
+      </c>
+      <c r="N86">
+        <v>-365.7804272</v>
+      </c>
+      <c r="O86">
+        <v>-91.4451068</v>
+      </c>
+      <c r="P86">
+        <v>-274.3353204</v>
+      </c>
+      <c r="Q86">
+        <v>-265.4353204</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.923941274065623</v>
+      </c>
+      <c r="T86">
+        <v>6.275087312673629</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.03588317100006871</v>
+      </c>
+      <c r="W86">
+        <v>0.2302310987651836</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.1435326840002749</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.3432247268132539</v>
+      </c>
+      <c r="C87">
+        <v>-784.4560653989254</v>
+      </c>
+      <c r="D87">
+        <v>1019.018934601074</v>
+      </c>
+      <c r="E87">
+        <v>1795.335</v>
+      </c>
+      <c r="F87">
+        <v>1809.735</v>
+      </c>
+      <c r="G87">
+        <v>6.26</v>
+      </c>
+      <c r="H87">
+        <v>2114.7</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>70.2</v>
+      </c>
+      <c r="K87">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L87">
+        <v>61.3</v>
+      </c>
+      <c r="M87">
+        <v>432.164718</v>
+      </c>
+      <c r="N87">
+        <v>-370.864718</v>
+      </c>
+      <c r="O87">
+        <v>-92.7161795</v>
+      </c>
+      <c r="P87">
+        <v>-278.1485385</v>
+      </c>
+      <c r="Q87">
+        <v>-269.2485385</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.9829506923366644</v>
+      </c>
+      <c r="T87">
+        <v>6.693426466851871</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.03546101604712673</v>
+      </c>
+      <c r="W87">
+        <v>0.2303319093679461</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.1418440641885069</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.3452247268132539</v>
+      </c>
+      <c r="C88">
+        <v>-812.3980882794785</v>
+      </c>
+      <c r="D88">
+        <v>1012.367911720521</v>
+      </c>
+      <c r="E88">
+        <v>1816.626</v>
+      </c>
+      <c r="F88">
+        <v>1831.026</v>
+      </c>
+      <c r="G88">
+        <v>6.26</v>
+      </c>
+      <c r="H88">
+        <v>2114.7</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>70.2</v>
+      </c>
+      <c r="K88">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L88">
+        <v>61.3</v>
+      </c>
+      <c r="M88">
+        <v>437.2490088</v>
+      </c>
+      <c r="N88">
+        <v>-375.9490087999999</v>
+      </c>
+      <c r="O88">
+        <v>-93.98725219999999</v>
+      </c>
+      <c r="P88">
+        <v>-281.9617565999999</v>
+      </c>
+      <c r="Q88">
+        <v>-273.0617566</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>1.050390027503569</v>
+      </c>
+      <c r="T88">
+        <v>7.17152835734129</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.03504867865122992</v>
+      </c>
+      <c r="W88">
+        <v>0.2304303755380863</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.1401947146049197</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.3472247268132539</v>
+      </c>
+      <c r="C89">
+        <v>-840.253853187796</v>
+      </c>
+      <c r="D89">
+        <v>1005.803146812204</v>
+      </c>
+      <c r="E89">
+        <v>1837.917</v>
+      </c>
+      <c r="F89">
+        <v>1852.317</v>
+      </c>
+      <c r="G89">
+        <v>6.26</v>
+      </c>
+      <c r="H89">
+        <v>2114.7</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>70.2</v>
+      </c>
+      <c r="K89">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L89">
+        <v>61.3</v>
+      </c>
+      <c r="M89">
+        <v>442.3332996</v>
+      </c>
+      <c r="N89">
+        <v>-381.0332996</v>
+      </c>
+      <c r="O89">
+        <v>-95.25832490000001</v>
+      </c>
+      <c r="P89">
+        <v>-285.7749747</v>
+      </c>
+      <c r="Q89">
+        <v>-276.8749747000001</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>1.128204645003843</v>
+      </c>
+      <c r="T89">
+        <v>7.723184384829081</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.03464582027592841</v>
+      </c>
+      <c r="W89">
+        <v>0.2305265781181083</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.1385832811037137</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.3492247268132539</v>
+      </c>
+      <c r="C90">
+        <v>-868.0250273487757</v>
+      </c>
+      <c r="D90">
+        <v>999.3229726512243</v>
+      </c>
+      <c r="E90">
+        <v>1859.208</v>
+      </c>
+      <c r="F90">
+        <v>1873.608</v>
+      </c>
+      <c r="G90">
+        <v>6.26</v>
+      </c>
+      <c r="H90">
+        <v>2114.7</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>70.2</v>
+      </c>
+      <c r="K90">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L90">
+        <v>61.3</v>
+      </c>
+      <c r="M90">
+        <v>447.4175904</v>
+      </c>
+      <c r="N90">
+        <v>-386.1175904</v>
+      </c>
+      <c r="O90">
+        <v>-96.5293976</v>
+      </c>
+      <c r="P90">
+        <v>-289.5881928</v>
+      </c>
+      <c r="Q90">
+        <v>-280.6881928</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>1.21898836542083</v>
+      </c>
+      <c r="T90">
+        <v>8.366783083564838</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.03425211777279287</v>
+      </c>
+      <c r="W90">
+        <v>0.2306205942758571</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.1370084710911715</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.3512247268132539</v>
+      </c>
+      <c r="C91">
+        <v>-895.7132352960746</v>
+      </c>
+      <c r="D91">
+        <v>992.9257647039253</v>
+      </c>
+      <c r="E91">
+        <v>1880.499</v>
+      </c>
+      <c r="F91">
+        <v>1894.899</v>
+      </c>
+      <c r="G91">
+        <v>6.26</v>
+      </c>
+      <c r="H91">
+        <v>2114.7</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>70.2</v>
+      </c>
+      <c r="K91">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L91">
+        <v>61.3</v>
+      </c>
+      <c r="M91">
+        <v>452.5018812</v>
+      </c>
+      <c r="N91">
+        <v>-391.2018812</v>
+      </c>
+      <c r="O91">
+        <v>-97.8004703</v>
+      </c>
+      <c r="P91">
+        <v>-293.4014109</v>
+      </c>
+      <c r="Q91">
+        <v>-284.5014109</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>1.326278216822724</v>
+      </c>
+      <c r="T91">
+        <v>9.12739972752528</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.03386726251691879</v>
+      </c>
+      <c r="W91">
+        <v>0.2307124977109598</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.1354690500676752</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.3532247268132539</v>
+      </c>
+      <c r="C92">
+        <v>-923.3200602298666</v>
+      </c>
+      <c r="D92">
+        <v>986.6099397701335</v>
+      </c>
+      <c r="E92">
+        <v>1901.79</v>
+      </c>
+      <c r="F92">
+        <v>1916.19</v>
+      </c>
+      <c r="G92">
+        <v>6.26</v>
+      </c>
+      <c r="H92">
+        <v>2114.7</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>70.2</v>
+      </c>
+      <c r="K92">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L92">
+        <v>61.3</v>
+      </c>
+      <c r="M92">
+        <v>457.586172</v>
+      </c>
+      <c r="N92">
+        <v>-396.286172</v>
+      </c>
+      <c r="O92">
+        <v>-99.07154300000001</v>
+      </c>
+      <c r="P92">
+        <v>-297.214629</v>
+      </c>
+      <c r="Q92">
+        <v>-288.314629</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>1.455026038504997</v>
+      </c>
+      <c r="T92">
+        <v>10.04013970027781</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.03349095960006413</v>
+      </c>
+      <c r="W92">
+        <v>0.2308023588475047</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.1339638384002566</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.3552247268132539</v>
+      </c>
+      <c r="C93">
+        <v>-950.8470453231074</v>
+      </c>
+      <c r="D93">
+        <v>980.3739546768926</v>
+      </c>
+      <c r="E93">
+        <v>1923.081</v>
+      </c>
+      <c r="F93">
+        <v>1937.481</v>
+      </c>
+      <c r="G93">
+        <v>6.26</v>
+      </c>
+      <c r="H93">
+        <v>2114.7</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>70.2</v>
+      </c>
+      <c r="K93">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L93">
+        <v>61.3</v>
+      </c>
+      <c r="M93">
+        <v>462.6704628</v>
+      </c>
+      <c r="N93">
+        <v>-401.3704628</v>
+      </c>
+      <c r="O93">
+        <v>-100.3426157</v>
+      </c>
+      <c r="P93">
+        <v>-301.0278471</v>
+      </c>
+      <c r="Q93">
+        <v>-292.1278470999999</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>1.612384487227775</v>
+      </c>
+      <c r="T93">
+        <v>11.15571077808646</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.03312292707698651</v>
+      </c>
+      <c r="W93">
+        <v>0.2308902450140156</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.1324917083079461</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.3572247268132539</v>
+      </c>
+      <c r="C94">
+        <v>-978.2956949785744</v>
+      </c>
+      <c r="D94">
+        <v>974.2163050214256</v>
+      </c>
+      <c r="E94">
+        <v>1944.372</v>
+      </c>
+      <c r="F94">
+        <v>1958.772</v>
+      </c>
+      <c r="G94">
+        <v>6.26</v>
+      </c>
+      <c r="H94">
+        <v>2114.7</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>70.2</v>
+      </c>
+      <c r="K94">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L94">
+        <v>61.3</v>
+      </c>
+      <c r="M94">
+        <v>467.7547536</v>
+      </c>
+      <c r="N94">
+        <v>-406.4547536</v>
+      </c>
+      <c r="O94">
+        <v>-101.6136884</v>
+      </c>
+      <c r="P94">
+        <v>-304.8410652</v>
+      </c>
+      <c r="Q94">
+        <v>-295.9410652</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.809082548131247</v>
+      </c>
+      <c r="T94">
+        <v>12.55017462534727</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.0327628952609323</v>
+      </c>
+      <c r="W94">
+        <v>0.2309762206116894</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.1310515810437293</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.3592247268132539</v>
+      </c>
+      <c r="C95">
+        <v>-1005.667476038828</v>
+      </c>
+      <c r="D95">
+        <v>968.1355239611726</v>
+      </c>
+      <c r="E95">
+        <v>1965.663</v>
+      </c>
+      <c r="F95">
+        <v>1980.063</v>
+      </c>
+      <c r="G95">
+        <v>6.26</v>
+      </c>
+      <c r="H95">
+        <v>2114.7</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>70.2</v>
+      </c>
+      <c r="K95">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L95">
+        <v>61.3</v>
+      </c>
+      <c r="M95">
+        <v>472.8390444</v>
+      </c>
+      <c r="N95">
+        <v>-411.5390444</v>
+      </c>
+      <c r="O95">
+        <v>-102.8847611</v>
+      </c>
+      <c r="P95">
+        <v>-308.6542833</v>
+      </c>
+      <c r="Q95">
+        <v>-299.7542833</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>2.06198005500714</v>
+      </c>
+      <c r="T95">
+        <v>14.34305671468259</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.03241060606457819</v>
+      </c>
+      <c r="W95">
+        <v>0.2310603472717787</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.1296424242583128</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.3612247268132539</v>
+      </c>
+      <c r="C96">
+        <v>-1032.96381895114</v>
+      </c>
+      <c r="D96">
+        <v>962.1301810488598</v>
+      </c>
+      <c r="E96">
+        <v>1986.954</v>
+      </c>
+      <c r="F96">
+        <v>2001.354</v>
+      </c>
+      <c r="G96">
+        <v>6.26</v>
+      </c>
+      <c r="H96">
+        <v>2114.7</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>70.2</v>
+      </c>
+      <c r="K96">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L96">
+        <v>61.3</v>
+      </c>
+      <c r="M96">
+        <v>477.9233352000001</v>
+      </c>
+      <c r="N96">
+        <v>-416.6233352</v>
+      </c>
+      <c r="O96">
+        <v>-104.1558338</v>
+      </c>
+      <c r="P96">
+        <v>-312.4675014000001</v>
+      </c>
+      <c r="Q96">
+        <v>-303.5675014000001</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>2.399176730841663</v>
+      </c>
+      <c r="T96">
+        <v>16.73356616712969</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.03206581238304013</v>
+      </c>
+      <c r="W96">
+        <v>0.23114268400293</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.1282632495321605</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.3632247268132539</v>
+      </c>
+      <c r="C97">
+        <v>-1060.186118889339</v>
+      </c>
+      <c r="D97">
+        <v>956.1988811106606</v>
+      </c>
+      <c r="E97">
+        <v>2008.245</v>
+      </c>
+      <c r="F97">
+        <v>2022.645</v>
+      </c>
+      <c r="G97">
+        <v>6.26</v>
+      </c>
+      <c r="H97">
+        <v>2114.7</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>70.2</v>
+      </c>
+      <c r="K97">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L97">
+        <v>61.3</v>
+      </c>
+      <c r="M97">
+        <v>483.007626</v>
+      </c>
+      <c r="N97">
+        <v>-421.707626</v>
+      </c>
+      <c r="O97">
+        <v>-105.4269065</v>
+      </c>
+      <c r="P97">
+        <v>-316.2807195</v>
+      </c>
+      <c r="Q97">
+        <v>-307.3807195000001</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>2.871252077009997</v>
+      </c>
+      <c r="T97">
+        <v>20.08027940055564</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.03172827751585024</v>
+      </c>
+      <c r="W97">
+        <v>0.231223287329215</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.126913110063401</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.3652247268132539</v>
+      </c>
+      <c r="C98">
+        <v>-1087.335736834405</v>
+      </c>
+      <c r="D98">
+        <v>950.3402631655947</v>
+      </c>
+      <c r="E98">
+        <v>2029.536</v>
+      </c>
+      <c r="F98">
+        <v>2043.936</v>
+      </c>
+      <c r="G98">
+        <v>6.26</v>
+      </c>
+      <c r="H98">
+        <v>2114.7</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>70.2</v>
+      </c>
+      <c r="K98">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L98">
+        <v>61.3</v>
+      </c>
+      <c r="M98">
+        <v>488.0919168</v>
+      </c>
+      <c r="N98">
+        <v>-426.7919168</v>
+      </c>
+      <c r="O98">
+        <v>-106.6979792</v>
+      </c>
+      <c r="P98">
+        <v>-320.0939376</v>
+      </c>
+      <c r="Q98">
+        <v>-311.1939376</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>3.579365096262489</v>
+      </c>
+      <c r="T98">
+        <v>25.1003492506945</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.03139777462506013</v>
+      </c>
+      <c r="W98">
+        <v>0.2313022114195357</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.1255910985002405</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.3672247268132539</v>
+      </c>
+      <c r="C99">
+        <v>-1114.414000615588</v>
+      </c>
+      <c r="D99">
+        <v>944.5529993844119</v>
+      </c>
+      <c r="E99">
+        <v>2050.827</v>
+      </c>
+      <c r="F99">
+        <v>2065.227</v>
+      </c>
+      <c r="G99">
+        <v>6.26</v>
+      </c>
+      <c r="H99">
+        <v>2114.7</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>70.2</v>
+      </c>
+      <c r="K99">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L99">
+        <v>61.3</v>
+      </c>
+      <c r="M99">
+        <v>493.1762076</v>
+      </c>
+      <c r="N99">
+        <v>-431.8762076</v>
+      </c>
+      <c r="O99">
+        <v>-107.9690519</v>
+      </c>
+      <c r="P99">
+        <v>-323.9071557</v>
+      </c>
+      <c r="Q99">
+        <v>-315.0071557</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>4.759553461683319</v>
+      </c>
+      <c r="T99">
+        <v>33.46713233425933</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.03107408622686363</v>
+      </c>
+      <c r="W99">
+        <v>0.231379508209025</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.1242963449074546</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.3692247268132539</v>
+      </c>
+      <c r="C100">
+        <v>-1141.422205913715</v>
+      </c>
+      <c r="D100">
+        <v>938.8357940862853</v>
+      </c>
+      <c r="E100">
+        <v>2072.118</v>
+      </c>
+      <c r="F100">
+        <v>2086.518</v>
+      </c>
+      <c r="G100">
+        <v>6.26</v>
+      </c>
+      <c r="H100">
+        <v>2114.7</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>70.2</v>
+      </c>
+      <c r="K100">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L100">
+        <v>61.3</v>
+      </c>
+      <c r="M100">
+        <v>498.2604984</v>
+      </c>
+      <c r="N100">
+        <v>-436.9604984</v>
+      </c>
+      <c r="O100">
+        <v>-109.2401246</v>
+      </c>
+      <c r="P100">
+        <v>-327.7203738</v>
+      </c>
+      <c r="Q100">
+        <v>-318.8203738</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>7.119930192524978</v>
+      </c>
+      <c r="T100">
+        <v>50.20069850138899</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.03075700371434461</v>
+      </c>
+      <c r="W100">
+        <v>0.2314552275130145</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.1230280148573785</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3712247268132539</v>
+      </c>
+      <c r="C101">
+        <v>-1168.361617228278</v>
+      </c>
+      <c r="D101">
+        <v>933.1873827717219</v>
+      </c>
+      <c r="E101">
+        <v>2093.409</v>
+      </c>
+      <c r="F101">
+        <v>2107.809</v>
+      </c>
+      <c r="G101">
+        <v>6.26</v>
+      </c>
+      <c r="H101">
+        <v>2114.7</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>70.2</v>
+      </c>
+      <c r="K101">
+        <v>8.900000000000006</v>
+      </c>
+      <c r="L101">
+        <v>61.3</v>
+      </c>
+      <c r="M101">
+        <v>503.3447892</v>
+      </c>
+      <c r="N101">
+        <v>-442.0447892</v>
+      </c>
+      <c r="O101">
+        <v>-110.5111973</v>
+      </c>
+      <c r="P101">
+        <v>-331.5335919</v>
+      </c>
+      <c r="Q101">
+        <v>-322.6335918999999</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>14.20106038504996</v>
+      </c>
+      <c r="T101">
+        <v>100.401397002778</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.03044632690914922</v>
+      </c>
+      <c r="W101">
+        <v>0.2315294171340952</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.1217853076365969</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/turkey/turkey_precious_metals.xlsx
+++ b/research/traditional_assets/database/data/turkey/turkey_precious_metals.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1528460741268359</v>
+        <v>0.1524977089415188</v>
       </c>
       <c r="C2">
-        <v>2044.233945417889</v>
+        <v>2030.355668843399</v>
       </c>
       <c r="D2">
-        <v>2010.433945417889</v>
+        <v>2016.997958843399</v>
       </c>
       <c r="E2">
-        <v>-0.229</v>
+        <v>20.21329</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>20.44229</v>
       </c>
       <c r="G2">
         <v>33.8</v>
@@ -1451,28 +1451,28 @@
         <v>35.1</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.028247187</v>
       </c>
       <c r="N2">
-        <v>35.1</v>
+        <v>34.071752813</v>
       </c>
       <c r="O2">
-        <v>8.775</v>
+        <v>8.517938203250001</v>
       </c>
       <c r="P2">
-        <v>26.325</v>
+        <v>25.55381460975</v>
       </c>
       <c r="Q2">
-        <v>58.12500000000001</v>
+        <v>57.35381460975</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1528460741268359</v>
+        <v>0.1536570292338574</v>
       </c>
       <c r="T2">
-        <v>1.035217350236429</v>
+        <v>1.043059905920038</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>34.13576078180898</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1524977089415188</v>
+        <v>0.1521493437562017</v>
       </c>
       <c r="C3">
-        <v>2030.355668843399</v>
+        <v>2016.520395331695</v>
       </c>
       <c r="D3">
-        <v>2016.997958843399</v>
+        <v>2023.604975331695</v>
       </c>
       <c r="E3">
-        <v>20.21329</v>
+        <v>40.65558</v>
       </c>
       <c r="F3">
-        <v>20.44229</v>
+        <v>40.88458</v>
       </c>
       <c r="G3">
         <v>33.8</v>
@@ -1533,28 +1533,28 @@
         <v>35.1</v>
       </c>
       <c r="M3">
-        <v>1.028247187</v>
+        <v>2.056494374</v>
       </c>
       <c r="N3">
-        <v>34.071752813</v>
+        <v>33.043505626</v>
       </c>
       <c r="O3">
-        <v>8.517938203250001</v>
+        <v>8.2608764065</v>
       </c>
       <c r="P3">
-        <v>25.55381460975</v>
+        <v>24.7826292195</v>
       </c>
       <c r="Q3">
-        <v>57.35381460975</v>
+        <v>56.58262921950001</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1536570292338574</v>
+        <v>0.1544845344451038</v>
       </c>
       <c r="T3">
-        <v>1.043059905920038</v>
+        <v>1.051062513760456</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>34.13576078180898</v>
+        <v>17.06788039090449</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1521493437562017</v>
+        <v>0.1518347285708846</v>
       </c>
       <c r="C4">
-        <v>2016.520395331695</v>
+        <v>2002.082334916693</v>
       </c>
       <c r="D4">
-        <v>2023.604975331695</v>
+        <v>2029.609204916693</v>
       </c>
       <c r="E4">
-        <v>40.65558</v>
+        <v>61.09787</v>
       </c>
       <c r="F4">
-        <v>40.88458</v>
+        <v>61.32687</v>
       </c>
       <c r="G4">
         <v>33.8</v>
@@ -1615,45 +1615,45 @@
         <v>35.1</v>
       </c>
       <c r="M4">
-        <v>2.056494374</v>
+        <v>3.176731866</v>
       </c>
       <c r="N4">
-        <v>33.043505626</v>
+        <v>31.923268134</v>
       </c>
       <c r="O4">
-        <v>8.2608764065</v>
+        <v>7.9808170335</v>
       </c>
       <c r="P4">
-        <v>24.7826292195</v>
+        <v>23.9424511005</v>
       </c>
       <c r="Q4">
-        <v>56.58262921950001</v>
+        <v>55.74245110050001</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1544845344451038</v>
+        <v>0.1553291016194686</v>
       </c>
       <c r="T4">
-        <v>1.051062513760456</v>
+        <v>1.059230123824387</v>
       </c>
       <c r="U4">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V4">
         <v>0.25</v>
       </c>
       <c r="W4">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y4">
-        <v>17.06788039090449</v>
+        <v>11.04909116682749</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1518347285708846</v>
+        <v>0.1515486133855675</v>
       </c>
       <c r="C5">
-        <v>2002.082334916693</v>
+        <v>1987.131388918234</v>
       </c>
       <c r="D5">
-        <v>2029.609204916693</v>
+        <v>2035.100548918233</v>
       </c>
       <c r="E5">
-        <v>61.09787</v>
+        <v>81.54016</v>
       </c>
       <c r="F5">
-        <v>61.32687</v>
+        <v>81.76916</v>
       </c>
       <c r="G5">
         <v>33.8</v>
@@ -1697,45 +1697,45 @@
         <v>35.1</v>
       </c>
       <c r="M5">
-        <v>3.176731866</v>
+        <v>4.37465006</v>
       </c>
       <c r="N5">
-        <v>31.923268134</v>
+        <v>30.72534994</v>
       </c>
       <c r="O5">
-        <v>7.9808170335</v>
+        <v>7.681337485</v>
       </c>
       <c r="P5">
-        <v>23.9424511005</v>
+        <v>23.044012455</v>
       </c>
       <c r="Q5">
-        <v>55.74245110050001</v>
+        <v>54.844012455</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1553291016194686</v>
+        <v>0.1561912639432995</v>
       </c>
       <c r="T5">
-        <v>1.059230123824387</v>
+        <v>1.067567892431317</v>
       </c>
       <c r="U5">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V5">
         <v>0.25</v>
       </c>
       <c r="W5">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y5">
-        <v>11.04909116682749</v>
+        <v>8.023498912733606</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1515486133855675</v>
+        <v>0.1512542482002504</v>
       </c>
       <c r="C6">
-        <v>1987.131388918234</v>
+        <v>1972.369882390168</v>
       </c>
       <c r="D6">
-        <v>2035.100548918233</v>
+        <v>2040.781332390168</v>
       </c>
       <c r="E6">
-        <v>81.54016</v>
+        <v>101.98245</v>
       </c>
       <c r="F6">
-        <v>81.76916</v>
+        <v>102.21145</v>
       </c>
       <c r="G6">
         <v>33.8</v>
@@ -1779,45 +1779,45 @@
         <v>35.1</v>
       </c>
       <c r="M6">
-        <v>4.37465006</v>
+        <v>5.550081735000001</v>
       </c>
       <c r="N6">
-        <v>30.72534994</v>
+        <v>29.549918265</v>
       </c>
       <c r="O6">
-        <v>7.681337485</v>
+        <v>7.387479566250001</v>
       </c>
       <c r="P6">
-        <v>23.044012455</v>
+        <v>22.16243869875</v>
       </c>
       <c r="Q6">
-        <v>54.844012455</v>
+        <v>53.96243869875001</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1561912639432995</v>
+        <v>0.1570715770528952</v>
       </c>
       <c r="T6">
-        <v>1.067567892431317</v>
+        <v>1.07608119300892</v>
       </c>
       <c r="U6">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V6">
         <v>0.25</v>
       </c>
       <c r="W6">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y6">
-        <v>8.023498912733606</v>
+        <v>6.324231187200705</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1512542482002504</v>
+        <v>0.1509808830149333</v>
       </c>
       <c r="C7">
-        <v>1972.369882390168</v>
+        <v>1957.231584438239</v>
       </c>
       <c r="D7">
-        <v>2040.781332390168</v>
+        <v>2046.085324438239</v>
       </c>
       <c r="E7">
-        <v>101.98245</v>
+        <v>122.42474</v>
       </c>
       <c r="F7">
-        <v>102.21145</v>
+        <v>122.65374</v>
       </c>
       <c r="G7">
         <v>33.8</v>
@@ -1861,45 +1861,45 @@
         <v>35.1</v>
       </c>
       <c r="M7">
-        <v>5.550081735000001</v>
+        <v>6.782751822000001</v>
       </c>
       <c r="N7">
-        <v>29.549918265</v>
+        <v>28.317248178</v>
       </c>
       <c r="O7">
-        <v>7.387479566250001</v>
+        <v>7.0793120445</v>
       </c>
       <c r="P7">
-        <v>22.16243869875</v>
+        <v>21.2379361335</v>
       </c>
       <c r="Q7">
-        <v>53.96243869875001</v>
+        <v>53.0379361335</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1570715770528952</v>
+        <v>0.1579706202286525</v>
       </c>
       <c r="T7">
-        <v>1.07608119300892</v>
+        <v>1.084775627641364</v>
       </c>
       <c r="U7">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V7">
         <v>0.25</v>
       </c>
       <c r="W7">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y7">
-        <v>6.324231187200705</v>
+        <v>5.17489079965338</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1509808830149333</v>
+        <v>0.1508012678296163</v>
       </c>
       <c r="C8">
-        <v>1957.231584438239</v>
+        <v>1940.289328317068</v>
       </c>
       <c r="D8">
-        <v>2046.085324438239</v>
+        <v>2049.585358317068</v>
       </c>
       <c r="E8">
-        <v>122.42474</v>
+        <v>142.86703</v>
       </c>
       <c r="F8">
-        <v>122.65374</v>
+        <v>143.09603</v>
       </c>
       <c r="G8">
         <v>33.8</v>
@@ -1943,45 +1943,45 @@
         <v>35.1</v>
       </c>
       <c r="M8">
-        <v>6.782751822</v>
+        <v>8.270950533999999</v>
       </c>
       <c r="N8">
-        <v>28.317248178</v>
+        <v>26.829049466</v>
       </c>
       <c r="O8">
-        <v>7.0793120445</v>
+        <v>6.7072623665</v>
       </c>
       <c r="P8">
-        <v>21.2379361335</v>
+        <v>20.1217870995</v>
       </c>
       <c r="Q8">
-        <v>53.0379361335</v>
+        <v>51.92178709950001</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1579706202286525</v>
+        <v>0.158888997666254</v>
       </c>
       <c r="T8">
-        <v>1.084775627641364</v>
+        <v>1.093657039362679</v>
       </c>
       <c r="U8">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V8">
         <v>0.25</v>
       </c>
       <c r="W8">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y8">
-        <v>5.17489079965338</v>
+        <v>4.243768579646543</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1508012678296162</v>
+        <v>0.1507191526442991</v>
       </c>
       <c r="C9">
-        <v>1940.289328317069</v>
+        <v>1921.451150409853</v>
       </c>
       <c r="D9">
-        <v>2049.585358317068</v>
+        <v>2051.189470409853</v>
       </c>
       <c r="E9">
-        <v>142.86703</v>
+        <v>163.30932</v>
       </c>
       <c r="F9">
-        <v>143.09603</v>
+        <v>163.53832</v>
       </c>
       <c r="G9">
         <v>33.8</v>
@@ -2025,45 +2025,45 @@
         <v>35.1</v>
       </c>
       <c r="M9">
-        <v>8.270950534000001</v>
+        <v>10.024899016</v>
       </c>
       <c r="N9">
-        <v>26.829049466</v>
+        <v>25.075100984</v>
       </c>
       <c r="O9">
-        <v>6.7072623665</v>
+        <v>6.268775246000001</v>
       </c>
       <c r="P9">
-        <v>20.1217870995</v>
+        <v>18.806325738</v>
       </c>
       <c r="Q9">
-        <v>51.92178709950001</v>
+        <v>50.60632573800001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.158888997666254</v>
+        <v>0.1598273398307599</v>
       </c>
       <c r="T9">
-        <v>1.093657039362679</v>
+        <v>1.102731525251848</v>
       </c>
       <c r="U9">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V9">
         <v>0.25</v>
       </c>
       <c r="W9">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y9">
-        <v>4.243768579646543</v>
+        <v>3.501282151967764</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1507191526442991</v>
+        <v>0.1511687874589821</v>
       </c>
       <c r="C10">
-        <v>1921.451150409853</v>
+        <v>1892.255924937701</v>
       </c>
       <c r="D10">
-        <v>2051.189470409853</v>
+        <v>2042.436534937701</v>
       </c>
       <c r="E10">
-        <v>163.30932</v>
+        <v>183.75161</v>
       </c>
       <c r="F10">
-        <v>163.53832</v>
+        <v>183.98061</v>
       </c>
       <c r="G10">
         <v>33.8</v>
@@ -2107,45 +2107,45 @@
         <v>35.1</v>
       </c>
       <c r="M10">
-        <v>10.024899016</v>
+        <v>13.228205859</v>
       </c>
       <c r="N10">
-        <v>25.075100984</v>
+        <v>21.871794141</v>
       </c>
       <c r="O10">
-        <v>6.268775246000001</v>
+        <v>5.467948535250001</v>
       </c>
       <c r="P10">
-        <v>18.806325738</v>
+        <v>16.40384560575</v>
       </c>
       <c r="Q10">
-        <v>50.60632573800001</v>
+        <v>48.20384560575</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1598273398307599</v>
+        <v>0.1607863048999803</v>
       </c>
       <c r="T10">
-        <v>1.102731525251848</v>
+        <v>1.112005450391329</v>
       </c>
       <c r="U10">
-        <v>0.0613</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V10">
         <v>0.25</v>
       </c>
       <c r="W10">
-        <v>0.045975</v>
+        <v>0.053925</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y10">
-        <v>3.501282151967764</v>
+        <v>2.653421059071228</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1511687874589821</v>
+        <v>0.151274922273665</v>
       </c>
       <c r="C11">
-        <v>1892.255924937701</v>
+        <v>1869.758420120147</v>
       </c>
       <c r="D11">
-        <v>2042.436534937701</v>
+        <v>2040.381320120147</v>
       </c>
       <c r="E11">
-        <v>183.75161</v>
+        <v>204.1939</v>
       </c>
       <c r="F11">
-        <v>183.98061</v>
+        <v>204.4229</v>
       </c>
       <c r="G11">
         <v>33.8</v>
@@ -2189,45 +2189,45 @@
         <v>35.1</v>
       </c>
       <c r="M11">
-        <v>13.228205859</v>
+        <v>15.49525582</v>
       </c>
       <c r="N11">
-        <v>21.871794141</v>
+        <v>19.60474418</v>
       </c>
       <c r="O11">
-        <v>5.467948535250001</v>
+        <v>4.901186045</v>
       </c>
       <c r="P11">
-        <v>16.40384560575</v>
+        <v>14.703558135</v>
       </c>
       <c r="Q11">
-        <v>48.20384560575</v>
+        <v>46.50355813500001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1607863048999803</v>
+        <v>0.1617665803040722</v>
       </c>
       <c r="T11">
-        <v>1.112005450391329</v>
+        <v>1.121485462756131</v>
       </c>
       <c r="U11">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V11">
         <v>0.25</v>
       </c>
       <c r="W11">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y11">
-        <v>2.653421059071228</v>
+        <v>2.265209455573867</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.151274922273665</v>
+        <v>0.1511178070883479</v>
       </c>
       <c r="C12">
-        <v>1869.758420120147</v>
+        <v>1852.36001128413</v>
       </c>
       <c r="D12">
-        <v>2040.381320120147</v>
+        <v>2043.425201284129</v>
       </c>
       <c r="E12">
-        <v>204.1939</v>
+        <v>224.63619</v>
       </c>
       <c r="F12">
-        <v>204.4229</v>
+        <v>224.86519</v>
       </c>
       <c r="G12">
         <v>33.8</v>
@@ -2271,28 +2271,28 @@
         <v>35.1</v>
       </c>
       <c r="M12">
-        <v>15.49525582</v>
+        <v>17.044781402</v>
       </c>
       <c r="N12">
-        <v>19.60474418</v>
+        <v>18.055218598</v>
       </c>
       <c r="O12">
-        <v>4.901186044999999</v>
+        <v>4.5138046495</v>
       </c>
       <c r="P12">
-        <v>14.703558135</v>
+        <v>13.5414139485</v>
       </c>
       <c r="Q12">
-        <v>46.50355813500001</v>
+        <v>45.3414139485</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1617665803040722</v>
+        <v>0.1627688843689302</v>
       </c>
       <c r="T12">
-        <v>1.121485462756131</v>
+        <v>1.13117850910666</v>
       </c>
       <c r="U12">
         <v>0.07580000000000001</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>2.265209455573867</v>
+        <v>2.05928132324897</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1511178070883479</v>
+        <v>0.1522386919030308</v>
       </c>
       <c r="C13">
-        <v>1852.36001128413</v>
+        <v>1810.398814605472</v>
       </c>
       <c r="D13">
-        <v>2043.425201284129</v>
+        <v>2021.906294605472</v>
       </c>
       <c r="E13">
-        <v>224.63619</v>
+        <v>245.07848</v>
       </c>
       <c r="F13">
-        <v>224.86519</v>
+        <v>245.30748</v>
       </c>
       <c r="G13">
         <v>33.8</v>
@@ -2353,45 +2353,45 @@
         <v>35.1</v>
       </c>
       <c r="M13">
-        <v>17.044781402</v>
+        <v>22.0776732</v>
       </c>
       <c r="N13">
-        <v>18.055218598</v>
+        <v>13.0223268</v>
       </c>
       <c r="O13">
-        <v>4.5138046495</v>
+        <v>3.2555817</v>
       </c>
       <c r="P13">
-        <v>13.5414139485</v>
+        <v>9.766745100000001</v>
       </c>
       <c r="Q13">
-        <v>45.3414139485</v>
+        <v>41.56674510000001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1627688843689302</v>
+        <v>0.1637939680716259</v>
       </c>
       <c r="T13">
-        <v>1.13117850910666</v>
+        <v>1.141091851965155</v>
       </c>
       <c r="U13">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V13">
         <v>0.25</v>
       </c>
       <c r="W13">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y13">
-        <v>2.05928132324897</v>
+        <v>1.589841451226844</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1522386919030308</v>
+        <v>0.1585533729730843</v>
       </c>
       <c r="C14">
-        <v>1810.398814605472</v>
+        <v>1676.720946216034</v>
       </c>
       <c r="D14">
-        <v>2021.906294605472</v>
+        <v>1908.670716216033</v>
       </c>
       <c r="E14">
-        <v>245.07848</v>
+        <v>265.52077</v>
       </c>
       <c r="F14">
-        <v>245.30748</v>
+        <v>265.74977</v>
       </c>
       <c r="G14">
         <v>33.8</v>
@@ -2435,45 +2435,45 @@
         <v>35.1</v>
       </c>
       <c r="M14">
-        <v>22.0776732</v>
+        <v>39.012066236</v>
       </c>
       <c r="N14">
-        <v>13.0223268</v>
+        <v>-3.912066236000001</v>
       </c>
       <c r="O14">
-        <v>3.2555817</v>
+        <v>-0.9780165590000003</v>
       </c>
       <c r="P14">
-        <v>9.766745100000001</v>
+        <v>-2.934049677000001</v>
       </c>
       <c r="Q14">
-        <v>41.56674510000001</v>
+        <v>28.865950323</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1637939680716259</v>
+        <v>0.1652436148176975</v>
       </c>
       <c r="T14">
-        <v>1.141091851965155</v>
+        <v>1.155111043939154</v>
       </c>
       <c r="U14">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V14">
-        <v>0.25</v>
+        <v>0.2249304086309201</v>
       </c>
       <c r="W14">
-        <v>0.0675</v>
+        <v>0.1137802160129809</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y14">
-        <v>1.589841451226844</v>
+        <v>0.8997216345236803</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1585533729730843</v>
+        <v>0.1595633729730843</v>
       </c>
       <c r="C15">
-        <v>1676.720946216034</v>
+        <v>1639.333330378742</v>
       </c>
       <c r="D15">
-        <v>1908.670716216033</v>
+        <v>1891.725390378743</v>
       </c>
       <c r="E15">
-        <v>265.52077</v>
+        <v>285.96306</v>
       </c>
       <c r="F15">
-        <v>265.74977</v>
+        <v>286.19206</v>
       </c>
       <c r="G15">
         <v>33.8</v>
@@ -2517,37 +2517,37 @@
         <v>35.1</v>
       </c>
       <c r="M15">
-        <v>39.012066236</v>
+        <v>42.012994408</v>
       </c>
       <c r="N15">
-        <v>-3.912066236000001</v>
+        <v>-6.912994408000003</v>
       </c>
       <c r="O15">
-        <v>-0.9780165590000003</v>
+        <v>-1.728248602000001</v>
       </c>
       <c r="P15">
-        <v>-2.934049677000001</v>
+        <v>-5.184745806000002</v>
       </c>
       <c r="Q15">
-        <v>28.865950323</v>
+        <v>26.615254194</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1652436148176975</v>
+        <v>0.1666324940597637</v>
       </c>
       <c r="T15">
-        <v>1.155111043939154</v>
+        <v>1.168542567705889</v>
       </c>
       <c r="U15">
         <v>0.1468</v>
       </c>
       <c r="V15">
-        <v>0.2249304086309201</v>
+        <v>0.2088639508715686</v>
       </c>
       <c r="W15">
-        <v>0.1137802160129809</v>
+        <v>0.1161387720120537</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>0.8997216345236803</v>
+        <v>0.8354558034862745</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1595633729730843</v>
+        <v>0.1695151407953638</v>
       </c>
       <c r="C16">
-        <v>1639.333330378742</v>
+        <v>1466.718786057017</v>
       </c>
       <c r="D16">
-        <v>1891.725390378743</v>
+        <v>1739.553136057017</v>
       </c>
       <c r="E16">
-        <v>285.96306</v>
+        <v>306.4053500000001</v>
       </c>
       <c r="F16">
-        <v>286.19206</v>
+        <v>306.63435</v>
       </c>
       <c r="G16">
         <v>33.8</v>
@@ -2599,45 +2599,45 @@
         <v>35.1</v>
       </c>
       <c r="M16">
-        <v>42.012994408</v>
+        <v>61.57217748000001</v>
       </c>
       <c r="N16">
-        <v>-6.912994408000003</v>
+        <v>-26.47217748000001</v>
       </c>
       <c r="O16">
-        <v>-1.728248602000001</v>
+        <v>-6.618044370000002</v>
       </c>
       <c r="P16">
-        <v>-5.184745806000002</v>
+        <v>-19.85413311000001</v>
       </c>
       <c r="Q16">
-        <v>26.615254194</v>
+        <v>11.94586689</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1666324940597637</v>
+        <v>0.1690443678984426</v>
       </c>
       <c r="T16">
-        <v>1.168542567705889</v>
+        <v>1.191867231078628</v>
       </c>
       <c r="U16">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V16">
-        <v>0.2088639508715686</v>
+        <v>0.1425156679386613</v>
       </c>
       <c r="W16">
-        <v>0.1161387720120537</v>
+        <v>0.1721828538779168</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y16">
-        <v>0.8354558034862745</v>
+        <v>0.5700626717546452</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1695151407953638</v>
+        <v>0.1710651407953638</v>
       </c>
       <c r="C17">
-        <v>1466.718786057017</v>
+        <v>1424.75169399502</v>
       </c>
       <c r="D17">
-        <v>1739.553136057017</v>
+        <v>1718.02833399502</v>
       </c>
       <c r="E17">
-        <v>306.40535</v>
+        <v>326.84764</v>
       </c>
       <c r="F17">
-        <v>306.63435</v>
+        <v>327.07664</v>
       </c>
       <c r="G17">
         <v>33.8</v>
@@ -2681,37 +2681,37 @@
         <v>35.1</v>
       </c>
       <c r="M17">
-        <v>61.57217748</v>
+        <v>65.676989312</v>
       </c>
       <c r="N17">
-        <v>-26.47217748</v>
+        <v>-30.576989312</v>
       </c>
       <c r="O17">
-        <v>-6.61804437</v>
+        <v>-7.644247328000001</v>
       </c>
       <c r="P17">
-        <v>-19.85413311</v>
+        <v>-22.932741984</v>
       </c>
       <c r="Q17">
-        <v>11.94586689</v>
+        <v>8.867258016000001</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1690443678984426</v>
+        <v>0.1705115627543765</v>
       </c>
       <c r="T17">
-        <v>1.191867231078628</v>
+        <v>1.206056126686707</v>
       </c>
       <c r="U17">
         <v>0.2008</v>
       </c>
       <c r="V17">
-        <v>0.1425156679386613</v>
+        <v>0.133608438692495</v>
       </c>
       <c r="W17">
-        <v>0.1721828538779168</v>
+        <v>0.173971425510547</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>0.5700626717546453</v>
+        <v>0.5344337547699799</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1710651407953638</v>
+        <v>0.1726151407953638</v>
       </c>
       <c r="C18">
-        <v>1424.75169399502</v>
+        <v>1383.310776378548</v>
       </c>
       <c r="D18">
-        <v>1718.02833399502</v>
+        <v>1697.029706378548</v>
       </c>
       <c r="E18">
-        <v>326.84764</v>
+        <v>347.28993</v>
       </c>
       <c r="F18">
-        <v>327.07664</v>
+        <v>347.51893</v>
       </c>
       <c r="G18">
         <v>33.8</v>
@@ -2763,37 +2763,37 @@
         <v>35.1</v>
       </c>
       <c r="M18">
-        <v>65.676989312</v>
+        <v>69.781801144</v>
       </c>
       <c r="N18">
-        <v>-30.576989312</v>
+        <v>-34.681801144</v>
       </c>
       <c r="O18">
-        <v>-7.644247328000001</v>
+        <v>-8.670450285999999</v>
       </c>
       <c r="P18">
-        <v>-22.932741984</v>
+        <v>-26.011350858</v>
       </c>
       <c r="Q18">
-        <v>8.867258016000001</v>
+        <v>5.788649142000004</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1705115627543765</v>
+        <v>0.1720141117032244</v>
       </c>
       <c r="T18">
-        <v>1.206056126686707</v>
+        <v>1.220586923393775</v>
       </c>
       <c r="U18">
         <v>0.2008</v>
       </c>
       <c r="V18">
-        <v>0.133608438692495</v>
+        <v>0.1257491187694071</v>
       </c>
       <c r="W18">
-        <v>0.173971425510547</v>
+        <v>0.1755495769511031</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>0.5344337547699799</v>
+        <v>0.5029964750776281</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1726151407953638</v>
+        <v>0.1808048042790813</v>
       </c>
       <c r="C19">
-        <v>1383.310776378548</v>
+        <v>1259.923244604914</v>
       </c>
       <c r="D19">
-        <v>1697.029706378548</v>
+        <v>1594.084464604914</v>
       </c>
       <c r="E19">
-        <v>347.28993</v>
+        <v>367.73222</v>
       </c>
       <c r="F19">
-        <v>347.51893</v>
+        <v>367.96122</v>
       </c>
       <c r="G19">
         <v>33.8</v>
@@ -2845,45 +2845,45 @@
         <v>35.1</v>
       </c>
       <c r="M19">
-        <v>69.781801144</v>
+        <v>86.76525567600001</v>
       </c>
       <c r="N19">
-        <v>-34.681801144</v>
+        <v>-51.66525567600001</v>
       </c>
       <c r="O19">
-        <v>-8.670450285999999</v>
+        <v>-12.916313919</v>
       </c>
       <c r="P19">
-        <v>-26.011350858</v>
+        <v>-38.748941757</v>
       </c>
       <c r="Q19">
-        <v>5.788649142000004</v>
+        <v>-6.948941757</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1720141117032244</v>
+        <v>0.1739675319480412</v>
       </c>
       <c r="T19">
-        <v>1.220586923393775</v>
+        <v>1.239477990125857</v>
       </c>
       <c r="U19">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V19">
-        <v>0.1257491187694071</v>
+        <v>0.1011349523681198</v>
       </c>
       <c r="W19">
-        <v>0.1755495769511031</v>
+        <v>0.2119523782315973</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y19">
-        <v>0.5029964750776281</v>
+        <v>0.4045398094724794</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1808048042790813</v>
+        <v>0.1827048042790813</v>
       </c>
       <c r="C20">
-        <v>1259.923244604913</v>
+        <v>1217.35784140448</v>
       </c>
       <c r="D20">
-        <v>1594.084464604913</v>
+        <v>1571.96135140448</v>
       </c>
       <c r="E20">
-        <v>367.73222</v>
+        <v>388.1745100000001</v>
       </c>
       <c r="F20">
-        <v>367.96122</v>
+        <v>388.40351</v>
       </c>
       <c r="G20">
         <v>33.8</v>
@@ -2927,37 +2927,37 @@
         <v>35.1</v>
       </c>
       <c r="M20">
-        <v>86.765255676</v>
+        <v>91.58554765800001</v>
       </c>
       <c r="N20">
-        <v>-51.66525567599999</v>
+        <v>-56.48554765800001</v>
       </c>
       <c r="O20">
-        <v>-12.916313919</v>
+        <v>-14.1213869145</v>
       </c>
       <c r="P20">
-        <v>-38.748941757</v>
+        <v>-42.36416074350001</v>
       </c>
       <c r="Q20">
-        <v>-6.948941756999993</v>
+        <v>-10.5641607435</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1739675319480412</v>
+        <v>0.1755498471572762</v>
       </c>
       <c r="T20">
-        <v>1.239477990125857</v>
+        <v>1.254780187534818</v>
       </c>
       <c r="U20">
         <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>0.1011349523681199</v>
+        <v>0.09581206013821879</v>
       </c>
       <c r="W20">
-        <v>0.2119523782315973</v>
+        <v>0.213207516219408</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.4045398094724795</v>
+        <v>0.3832482405528752</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1827048042790813</v>
+        <v>0.1846048042790813</v>
       </c>
       <c r="C21">
-        <v>1217.35784140448</v>
+        <v>1175.398093250341</v>
       </c>
       <c r="D21">
-        <v>1571.96135140448</v>
+        <v>1550.443893250341</v>
       </c>
       <c r="E21">
-        <v>388.1745100000001</v>
+        <v>408.6168000000001</v>
       </c>
       <c r="F21">
-        <v>388.40351</v>
+        <v>408.8458000000001</v>
       </c>
       <c r="G21">
         <v>33.8</v>
@@ -3009,37 +3009,37 @@
         <v>35.1</v>
       </c>
       <c r="M21">
-        <v>91.58554765800001</v>
+        <v>96.40583964000001</v>
       </c>
       <c r="N21">
-        <v>-56.48554765800001</v>
+        <v>-61.30583964000001</v>
       </c>
       <c r="O21">
-        <v>-14.1213869145</v>
+        <v>-15.32645991</v>
       </c>
       <c r="P21">
-        <v>-42.36416074350001</v>
+        <v>-45.97937973000001</v>
       </c>
       <c r="Q21">
-        <v>-10.5641607435</v>
+        <v>-14.17937973</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1755498471572762</v>
+        <v>0.1771717202467422</v>
       </c>
       <c r="T21">
-        <v>1.254780187534818</v>
+        <v>1.270464939879004</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>0.09581206013821879</v>
+        <v>0.09102145713130785</v>
       </c>
       <c r="W21">
-        <v>0.213207516219408</v>
+        <v>0.2143371404084376</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.3832482405528752</v>
+        <v>0.3640858285252314</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1846048042790813</v>
+        <v>0.1865048042790813</v>
       </c>
       <c r="C22">
-        <v>1175.398093250341</v>
+        <v>1134.01946484833</v>
       </c>
       <c r="D22">
-        <v>1550.443893250341</v>
+        <v>1529.50755484833</v>
       </c>
       <c r="E22">
-        <v>408.6168000000001</v>
+        <v>429.0590900000001</v>
       </c>
       <c r="F22">
-        <v>408.8458000000001</v>
+        <v>429.2880900000001</v>
       </c>
       <c r="G22">
         <v>33.8</v>
@@ -3091,37 +3091,37 @@
         <v>35.1</v>
       </c>
       <c r="M22">
-        <v>96.40583964000001</v>
+        <v>101.226131622</v>
       </c>
       <c r="N22">
-        <v>-61.30583964000001</v>
+        <v>-66.12613162200003</v>
       </c>
       <c r="O22">
-        <v>-15.32645991</v>
+        <v>-16.53153290550001</v>
       </c>
       <c r="P22">
-        <v>-45.97937973000001</v>
+        <v>-49.59459871650002</v>
       </c>
       <c r="Q22">
-        <v>-14.17937973</v>
+        <v>-17.79459871650002</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1771717202467422</v>
+        <v>0.1788346534144225</v>
       </c>
       <c r="T22">
-        <v>1.270464939879004</v>
+        <v>1.286546774561016</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>0.09102145713130785</v>
+        <v>0.086687102029817</v>
       </c>
       <c r="W22">
-        <v>0.2143371404084376</v>
+        <v>0.2153591813413692</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.3640858285252314</v>
+        <v>0.3467484081192679</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1865048042790813</v>
+        <v>0.1884048042790813</v>
       </c>
       <c r="C23">
-        <v>1134.01946484833</v>
+        <v>1093.19872849161</v>
       </c>
       <c r="D23">
-        <v>1529.50755484833</v>
+        <v>1509.12910849161</v>
       </c>
       <c r="E23">
-        <v>429.05909</v>
+        <v>449.50138</v>
       </c>
       <c r="F23">
-        <v>429.28809</v>
+        <v>449.73038</v>
       </c>
       <c r="G23">
         <v>33.8</v>
@@ -3173,37 +3173,37 @@
         <v>35.1</v>
       </c>
       <c r="M23">
-        <v>101.226131622</v>
+        <v>106.046423604</v>
       </c>
       <c r="N23">
-        <v>-66.126131622</v>
+        <v>-70.94642360400002</v>
       </c>
       <c r="O23">
-        <v>-16.5315329055</v>
+        <v>-17.736605901</v>
       </c>
       <c r="P23">
-        <v>-49.5945987165</v>
+        <v>-53.20981770300001</v>
       </c>
       <c r="Q23">
-        <v>-17.7945987165</v>
+        <v>-21.40981770300001</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1788346534144225</v>
+        <v>0.1805402258940945</v>
       </c>
       <c r="T23">
-        <v>1.286546774561016</v>
+        <v>1.303040963978465</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>0.086687102029817</v>
+        <v>0.08274677921027987</v>
       </c>
       <c r="W23">
-        <v>0.2153591813413692</v>
+        <v>0.216288309462216</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.3467484081192681</v>
+        <v>0.3309871168411194</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1884048042790813</v>
+        <v>0.1903048042790813</v>
       </c>
       <c r="C24">
-        <v>1093.19872849161</v>
+        <v>1052.913878097587</v>
       </c>
       <c r="D24">
-        <v>1509.12910849161</v>
+        <v>1489.286548097587</v>
       </c>
       <c r="E24">
-        <v>449.50138</v>
+        <v>469.9436700000001</v>
       </c>
       <c r="F24">
-        <v>449.73038</v>
+        <v>470.17267</v>
       </c>
       <c r="G24">
         <v>33.8</v>
@@ -3255,37 +3255,37 @@
         <v>35.1</v>
       </c>
       <c r="M24">
-        <v>106.046423604</v>
+        <v>110.866715586</v>
       </c>
       <c r="N24">
-        <v>-70.94642360400002</v>
+        <v>-75.766715586</v>
       </c>
       <c r="O24">
-        <v>-17.736605901</v>
+        <v>-18.9416788965</v>
       </c>
       <c r="P24">
-        <v>-53.20981770300001</v>
+        <v>-56.8250366895</v>
       </c>
       <c r="Q24">
-        <v>-21.40981770300001</v>
+        <v>-25.0250366895</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1805402258940945</v>
+        <v>0.1822900989576542</v>
       </c>
       <c r="T24">
-        <v>1.303040963978465</v>
+        <v>1.319963573900263</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>0.08274677921027987</v>
+        <v>0.079149093157659</v>
       </c>
       <c r="W24">
-        <v>0.216288309462216</v>
+        <v>0.217136643833424</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.3309871168411194</v>
+        <v>0.3165963726306361</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1903048042790813</v>
+        <v>0.1922048042790813</v>
       </c>
       <c r="C25">
-        <v>1052.913878097587</v>
+        <v>1013.144049938447</v>
       </c>
       <c r="D25">
-        <v>1489.286548097587</v>
+        <v>1469.959009938447</v>
       </c>
       <c r="E25">
-        <v>469.9436700000001</v>
+        <v>490.3859600000001</v>
       </c>
       <c r="F25">
-        <v>470.17267</v>
+        <v>490.6149600000001</v>
       </c>
       <c r="G25">
         <v>33.8</v>
@@ -3337,37 +3337,37 @@
         <v>35.1</v>
       </c>
       <c r="M25">
-        <v>110.866715586</v>
+        <v>115.687007568</v>
       </c>
       <c r="N25">
-        <v>-75.766715586</v>
+        <v>-80.58700756800002</v>
       </c>
       <c r="O25">
-        <v>-18.9416788965</v>
+        <v>-20.146751892</v>
       </c>
       <c r="P25">
-        <v>-56.8250366895</v>
+        <v>-60.44025567600001</v>
       </c>
       <c r="Q25">
-        <v>-25.0250366895</v>
+        <v>-28.64025567600001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1822900989576542</v>
+        <v>0.1840860213123602</v>
       </c>
       <c r="T25">
-        <v>1.319963573900263</v>
+        <v>1.337331515662109</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>0.079149093157659</v>
+        <v>0.07585121427608987</v>
       </c>
       <c r="W25">
-        <v>0.217136643833424</v>
+        <v>0.217914283673698</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.3165963726306361</v>
+        <v>0.3034048571043595</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1922048042790813</v>
+        <v>0.1941048042790813</v>
       </c>
       <c r="C26">
-        <v>1013.144049938447</v>
+        <v>973.8694494650297</v>
       </c>
       <c r="D26">
-        <v>1469.959009938447</v>
+        <v>1451.12669946503</v>
       </c>
       <c r="E26">
-        <v>490.38596</v>
+        <v>510.82825</v>
       </c>
       <c r="F26">
-        <v>490.61496</v>
+        <v>511.05725</v>
       </c>
       <c r="G26">
         <v>33.8</v>
@@ -3419,37 +3419,37 @@
         <v>35.1</v>
       </c>
       <c r="M26">
-        <v>115.687007568</v>
+        <v>120.50729955</v>
       </c>
       <c r="N26">
-        <v>-80.58700756799999</v>
+        <v>-85.40729955</v>
       </c>
       <c r="O26">
-        <v>-20.146751892</v>
+        <v>-21.3518248875</v>
       </c>
       <c r="P26">
-        <v>-60.44025567599999</v>
+        <v>-64.0554746625</v>
       </c>
       <c r="Q26">
-        <v>-28.64025567599999</v>
+        <v>-32.2554746625</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1840860213123602</v>
+        <v>0.1859298349298583</v>
       </c>
       <c r="T26">
-        <v>1.337331515662109</v>
+        <v>1.355162602537604</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.07585121427608989</v>
+        <v>0.07281716570504629</v>
       </c>
       <c r="W26">
-        <v>0.217914283673698</v>
+        <v>0.2186297123267501</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.3034048571043596</v>
+        <v>0.2912686628201852</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1941048042790813</v>
+        <v>0.1960048042790813</v>
       </c>
       <c r="C27">
-        <v>973.8694494650297</v>
+        <v>935.0712836845134</v>
       </c>
       <c r="D27">
-        <v>1451.12669946503</v>
+        <v>1432.770823684514</v>
       </c>
       <c r="E27">
-        <v>510.82825</v>
+        <v>531.27054</v>
       </c>
       <c r="F27">
-        <v>511.05725</v>
+        <v>531.49954</v>
       </c>
       <c r="G27">
         <v>33.8</v>
@@ -3501,37 +3501,37 @@
         <v>35.1</v>
       </c>
       <c r="M27">
-        <v>120.50729955</v>
+        <v>125.327591532</v>
       </c>
       <c r="N27">
-        <v>-85.40729955</v>
+        <v>-90.22759153200002</v>
       </c>
       <c r="O27">
-        <v>-21.3518248875</v>
+        <v>-22.556897883</v>
       </c>
       <c r="P27">
-        <v>-64.0554746625</v>
+        <v>-67.67069364900001</v>
       </c>
       <c r="Q27">
-        <v>-32.2554746625</v>
+        <v>-35.87069364900001</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1859298349298583</v>
+        <v>0.1878234813478294</v>
       </c>
       <c r="T27">
-        <v>1.355162602537604</v>
+        <v>1.373475610680004</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.07281716570504629</v>
+        <v>0.07001650548562142</v>
       </c>
       <c r="W27">
-        <v>0.2186297123267501</v>
+        <v>0.2192901080064905</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.2912686628201852</v>
+        <v>0.2800660219424856</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1960048042790813</v>
+        <v>0.1979048042790813</v>
       </c>
       <c r="C28">
-        <v>935.0712836845134</v>
+        <v>896.7316986062739</v>
       </c>
       <c r="D28">
-        <v>1432.770823684514</v>
+        <v>1414.873528606274</v>
       </c>
       <c r="E28">
-        <v>531.27054</v>
+        <v>551.7128300000001</v>
       </c>
       <c r="F28">
-        <v>531.49954</v>
+        <v>551.9418300000001</v>
       </c>
       <c r="G28">
         <v>33.8</v>
@@ -3583,37 +3583,37 @@
         <v>35.1</v>
       </c>
       <c r="M28">
-        <v>125.327591532</v>
+        <v>130.147883514</v>
       </c>
       <c r="N28">
-        <v>-90.22759153200002</v>
+        <v>-95.04788351400003</v>
       </c>
       <c r="O28">
-        <v>-22.556897883</v>
+        <v>-23.76197087850001</v>
       </c>
       <c r="P28">
-        <v>-67.67069364900001</v>
+        <v>-71.28591263550003</v>
       </c>
       <c r="Q28">
-        <v>-35.87069364900001</v>
+        <v>-39.48591263550002</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1878234813478294</v>
+        <v>0.1897690084895805</v>
       </c>
       <c r="T28">
-        <v>1.373475610680004</v>
+        <v>1.392290345072881</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.07001650548562142</v>
+        <v>0.06742330157874656</v>
       </c>
       <c r="W28">
-        <v>0.2192901080064905</v>
+        <v>0.2199015854877316</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.2800660219424856</v>
+        <v>0.2696932063149862</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1979048042790813</v>
+        <v>0.1998048042790813</v>
       </c>
       <c r="C29">
-        <v>896.7316986062739</v>
+        <v>858.8337213182307</v>
       </c>
       <c r="D29">
-        <v>1414.873528606274</v>
+        <v>1397.417841318231</v>
       </c>
       <c r="E29">
-        <v>551.7128300000001</v>
+        <v>572.15512</v>
       </c>
       <c r="F29">
-        <v>551.9418300000001</v>
+        <v>572.3841200000001</v>
       </c>
       <c r="G29">
         <v>33.8</v>
@@ -3665,37 +3665,37 @@
         <v>35.1</v>
       </c>
       <c r="M29">
-        <v>130.147883514</v>
+        <v>134.968175496</v>
       </c>
       <c r="N29">
-        <v>-95.04788351400003</v>
+        <v>-99.86817549600002</v>
       </c>
       <c r="O29">
-        <v>-23.76197087850001</v>
+        <v>-24.96704387400001</v>
       </c>
       <c r="P29">
-        <v>-71.28591263550003</v>
+        <v>-74.90113162200001</v>
       </c>
       <c r="Q29">
-        <v>-39.48591263550002</v>
+        <v>-43.101131622</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1897690084895805</v>
+        <v>0.1917685780519358</v>
       </c>
       <c r="T29">
-        <v>1.392290345072881</v>
+        <v>1.411627710976671</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.06742330157874656</v>
+        <v>0.06501532652236275</v>
       </c>
       <c r="W29">
-        <v>0.2199015854877316</v>
+        <v>0.2204693860060269</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.2696932063149862</v>
+        <v>0.260061306089451</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1998048042790813</v>
+        <v>0.2017048042790813</v>
       </c>
       <c r="C30">
-        <v>858.8337213182307</v>
+        <v>821.3612062986617</v>
       </c>
       <c r="D30">
-        <v>1397.417841318231</v>
+        <v>1380.387616298662</v>
       </c>
       <c r="E30">
-        <v>572.15512</v>
+        <v>592.5974100000001</v>
       </c>
       <c r="F30">
-        <v>572.3841200000001</v>
+        <v>592.8264100000001</v>
       </c>
       <c r="G30">
         <v>33.8</v>
@@ -3747,37 +3747,37 @@
         <v>35.1</v>
       </c>
       <c r="M30">
-        <v>134.968175496</v>
+        <v>139.788467478</v>
       </c>
       <c r="N30">
-        <v>-99.86817549600002</v>
+        <v>-104.688467478</v>
       </c>
       <c r="O30">
-        <v>-24.96704387400001</v>
+        <v>-26.17211686950001</v>
       </c>
       <c r="P30">
-        <v>-74.90113162200001</v>
+        <v>-78.51635060850003</v>
       </c>
       <c r="Q30">
-        <v>-43.101131622</v>
+        <v>-46.71635060850003</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1917685780519358</v>
+        <v>0.193824473517456</v>
       </c>
       <c r="T30">
-        <v>1.411627710976671</v>
+        <v>1.431509791412962</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.06501532652236275</v>
+        <v>0.0627734187112468</v>
       </c>
       <c r="W30">
-        <v>0.2204693860060269</v>
+        <v>0.220998027867888</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.260061306089451</v>
+        <v>0.2510936748449871</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.2017048042790813</v>
+        <v>0.2036048042790813</v>
       </c>
       <c r="C31">
-        <v>821.3612062986618</v>
+        <v>784.2987856065121</v>
       </c>
       <c r="D31">
-        <v>1380.387616298662</v>
+        <v>1363.767485606512</v>
       </c>
       <c r="E31">
-        <v>592.59741</v>
+        <v>613.0396999999999</v>
       </c>
       <c r="F31">
-        <v>592.82641</v>
+        <v>613.2687</v>
       </c>
       <c r="G31">
         <v>33.8</v>
@@ -3829,37 +3829,37 @@
         <v>35.1</v>
       </c>
       <c r="M31">
-        <v>139.788467478</v>
+        <v>144.60875946</v>
       </c>
       <c r="N31">
-        <v>-104.688467478</v>
+        <v>-109.50875946</v>
       </c>
       <c r="O31">
-        <v>-26.1721168695</v>
+        <v>-27.377189865</v>
       </c>
       <c r="P31">
-        <v>-78.51635060850001</v>
+        <v>-82.131569595</v>
       </c>
       <c r="Q31">
-        <v>-46.7163506085</v>
+        <v>-50.331569595</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.193824473517456</v>
+        <v>0.1959391088534196</v>
       </c>
       <c r="T31">
-        <v>1.431509791412962</v>
+        <v>1.45195993129029</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.06277341871124681</v>
+        <v>0.06068097142087191</v>
       </c>
       <c r="W31">
-        <v>0.220998027867888</v>
+        <v>0.2214914269389584</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.2510936748449871</v>
+        <v>0.2427238856834876</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.2036048042790813</v>
+        <v>0.2055048042790813</v>
       </c>
       <c r="C32">
-        <v>784.2987856065121</v>
+        <v>747.6318226272049</v>
       </c>
       <c r="D32">
-        <v>1363.767485606512</v>
+        <v>1347.542812627205</v>
       </c>
       <c r="E32">
-        <v>613.0396999999999</v>
+        <v>633.48199</v>
       </c>
       <c r="F32">
-        <v>613.2687</v>
+        <v>633.71099</v>
       </c>
       <c r="G32">
         <v>33.8</v>
@@ -3911,37 +3911,37 @@
         <v>35.1</v>
       </c>
       <c r="M32">
-        <v>144.60875946</v>
+        <v>149.429051442</v>
       </c>
       <c r="N32">
-        <v>-109.50875946</v>
+        <v>-114.329051442</v>
       </c>
       <c r="O32">
-        <v>-27.377189865</v>
+        <v>-28.5822628605</v>
       </c>
       <c r="P32">
-        <v>-82.131569595</v>
+        <v>-85.7467885815</v>
       </c>
       <c r="Q32">
-        <v>-50.331569595</v>
+        <v>-53.94678858149999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1959391088534196</v>
+        <v>0.1981150379672373</v>
       </c>
       <c r="T32">
-        <v>1.45195993129029</v>
+        <v>1.473002828845221</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.06068097142087191</v>
+        <v>0.05872352072987604</v>
       </c>
       <c r="W32">
-        <v>0.2214914269389584</v>
+        <v>0.2219529938118952</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.2427238856834876</v>
+        <v>0.2348940829195041</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.2055048042790813</v>
+        <v>0.2074048042790813</v>
       </c>
       <c r="C33">
-        <v>747.6318226272049</v>
+        <v>711.3463690813355</v>
       </c>
       <c r="D33">
-        <v>1347.542812627205</v>
+        <v>1331.699649081336</v>
       </c>
       <c r="E33">
-        <v>633.48199</v>
+        <v>653.92428</v>
       </c>
       <c r="F33">
-        <v>633.71099</v>
+        <v>654.15328</v>
       </c>
       <c r="G33">
         <v>33.8</v>
@@ -3993,37 +3993,37 @@
         <v>35.1</v>
       </c>
       <c r="M33">
-        <v>149.429051442</v>
+        <v>154.249343424</v>
       </c>
       <c r="N33">
-        <v>-114.329051442</v>
+        <v>-119.149343424</v>
       </c>
       <c r="O33">
-        <v>-28.5822628605</v>
+        <v>-29.78733585600001</v>
       </c>
       <c r="P33">
-        <v>-85.7467885815</v>
+        <v>-89.36200756800002</v>
       </c>
       <c r="Q33">
-        <v>-53.94678858149999</v>
+        <v>-57.56200756800002</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1981150379672373</v>
+        <v>0.2003549649961673</v>
       </c>
       <c r="T33">
-        <v>1.473002828845221</v>
+        <v>1.494664635151769</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.05872352072987604</v>
+        <v>0.05688841070706741</v>
       </c>
       <c r="W33">
-        <v>0.2219529938118952</v>
+        <v>0.2223857127552735</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.2348940829195041</v>
+        <v>0.2275536428282696</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.2074048042790813</v>
+        <v>0.2093048042790813</v>
       </c>
       <c r="C34">
-        <v>711.3463690813355</v>
+        <v>675.4291250308366</v>
       </c>
       <c r="D34">
-        <v>1331.699649081336</v>
+        <v>1316.224695030837</v>
       </c>
       <c r="E34">
-        <v>653.92428</v>
+        <v>674.36657</v>
       </c>
       <c r="F34">
-        <v>654.15328</v>
+        <v>674.5955700000001</v>
       </c>
       <c r="G34">
         <v>33.8</v>
@@ -4075,37 +4075,37 @@
         <v>35.1</v>
       </c>
       <c r="M34">
-        <v>154.249343424</v>
+        <v>159.069635406</v>
       </c>
       <c r="N34">
-        <v>-119.149343424</v>
+        <v>-123.969635406</v>
       </c>
       <c r="O34">
-        <v>-29.78733585600001</v>
+        <v>-30.99240885150001</v>
       </c>
       <c r="P34">
-        <v>-89.36200756800002</v>
+        <v>-92.97722655450002</v>
       </c>
       <c r="Q34">
-        <v>-57.56200756800002</v>
+        <v>-61.17722655450002</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2003549649961673</v>
+        <v>0.2026617555184982</v>
       </c>
       <c r="T34">
-        <v>1.494664635151769</v>
+        <v>1.516973062542094</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.05688841070706741</v>
+        <v>0.05516451947351991</v>
       </c>
       <c r="W34">
-        <v>0.2223857127552735</v>
+        <v>0.222792206308144</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.2275536428282696</v>
+        <v>0.2206580778940795</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.2093048042790813</v>
+        <v>0.2112048042790813</v>
       </c>
       <c r="C35">
-        <v>675.4291250308366</v>
+        <v>639.8674016415924</v>
       </c>
       <c r="D35">
-        <v>1316.224695030837</v>
+        <v>1301.105261641593</v>
       </c>
       <c r="E35">
-        <v>674.36657</v>
+        <v>694.80886</v>
       </c>
       <c r="F35">
-        <v>674.5955700000001</v>
+        <v>695.03786</v>
       </c>
       <c r="G35">
         <v>33.8</v>
@@ -4157,37 +4157,37 @@
         <v>35.1</v>
       </c>
       <c r="M35">
-        <v>159.069635406</v>
+        <v>163.889927388</v>
       </c>
       <c r="N35">
-        <v>-123.969635406</v>
+        <v>-128.789927388</v>
       </c>
       <c r="O35">
-        <v>-30.99240885150001</v>
+        <v>-32.19748184700001</v>
       </c>
       <c r="P35">
-        <v>-92.97722655450002</v>
+        <v>-96.59244554100002</v>
       </c>
       <c r="Q35">
-        <v>-61.17722655450002</v>
+        <v>-64.79244554100001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2026617555184982</v>
+        <v>0.2050384487839299</v>
       </c>
       <c r="T35">
-        <v>1.516973062542094</v>
+        <v>1.539957502883641</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.05516451947351991</v>
+        <v>0.05354203360665168</v>
       </c>
       <c r="W35">
-        <v>0.222792206308144</v>
+        <v>0.2231747884755516</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.2206580778940795</v>
+        <v>0.2141681344266066</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.2112048042790813</v>
+        <v>0.2131048042790813</v>
       </c>
       <c r="C36">
-        <v>639.8674016415924</v>
+        <v>604.6490864833706</v>
       </c>
       <c r="D36">
-        <v>1301.105261641593</v>
+        <v>1286.329236483371</v>
       </c>
       <c r="E36">
-        <v>694.80886</v>
+        <v>715.2511500000001</v>
       </c>
       <c r="F36">
-        <v>695.03786</v>
+        <v>715.4801500000001</v>
       </c>
       <c r="G36">
         <v>33.8</v>
@@ -4239,37 +4239,37 @@
         <v>35.1</v>
       </c>
       <c r="M36">
-        <v>163.889927388</v>
+        <v>168.71021937</v>
       </c>
       <c r="N36">
-        <v>-128.789927388</v>
+        <v>-133.61021937</v>
       </c>
       <c r="O36">
-        <v>-32.19748184700001</v>
+        <v>-33.40255484250001</v>
       </c>
       <c r="P36">
-        <v>-96.59244554100002</v>
+        <v>-100.2076645275</v>
       </c>
       <c r="Q36">
-        <v>-64.79244554100001</v>
+        <v>-68.40766452750003</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2050384487839299</v>
+        <v>0.2074882710729135</v>
       </c>
       <c r="T36">
-        <v>1.539957502883641</v>
+        <v>1.563649156774158</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.05354203360665168</v>
+        <v>0.0520122612178902</v>
       </c>
       <c r="W36">
-        <v>0.2231747884755516</v>
+        <v>0.2235355088048215</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.2141681344266066</v>
+        <v>0.2080490448715607</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.2131048042790813</v>
+        <v>0.2150048042790813</v>
       </c>
       <c r="C37">
-        <v>604.6490864833706</v>
+        <v>569.7626111676436</v>
       </c>
       <c r="D37">
-        <v>1286.329236483371</v>
+        <v>1271.885051167644</v>
       </c>
       <c r="E37">
-        <v>715.2511500000001</v>
+        <v>735.69344</v>
       </c>
       <c r="F37">
-        <v>715.4801500000001</v>
+        <v>735.9224400000001</v>
       </c>
       <c r="G37">
         <v>33.8</v>
@@ -4321,37 +4321,37 @@
         <v>35.1</v>
       </c>
       <c r="M37">
-        <v>168.71021937</v>
+        <v>173.530511352</v>
       </c>
       <c r="N37">
-        <v>-133.61021937</v>
+        <v>-138.430511352</v>
       </c>
       <c r="O37">
-        <v>-33.40255484250001</v>
+        <v>-34.60762783800001</v>
       </c>
       <c r="P37">
-        <v>-100.2076645275</v>
+        <v>-103.822883514</v>
       </c>
       <c r="Q37">
-        <v>-68.40766452750003</v>
+        <v>-72.022883514</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2074882710729135</v>
+        <v>0.2100146503084278</v>
       </c>
       <c r="T37">
-        <v>1.563649156774158</v>
+        <v>1.588081174848754</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.0520122612178902</v>
+        <v>0.05056747618405992</v>
       </c>
       <c r="W37">
-        <v>0.2235355088048215</v>
+        <v>0.2238761891157987</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.2080490448715607</v>
+        <v>0.2022699047362396</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.2150048042790813</v>
+        <v>0.2169048042790813</v>
       </c>
       <c r="C38">
-        <v>569.7626111676433</v>
+        <v>535.1969211415581</v>
       </c>
       <c r="D38">
-        <v>1271.885051167643</v>
+        <v>1257.761651141558</v>
       </c>
       <c r="E38">
-        <v>735.6934399999999</v>
+        <v>756.13573</v>
       </c>
       <c r="F38">
-        <v>735.9224399999999</v>
+        <v>756.36473</v>
       </c>
       <c r="G38">
         <v>33.8</v>
@@ -4403,37 +4403,37 @@
         <v>35.1</v>
       </c>
       <c r="M38">
-        <v>173.530511352</v>
+        <v>178.350803334</v>
       </c>
       <c r="N38">
-        <v>-138.430511352</v>
+        <v>-143.250803334</v>
       </c>
       <c r="O38">
-        <v>-34.607627838</v>
+        <v>-35.8127008335</v>
       </c>
       <c r="P38">
-        <v>-103.822883514</v>
+        <v>-107.4381025005</v>
       </c>
       <c r="Q38">
-        <v>-72.022883514</v>
+        <v>-75.6381025005</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2100146503084278</v>
+        <v>0.2126212320593552</v>
       </c>
       <c r="T38">
-        <v>1.588081174848754</v>
+        <v>1.613288812544766</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.05056747618405993</v>
+        <v>0.04920078763854479</v>
       </c>
       <c r="W38">
-        <v>0.2238761891157987</v>
+        <v>0.2241984542748311</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.2022699047362396</v>
+        <v>0.1968031505541791</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.2169048042790813</v>
+        <v>0.2188048042790813</v>
       </c>
       <c r="C39">
-        <v>535.1969211415581</v>
+        <v>500.9414474723118</v>
       </c>
       <c r="D39">
-        <v>1257.761651141558</v>
+        <v>1243.948467472312</v>
       </c>
       <c r="E39">
-        <v>756.13573</v>
+        <v>776.57802</v>
       </c>
       <c r="F39">
-        <v>756.36473</v>
+        <v>776.8070200000001</v>
       </c>
       <c r="G39">
         <v>33.8</v>
@@ -4485,37 +4485,37 @@
         <v>35.1</v>
       </c>
       <c r="M39">
-        <v>178.350803334</v>
+        <v>183.171095316</v>
       </c>
       <c r="N39">
-        <v>-143.250803334</v>
+        <v>-148.071095316</v>
       </c>
       <c r="O39">
-        <v>-35.8127008335</v>
+        <v>-37.01777382900001</v>
       </c>
       <c r="P39">
-        <v>-107.4381025005</v>
+        <v>-111.053321487</v>
       </c>
       <c r="Q39">
-        <v>-75.6381025005</v>
+        <v>-79.25332148700002</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2126212320593552</v>
+        <v>0.2153118970925706</v>
       </c>
       <c r="T39">
-        <v>1.613288812544766</v>
+        <v>1.639309599843876</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.04920078763854479</v>
+        <v>0.04790603006910939</v>
       </c>
       <c r="W39">
-        <v>0.2241984542748311</v>
+        <v>0.224503758109704</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.1968031505541791</v>
+        <v>0.1916241202764376</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.2188048042790813</v>
+        <v>0.2207048042790813</v>
       </c>
       <c r="C40">
-        <v>500.9414474723118</v>
+        <v>466.9860804705723</v>
       </c>
       <c r="D40">
-        <v>1243.948467472312</v>
+        <v>1230.435390470572</v>
       </c>
       <c r="E40">
-        <v>776.57802</v>
+        <v>797.02031</v>
       </c>
       <c r="F40">
-        <v>776.8070200000001</v>
+        <v>797.24931</v>
       </c>
       <c r="G40">
         <v>33.8</v>
@@ -4567,37 +4567,37 @@
         <v>35.1</v>
       </c>
       <c r="M40">
-        <v>183.171095316</v>
+        <v>187.991387298</v>
       </c>
       <c r="N40">
-        <v>-148.071095316</v>
+        <v>-152.891387298</v>
       </c>
       <c r="O40">
-        <v>-37.01777382900001</v>
+        <v>-38.2228468245</v>
       </c>
       <c r="P40">
-        <v>-111.053321487</v>
+        <v>-114.6685404735</v>
       </c>
       <c r="Q40">
-        <v>-79.25332148700002</v>
+        <v>-82.86854047349999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2153118970925706</v>
+        <v>0.2180907806514652</v>
       </c>
       <c r="T40">
-        <v>1.639309599843876</v>
+        <v>1.666183527710169</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.04790603006910939</v>
+        <v>0.04667767032374762</v>
       </c>
       <c r="W40">
-        <v>0.224503758109704</v>
+        <v>0.2247934053376603</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.1916241202764376</v>
+        <v>0.1867106812949905</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.2207048042790813</v>
+        <v>0.2226048042790812</v>
       </c>
       <c r="C41">
-        <v>466.9860804705723</v>
+        <v>433.3211450146046</v>
       </c>
       <c r="D41">
-        <v>1230.435390470572</v>
+        <v>1217.212745014605</v>
       </c>
       <c r="E41">
-        <v>797.02031</v>
+        <v>817.4626000000001</v>
       </c>
       <c r="F41">
-        <v>797.24931</v>
+        <v>817.6916000000001</v>
       </c>
       <c r="G41">
         <v>33.8</v>
@@ -4649,37 +4649,37 @@
         <v>35.1</v>
       </c>
       <c r="M41">
-        <v>187.991387298</v>
+        <v>192.81167928</v>
       </c>
       <c r="N41">
-        <v>-152.891387298</v>
+        <v>-157.71167928</v>
       </c>
       <c r="O41">
-        <v>-38.2228468245</v>
+        <v>-39.42791982000001</v>
       </c>
       <c r="P41">
-        <v>-114.6685404735</v>
+        <v>-118.28375946</v>
       </c>
       <c r="Q41">
-        <v>-82.86854047349999</v>
+        <v>-86.48375946000002</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2180907806514652</v>
+        <v>0.2209622936623229</v>
       </c>
       <c r="T41">
-        <v>1.666183527710169</v>
+        <v>1.693953253172005</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.04667767032374762</v>
+        <v>0.04551072856565393</v>
       </c>
       <c r="W41">
-        <v>0.2247934053376603</v>
+        <v>0.2250685702042188</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.1867106812949905</v>
+        <v>0.1820429142626157</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.2226048042790812</v>
+        <v>0.2245048042790813</v>
       </c>
       <c r="C42">
-        <v>433.3211450146046</v>
+        <v>399.9373774485284</v>
       </c>
       <c r="D42">
-        <v>1217.212745014605</v>
+        <v>1204.271267448529</v>
       </c>
       <c r="E42">
-        <v>817.4626000000001</v>
+        <v>837.90489</v>
       </c>
       <c r="F42">
-        <v>817.6916000000001</v>
+        <v>838.1338900000001</v>
       </c>
       <c r="G42">
         <v>33.8</v>
@@ -4731,37 +4731,37 @@
         <v>35.1</v>
       </c>
       <c r="M42">
-        <v>192.81167928</v>
+        <v>197.631971262</v>
       </c>
       <c r="N42">
-        <v>-157.71167928</v>
+        <v>-162.531971262</v>
       </c>
       <c r="O42">
-        <v>-39.42791982000001</v>
+        <v>-40.63299281550001</v>
       </c>
       <c r="P42">
-        <v>-118.28375946</v>
+        <v>-121.8989784465</v>
       </c>
       <c r="Q42">
-        <v>-86.48375946000002</v>
+        <v>-90.09897844650001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2209622936623229</v>
+        <v>0.2239311460972775</v>
       </c>
       <c r="T42">
-        <v>1.693953253172005</v>
+        <v>1.722664325259666</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.04551072856565393</v>
+        <v>0.04440071079575993</v>
       </c>
       <c r="W42">
-        <v>0.2250685702042188</v>
+        <v>0.2253303123943598</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.1820429142626157</v>
+        <v>0.1776028431830396</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.2245048042790813</v>
+        <v>0.2264048042790813</v>
       </c>
       <c r="C43">
-        <v>399.9373774485284</v>
+        <v>366.8259039387891</v>
       </c>
       <c r="D43">
-        <v>1204.271267448529</v>
+        <v>1191.602083938789</v>
       </c>
       <c r="E43">
-        <v>837.90489</v>
+        <v>858.3471800000001</v>
       </c>
       <c r="F43">
-        <v>838.1338900000001</v>
+        <v>858.5761800000001</v>
       </c>
       <c r="G43">
         <v>33.8</v>
@@ -4813,37 +4813,37 @@
         <v>35.1</v>
       </c>
       <c r="M43">
-        <v>197.631971262</v>
+        <v>202.4522632440001</v>
       </c>
       <c r="N43">
-        <v>-162.531971262</v>
+        <v>-167.3522632440001</v>
       </c>
       <c r="O43">
-        <v>-40.63299281550001</v>
+        <v>-41.83806581100001</v>
       </c>
       <c r="P43">
-        <v>-121.8989784465</v>
+        <v>-125.514197433</v>
       </c>
       <c r="Q43">
-        <v>-90.09897844650001</v>
+        <v>-93.71419743300004</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2239311460972775</v>
+        <v>0.2270023727541272</v>
       </c>
       <c r="T43">
-        <v>1.722664325259666</v>
+        <v>1.752365434315867</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.04440071079575993</v>
+        <v>0.0433435510149085</v>
       </c>
       <c r="W43">
-        <v>0.2253303123943598</v>
+        <v>0.2255795906706846</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.1776028431830396</v>
+        <v>0.173374204059634</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.2264048042790813</v>
+        <v>0.2283048042790813</v>
       </c>
       <c r="C44">
-        <v>366.8259039387892</v>
+        <v>333.9782201825703</v>
       </c>
       <c r="D44">
-        <v>1191.602083938789</v>
+        <v>1179.19669018257</v>
       </c>
       <c r="E44">
-        <v>858.34718</v>
+        <v>878.7894699999999</v>
       </c>
       <c r="F44">
-        <v>858.57618</v>
+        <v>879.01847</v>
       </c>
       <c r="G44">
         <v>33.8</v>
@@ -4895,37 +4895,37 @@
         <v>35.1</v>
       </c>
       <c r="M44">
-        <v>202.452263244</v>
+        <v>207.272555226</v>
       </c>
       <c r="N44">
-        <v>-167.352263244</v>
+        <v>-172.172555226</v>
       </c>
       <c r="O44">
-        <v>-41.83806581100001</v>
+        <v>-43.0431388065</v>
       </c>
       <c r="P44">
-        <v>-125.514197433</v>
+        <v>-129.1294164195</v>
       </c>
       <c r="Q44">
-        <v>-93.71419743300001</v>
+        <v>-97.32941641950001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2270023727541271</v>
+        <v>0.2301813617498136</v>
       </c>
       <c r="T44">
-        <v>1.752365434315867</v>
+        <v>1.783108687549478</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.0433435510149085</v>
+        <v>0.04233556145642226</v>
       </c>
       <c r="W44">
-        <v>0.2255795906706846</v>
+        <v>0.2258172746085756</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.173374204059634</v>
+        <v>0.169342245825689</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.2283048042790813</v>
+        <v>0.2302048042790813</v>
       </c>
       <c r="C45">
-        <v>333.9782201825703</v>
+        <v>301.3861723706417</v>
       </c>
       <c r="D45">
-        <v>1179.19669018257</v>
+        <v>1167.046932370642</v>
       </c>
       <c r="E45">
-        <v>878.7894699999999</v>
+        <v>899.23176</v>
       </c>
       <c r="F45">
-        <v>879.01847</v>
+        <v>899.4607600000001</v>
       </c>
       <c r="G45">
         <v>33.8</v>
@@ -4977,37 +4977,37 @@
         <v>35.1</v>
       </c>
       <c r="M45">
-        <v>207.272555226</v>
+        <v>212.092847208</v>
       </c>
       <c r="N45">
-        <v>-172.172555226</v>
+        <v>-176.992847208</v>
       </c>
       <c r="O45">
-        <v>-43.0431388065</v>
+        <v>-44.24821180200001</v>
       </c>
       <c r="P45">
-        <v>-129.1294164195</v>
+        <v>-132.744635406</v>
       </c>
       <c r="Q45">
-        <v>-97.32941641950001</v>
+        <v>-100.944635406</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2301813617498136</v>
+        <v>0.2334738860667745</v>
       </c>
       <c r="T45">
-        <v>1.783108687549478</v>
+        <v>1.814949914112862</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.04233556145642226</v>
+        <v>0.04137338960513993</v>
       </c>
       <c r="W45">
-        <v>0.2258172746085756</v>
+        <v>0.226044154731108</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.169342245825689</v>
+        <v>0.1654935584205597</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.2302048042790813</v>
+        <v>0.2321048042790813</v>
       </c>
       <c r="C46">
-        <v>301.3861723706417</v>
+        <v>269.0419393150959</v>
       </c>
       <c r="D46">
-        <v>1167.046932370642</v>
+        <v>1155.144989315096</v>
       </c>
       <c r="E46">
-        <v>899.23176</v>
+        <v>919.67405</v>
       </c>
       <c r="F46">
-        <v>899.4607600000001</v>
+        <v>919.90305</v>
       </c>
       <c r="G46">
         <v>33.8</v>
@@ -5059,37 +5059,37 @@
         <v>35.1</v>
       </c>
       <c r="M46">
-        <v>212.092847208</v>
+        <v>216.91313919</v>
       </c>
       <c r="N46">
-        <v>-176.992847208</v>
+        <v>-181.81313919</v>
       </c>
       <c r="O46">
-        <v>-44.24821180200001</v>
+        <v>-45.4532847975</v>
       </c>
       <c r="P46">
-        <v>-132.744635406</v>
+        <v>-136.3598543925</v>
       </c>
       <c r="Q46">
-        <v>-100.944635406</v>
+        <v>-104.5598543925</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2334738860667745</v>
+        <v>0.2368861385407159</v>
       </c>
       <c r="T46">
-        <v>1.814949914112862</v>
+        <v>1.847949003460369</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.04137338960513993</v>
+        <v>0.04045398094724794</v>
       </c>
       <c r="W46">
-        <v>0.226044154731108</v>
+        <v>0.226260951292639</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.1654935584205597</v>
+        <v>0.1618159237889917</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.2321048042790813</v>
+        <v>0.2340048042790813</v>
       </c>
       <c r="C47">
-        <v>269.0419393150959</v>
+        <v>236.938015659644</v>
       </c>
       <c r="D47">
-        <v>1155.144989315096</v>
+        <v>1143.483355659644</v>
       </c>
       <c r="E47">
-        <v>919.67405</v>
+        <v>940.11634</v>
       </c>
       <c r="F47">
-        <v>919.90305</v>
+        <v>940.3453400000001</v>
       </c>
       <c r="G47">
         <v>33.8</v>
@@ -5141,37 +5141,37 @@
         <v>35.1</v>
       </c>
       <c r="M47">
-        <v>216.91313919</v>
+        <v>221.733431172</v>
       </c>
       <c r="N47">
-        <v>-181.81313919</v>
+        <v>-186.633431172</v>
       </c>
       <c r="O47">
-        <v>-45.4532847975</v>
+        <v>-46.65835779300001</v>
       </c>
       <c r="P47">
-        <v>-136.3598543925</v>
+        <v>-139.975073379</v>
       </c>
       <c r="Q47">
-        <v>-104.5598543925</v>
+        <v>-108.175073379</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2368861385407159</v>
+        <v>0.2404247707359144</v>
       </c>
       <c r="T47">
-        <v>1.847949003460369</v>
+        <v>1.882170281302227</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.04045398094724794</v>
+        <v>0.0395745465788295</v>
       </c>
       <c r="W47">
-        <v>0.226260951292639</v>
+        <v>0.226468321916712</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.1618159237889917</v>
+        <v>0.158298186315318</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.2340048042790813</v>
+        <v>0.2359048042790813</v>
       </c>
       <c r="C48">
-        <v>236.938015659644</v>
+        <v>205.0671960967411</v>
       </c>
       <c r="D48">
-        <v>1143.483355659644</v>
+        <v>1132.054826096741</v>
       </c>
       <c r="E48">
-        <v>940.11634</v>
+        <v>960.55863</v>
       </c>
       <c r="F48">
-        <v>940.3453400000001</v>
+        <v>960.78763</v>
       </c>
       <c r="G48">
         <v>33.8</v>
@@ -5223,37 +5223,37 @@
         <v>35.1</v>
       </c>
       <c r="M48">
-        <v>221.733431172</v>
+        <v>226.553723154</v>
       </c>
       <c r="N48">
-        <v>-186.633431172</v>
+        <v>-191.453723154</v>
       </c>
       <c r="O48">
-        <v>-46.65835779300001</v>
+        <v>-47.8634307885</v>
       </c>
       <c r="P48">
-        <v>-139.975073379</v>
+        <v>-143.5902923655</v>
       </c>
       <c r="Q48">
-        <v>-108.175073379</v>
+        <v>-111.7902923655</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2404247707359144</v>
+        <v>0.2440969362214977</v>
       </c>
       <c r="T48">
-        <v>1.882170281302227</v>
+        <v>1.917682928119251</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.0395745465788295</v>
+        <v>0.03873253494949271</v>
       </c>
       <c r="W48">
-        <v>0.226468321916712</v>
+        <v>0.2266668682589096</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.158298186315318</v>
+        <v>0.1549301397979708</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.2359048042790813</v>
+        <v>0.2378048042790813</v>
       </c>
       <c r="C49">
-        <v>205.0671960967411</v>
+        <v>173.422560521797</v>
       </c>
       <c r="D49">
-        <v>1132.054826096741</v>
+        <v>1120.852480521797</v>
       </c>
       <c r="E49">
-        <v>960.55863</v>
+        <v>981.0009200000001</v>
       </c>
       <c r="F49">
-        <v>960.78763</v>
+        <v>981.2299200000001</v>
       </c>
       <c r="G49">
         <v>33.8</v>
@@ -5305,37 +5305,37 @@
         <v>35.1</v>
       </c>
       <c r="M49">
-        <v>226.553723154</v>
+        <v>231.374015136</v>
       </c>
       <c r="N49">
-        <v>-191.453723154</v>
+        <v>-196.274015136</v>
       </c>
       <c r="O49">
-        <v>-47.8634307885</v>
+        <v>-49.06850378400001</v>
       </c>
       <c r="P49">
-        <v>-143.5902923655</v>
+        <v>-147.205511352</v>
       </c>
       <c r="Q49">
-        <v>-111.7902923655</v>
+        <v>-115.405511352</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2440969362214977</v>
+        <v>0.2479103388411418</v>
       </c>
       <c r="T49">
-        <v>1.917682928119251</v>
+        <v>1.954561445967698</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.03873253494949271</v>
+        <v>0.03792560713804494</v>
       </c>
       <c r="W49">
-        <v>0.2266668682589096</v>
+        <v>0.226857141836849</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.1549301397979708</v>
+        <v>0.1517024285521797</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.2378048042790813</v>
+        <v>0.2397048042790813</v>
       </c>
       <c r="C50">
-        <v>173.4225605217971</v>
+        <v>141.997460060194</v>
       </c>
       <c r="D50">
-        <v>1120.852480521797</v>
+        <v>1109.869670060194</v>
       </c>
       <c r="E50">
-        <v>981.00092</v>
+        <v>1001.44321</v>
       </c>
       <c r="F50">
-        <v>981.22992</v>
+        <v>1001.67221</v>
       </c>
       <c r="G50">
         <v>33.8</v>
@@ -5387,37 +5387,37 @@
         <v>35.1</v>
       </c>
       <c r="M50">
-        <v>231.374015136</v>
+        <v>236.194307118</v>
       </c>
       <c r="N50">
-        <v>-196.274015136</v>
+        <v>-201.094307118</v>
       </c>
       <c r="O50">
-        <v>-49.068503784</v>
+        <v>-50.2735767795</v>
       </c>
       <c r="P50">
-        <v>-147.205511352</v>
+        <v>-150.8207303385</v>
       </c>
       <c r="Q50">
-        <v>-115.405511352</v>
+        <v>-119.0207303385</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2479103388411418</v>
+        <v>0.2518732866615563</v>
       </c>
       <c r="T50">
-        <v>1.954561445967698</v>
+        <v>1.992886180202358</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.03792560713804494</v>
+        <v>0.03715161515563586</v>
       </c>
       <c r="W50">
-        <v>0.226857141836849</v>
+        <v>0.2270396491463011</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.1517024285521797</v>
+        <v>0.1486064606225435</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.2397048042790813</v>
+        <v>0.2416048042790813</v>
       </c>
       <c r="C51">
-        <v>141.997460060194</v>
+        <v>110.7855039078314</v>
       </c>
       <c r="D51">
-        <v>1109.869670060194</v>
+        <v>1099.100003907831</v>
       </c>
       <c r="E51">
-        <v>1001.44321</v>
+        <v>1021.8855</v>
       </c>
       <c r="F51">
-        <v>1001.67221</v>
+        <v>1022.1145</v>
       </c>
       <c r="G51">
         <v>33.8</v>
@@ -5469,37 +5469,37 @@
         <v>35.1</v>
       </c>
       <c r="M51">
-        <v>236.194307118</v>
+        <v>241.0145991</v>
       </c>
       <c r="N51">
-        <v>-201.094307118</v>
+        <v>-205.9145991</v>
       </c>
       <c r="O51">
-        <v>-50.2735767795</v>
+        <v>-51.47864977500001</v>
       </c>
       <c r="P51">
-        <v>-150.8207303385</v>
+        <v>-154.435949325</v>
       </c>
       <c r="Q51">
-        <v>-119.0207303385</v>
+        <v>-122.635949325</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2518732866615563</v>
+        <v>0.2559947523947875</v>
       </c>
       <c r="T51">
-        <v>1.992886180202358</v>
+        <v>2.032743903806406</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.03715161515563586</v>
+        <v>0.03640858285252314</v>
       </c>
       <c r="W51">
-        <v>0.2270396491463011</v>
+        <v>0.2272148561633751</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.1486064606225435</v>
+        <v>0.1456343314100925</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.2416048042790813</v>
+        <v>0.2435048042790813</v>
       </c>
       <c r="C52">
-        <v>110.7855039078314</v>
+        <v>79.78054693046738</v>
       </c>
       <c r="D52">
-        <v>1099.100003907831</v>
+        <v>1088.537336930468</v>
       </c>
       <c r="E52">
-        <v>1021.8855</v>
+        <v>1042.32779</v>
       </c>
       <c r="F52">
-        <v>1022.1145</v>
+        <v>1042.55679</v>
       </c>
       <c r="G52">
         <v>33.8</v>
@@ -5551,37 +5551,37 @@
         <v>35.1</v>
       </c>
       <c r="M52">
-        <v>241.0145991</v>
+        <v>245.834891082</v>
       </c>
       <c r="N52">
-        <v>-205.9145991</v>
+        <v>-210.734891082</v>
       </c>
       <c r="O52">
-        <v>-51.47864977500001</v>
+        <v>-52.68372277050001</v>
       </c>
       <c r="P52">
-        <v>-154.435949325</v>
+        <v>-158.0511683115</v>
       </c>
       <c r="Q52">
-        <v>-122.635949325</v>
+        <v>-126.2511683115</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2559947523947875</v>
+        <v>0.2602844412191709</v>
       </c>
       <c r="T52">
-        <v>2.032743903806406</v>
+        <v>2.074228473271842</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.03640858285252314</v>
+        <v>0.03569468907110112</v>
       </c>
       <c r="W52">
-        <v>0.2272148561633751</v>
+        <v>0.2273831923170344</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.1456343314100925</v>
+        <v>0.1427787562844044</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.2435048042790813</v>
+        <v>0.2454048042790813</v>
       </c>
       <c r="C53">
-        <v>79.78054693046738</v>
+        <v>48.97667797129452</v>
       </c>
       <c r="D53">
-        <v>1088.537336930468</v>
+        <v>1078.175757971295</v>
       </c>
       <c r="E53">
-        <v>1042.32779</v>
+        <v>1062.77008</v>
       </c>
       <c r="F53">
-        <v>1042.55679</v>
+        <v>1062.99908</v>
       </c>
       <c r="G53">
         <v>33.8</v>
@@ -5633,37 +5633,37 @@
         <v>35.1</v>
       </c>
       <c r="M53">
-        <v>245.834891082</v>
+        <v>250.655183064</v>
       </c>
       <c r="N53">
-        <v>-210.734891082</v>
+        <v>-215.555183064</v>
       </c>
       <c r="O53">
-        <v>-52.68372277050001</v>
+        <v>-53.88879576600001</v>
       </c>
       <c r="P53">
-        <v>-158.0511683115</v>
+        <v>-161.666387298</v>
       </c>
       <c r="Q53">
-        <v>-126.2511683115</v>
+        <v>-129.866387298</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2602844412191709</v>
+        <v>0.2647528670779037</v>
       </c>
       <c r="T53">
-        <v>2.074228473271842</v>
+        <v>2.117441566465006</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.03569468907110112</v>
+        <v>0.03500825274281071</v>
       </c>
       <c r="W53">
-        <v>0.2273831923170344</v>
+        <v>0.2275450540032452</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.1427787562844044</v>
+        <v>0.1400330109712429</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.2454048042790813</v>
+        <v>0.2473048042790813</v>
       </c>
       <c r="C54">
-        <v>48.97667797129452</v>
+        <v>18.3682088200112</v>
       </c>
       <c r="D54">
-        <v>1078.175757971295</v>
+        <v>1068.009578820011</v>
       </c>
       <c r="E54">
-        <v>1062.77008</v>
+        <v>1083.21237</v>
       </c>
       <c r="F54">
-        <v>1062.99908</v>
+        <v>1083.44137</v>
       </c>
       <c r="G54">
         <v>33.8</v>
@@ -5715,37 +5715,37 @@
         <v>35.1</v>
       </c>
       <c r="M54">
-        <v>250.655183064</v>
+        <v>255.475475046</v>
       </c>
       <c r="N54">
-        <v>-215.555183064</v>
+        <v>-220.375475046</v>
       </c>
       <c r="O54">
-        <v>-53.88879576600001</v>
+        <v>-55.0938687615</v>
       </c>
       <c r="P54">
-        <v>-161.666387298</v>
+        <v>-165.2816062845</v>
       </c>
       <c r="Q54">
-        <v>-129.866387298</v>
+        <v>-133.4816062845</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2647528670779037</v>
+        <v>0.2694114387178591</v>
       </c>
       <c r="T54">
-        <v>2.117441566465006</v>
+        <v>2.162493514687666</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.03500825274281071</v>
+        <v>0.03434771967219165</v>
       </c>
       <c r="W54">
-        <v>0.2275450540032452</v>
+        <v>0.2277008077012972</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.1400330109712429</v>
+        <v>0.1373908786887665</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2473048042790813</v>
+        <v>0.2492048042790813</v>
       </c>
       <c r="C55">
-        <v>18.3682088200112</v>
+        <v>-12.05033619987444</v>
       </c>
       <c r="D55">
-        <v>1068.009578820011</v>
+        <v>1058.033323800126</v>
       </c>
       <c r="E55">
-        <v>1083.21237</v>
+        <v>1103.65466</v>
       </c>
       <c r="F55">
-        <v>1083.44137</v>
+        <v>1103.88366</v>
       </c>
       <c r="G55">
         <v>33.8</v>
@@ -5797,37 +5797,37 @@
         <v>35.1</v>
       </c>
       <c r="M55">
-        <v>255.475475046</v>
+        <v>260.2957670280001</v>
       </c>
       <c r="N55">
-        <v>-220.375475046</v>
+        <v>-225.1957670280001</v>
       </c>
       <c r="O55">
-        <v>-55.0938687615</v>
+        <v>-56.29894175700002</v>
       </c>
       <c r="P55">
-        <v>-165.2816062845</v>
+        <v>-168.896825271</v>
       </c>
       <c r="Q55">
-        <v>-133.4816062845</v>
+        <v>-137.096825271</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2694114387178591</v>
+        <v>0.274272556950856</v>
       </c>
       <c r="T55">
-        <v>2.162493514687666</v>
+        <v>2.209504243267832</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.03434771967219165</v>
+        <v>0.03371165078937328</v>
       </c>
       <c r="W55">
-        <v>0.2277008077012972</v>
+        <v>0.2278507927438658</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.1373908786887665</v>
+        <v>0.1348466031574931</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2492048042790813</v>
+        <v>0.2511048042790813</v>
       </c>
       <c r="C56">
-        <v>-12.05033619987444</v>
+        <v>-42.28423006554704</v>
       </c>
       <c r="D56">
-        <v>1058.033323800126</v>
+        <v>1048.241719934453</v>
       </c>
       <c r="E56">
-        <v>1103.65466</v>
+        <v>1124.09695</v>
       </c>
       <c r="F56">
-        <v>1103.88366</v>
+        <v>1124.32595</v>
       </c>
       <c r="G56">
         <v>33.8</v>
@@ -5879,37 +5879,37 @@
         <v>35.1</v>
       </c>
       <c r="M56">
-        <v>260.2957670280001</v>
+        <v>265.1160590100001</v>
       </c>
       <c r="N56">
-        <v>-225.1957670280001</v>
+        <v>-230.0160590100001</v>
       </c>
       <c r="O56">
-        <v>-56.29894175700002</v>
+        <v>-57.50401475250002</v>
       </c>
       <c r="P56">
-        <v>-168.896825271</v>
+        <v>-172.5120442575001</v>
       </c>
       <c r="Q56">
-        <v>-137.096825271</v>
+        <v>-140.7120442575001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.274272556950856</v>
+        <v>0.2793497248830972</v>
       </c>
       <c r="T56">
-        <v>2.209504243267832</v>
+        <v>2.258604337562673</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.03371165078937328</v>
+        <v>0.03309871168411194</v>
       </c>
       <c r="W56">
-        <v>0.2278507927438658</v>
+        <v>0.2279953237848864</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.1348466031574931</v>
+        <v>0.1323948467364477</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2511048042790813</v>
+        <v>0.2530048042790813</v>
       </c>
       <c r="C57">
-        <v>-42.28423006554704</v>
+        <v>-72.33855234831663</v>
       </c>
       <c r="D57">
-        <v>1048.241719934453</v>
+        <v>1038.629687651684</v>
       </c>
       <c r="E57">
-        <v>1124.09695</v>
+        <v>1144.53924</v>
       </c>
       <c r="F57">
-        <v>1124.32595</v>
+        <v>1144.76824</v>
       </c>
       <c r="G57">
         <v>33.8</v>
@@ -5961,37 +5961,37 @@
         <v>35.1</v>
       </c>
       <c r="M57">
-        <v>265.1160590100001</v>
+        <v>269.936350992</v>
       </c>
       <c r="N57">
-        <v>-230.0160590100001</v>
+        <v>-234.836350992</v>
       </c>
       <c r="O57">
-        <v>-57.50401475250002</v>
+        <v>-58.70908774800001</v>
       </c>
       <c r="P57">
-        <v>-172.5120442575001</v>
+        <v>-176.127263244</v>
       </c>
       <c r="Q57">
-        <v>-140.7120442575001</v>
+        <v>-144.327263244</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2793497248830972</v>
+        <v>0.2846576731758949</v>
       </c>
       <c r="T57">
-        <v>2.258604337562673</v>
+        <v>2.309936254325461</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.03309871168411194</v>
+        <v>0.03250766326118137</v>
       </c>
       <c r="W57">
-        <v>0.2279953237848864</v>
+        <v>0.2281346930030135</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.1323948467364477</v>
+        <v>0.1300306530447255</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2530048042790813</v>
+        <v>0.2549048042790813</v>
       </c>
       <c r="C58">
-        <v>-72.33855234831663</v>
+        <v>-102.2181980003866</v>
       </c>
       <c r="D58">
-        <v>1038.629687651684</v>
+        <v>1029.192331999614</v>
       </c>
       <c r="E58">
-        <v>1144.53924</v>
+        <v>1164.98153</v>
       </c>
       <c r="F58">
-        <v>1144.76824</v>
+        <v>1165.21053</v>
       </c>
       <c r="G58">
         <v>33.8</v>
@@ -6043,37 +6043,37 @@
         <v>35.1</v>
       </c>
       <c r="M58">
-        <v>269.936350992</v>
+        <v>274.756642974</v>
       </c>
       <c r="N58">
-        <v>-234.836350992</v>
+        <v>-239.6566429740001</v>
       </c>
       <c r="O58">
-        <v>-58.70908774800001</v>
+        <v>-59.91416074350001</v>
       </c>
       <c r="P58">
-        <v>-176.127263244</v>
+        <v>-179.7424822305</v>
       </c>
       <c r="Q58">
-        <v>-144.327263244</v>
+        <v>-147.9424822305</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2846576731758949</v>
+        <v>0.2902125027846367</v>
       </c>
       <c r="T58">
-        <v>2.309936254325461</v>
+        <v>2.363655702100472</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.03250766326118137</v>
+        <v>0.03193735337940627</v>
       </c>
       <c r="W58">
-        <v>0.2281346930030135</v>
+        <v>0.228269172073136</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.1300306530447255</v>
+        <v>0.127749413517625</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2549048042790813</v>
+        <v>0.2568048042790813</v>
       </c>
       <c r="C59">
-        <v>-102.2181980003866</v>
+        <v>-131.9278856669014</v>
       </c>
       <c r="D59">
-        <v>1029.192331999614</v>
+        <v>1019.924934333099</v>
       </c>
       <c r="E59">
-        <v>1164.98153</v>
+        <v>1185.42382</v>
       </c>
       <c r="F59">
-        <v>1165.21053</v>
+        <v>1185.65282</v>
       </c>
       <c r="G59">
         <v>33.8</v>
@@ -6125,37 +6125,37 @@
         <v>35.1</v>
       </c>
       <c r="M59">
-        <v>274.756642974</v>
+        <v>279.5769349560001</v>
       </c>
       <c r="N59">
-        <v>-239.6566429740001</v>
+        <v>-244.4769349560001</v>
       </c>
       <c r="O59">
-        <v>-59.91416074350001</v>
+        <v>-61.11923373900002</v>
       </c>
       <c r="P59">
-        <v>-179.7424822305</v>
+        <v>-183.3577012170001</v>
       </c>
       <c r="Q59">
-        <v>-147.9424822305</v>
+        <v>-151.557701217</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2902125027846367</v>
+        <v>0.2960318480890328</v>
       </c>
       <c r="T59">
-        <v>2.363655702100472</v>
+        <v>2.41993321881715</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.03193735337940627</v>
+        <v>0.0313867093556234</v>
       </c>
       <c r="W59">
-        <v>0.228269172073136</v>
+        <v>0.228399013933944</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.127749413517625</v>
+        <v>0.1255468374224935</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2568048042790813</v>
+        <v>0.2587048042790813</v>
       </c>
       <c r="C60">
-        <v>-131.9278856669007</v>
+        <v>-161.472165552919</v>
       </c>
       <c r="D60">
-        <v>1019.924934333099</v>
+        <v>1010.822944447081</v>
       </c>
       <c r="E60">
-        <v>1185.42382</v>
+        <v>1205.86611</v>
       </c>
       <c r="F60">
-        <v>1185.65282</v>
+        <v>1206.09511</v>
       </c>
       <c r="G60">
         <v>33.8</v>
@@ -6207,37 +6207,37 @@
         <v>35.1</v>
       </c>
       <c r="M60">
-        <v>279.576934956</v>
+        <v>284.397226938</v>
       </c>
       <c r="N60">
-        <v>-244.476934956</v>
+        <v>-249.297226938</v>
       </c>
       <c r="O60">
-        <v>-61.119233739</v>
+        <v>-62.32430673450001</v>
       </c>
       <c r="P60">
-        <v>-183.357701217</v>
+        <v>-186.9729202035</v>
       </c>
       <c r="Q60">
-        <v>-151.557701217</v>
+        <v>-155.1729202035</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2960318480890327</v>
+        <v>0.3021350638960823</v>
       </c>
       <c r="T60">
-        <v>2.419933218817149</v>
+        <v>2.478955980251714</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.0313867093556234</v>
+        <v>0.03085473123095182</v>
       </c>
       <c r="W60">
-        <v>0.228399013933944</v>
+        <v>0.2285244543757416</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.1255468374224936</v>
+        <v>0.1234189249238072</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2587048042790813</v>
+        <v>0.2606048042790813</v>
       </c>
       <c r="C61">
-        <v>-161.472165552919</v>
+        <v>-190.8554268728817</v>
       </c>
       <c r="D61">
-        <v>1010.822944447081</v>
+        <v>1001.881973127118</v>
       </c>
       <c r="E61">
-        <v>1205.86611</v>
+        <v>1226.3084</v>
       </c>
       <c r="F61">
-        <v>1206.09511</v>
+        <v>1226.5374</v>
       </c>
       <c r="G61">
         <v>33.8</v>
@@ -6289,37 +6289,37 @@
         <v>35.1</v>
       </c>
       <c r="M61">
-        <v>284.397226938</v>
+        <v>289.21751892</v>
       </c>
       <c r="N61">
-        <v>-249.297226938</v>
+        <v>-254.11751892</v>
       </c>
       <c r="O61">
-        <v>-62.32430673450001</v>
+        <v>-63.52937973</v>
       </c>
       <c r="P61">
-        <v>-186.9729202035</v>
+        <v>-190.58813919</v>
       </c>
       <c r="Q61">
-        <v>-155.1729202035</v>
+        <v>-158.78813919</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.3021350638960823</v>
+        <v>0.3085434404934844</v>
       </c>
       <c r="T61">
-        <v>2.478955980251714</v>
+        <v>2.540929879758007</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.03085473123095182</v>
+        <v>0.03034048571043596</v>
       </c>
       <c r="W61">
-        <v>0.2285244543757416</v>
+        <v>0.2286457134694792</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.1234189249238072</v>
+        <v>0.1213619428417438</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2606048042790813</v>
+        <v>0.2625048042790813</v>
       </c>
       <c r="C62">
-        <v>-190.8554268728817</v>
+        <v>-220.0819049081872</v>
       </c>
       <c r="D62">
-        <v>1001.881973127118</v>
+        <v>993.0977850918127</v>
       </c>
       <c r="E62">
-        <v>1226.3084</v>
+        <v>1246.75069</v>
       </c>
       <c r="F62">
-        <v>1226.5374</v>
+        <v>1246.97969</v>
       </c>
       <c r="G62">
         <v>33.8</v>
@@ -6371,37 +6371,37 @@
         <v>35.1</v>
       </c>
       <c r="M62">
-        <v>289.21751892</v>
+        <v>294.037810902</v>
       </c>
       <c r="N62">
-        <v>-254.11751892</v>
+        <v>-258.937810902</v>
       </c>
       <c r="O62">
-        <v>-63.52937973</v>
+        <v>-64.73445272549999</v>
       </c>
       <c r="P62">
-        <v>-190.58813919</v>
+        <v>-194.2033581765</v>
       </c>
       <c r="Q62">
-        <v>-158.78813919</v>
+        <v>-162.4033581765</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.3085434404934844</v>
+        <v>0.3152804517881891</v>
       </c>
       <c r="T62">
-        <v>2.540929879758007</v>
+        <v>2.60608192795693</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.03034048571043596</v>
+        <v>0.02984310069878946</v>
       </c>
       <c r="W62">
-        <v>0.2286457134694792</v>
+        <v>0.2287629968552254</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.1213619428417438</v>
+        <v>0.1193724027951579</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2625048042790813</v>
+        <v>0.2644048042790813</v>
       </c>
       <c r="C63">
-        <v>-220.0819049081872</v>
+        <v>-249.1556876967244</v>
       </c>
       <c r="D63">
-        <v>993.0977850918127</v>
+        <v>984.4662923032757</v>
       </c>
       <c r="E63">
-        <v>1246.75069</v>
+        <v>1267.19298</v>
       </c>
       <c r="F63">
-        <v>1246.97969</v>
+        <v>1267.42198</v>
       </c>
       <c r="G63">
         <v>33.8</v>
@@ -6453,37 +6453,37 @@
         <v>35.1</v>
       </c>
       <c r="M63">
-        <v>294.037810902</v>
+        <v>298.858102884</v>
       </c>
       <c r="N63">
-        <v>-258.937810902</v>
+        <v>-263.758102884</v>
       </c>
       <c r="O63">
-        <v>-64.73445272549999</v>
+        <v>-65.939525721</v>
       </c>
       <c r="P63">
-        <v>-194.2033581765</v>
+        <v>-197.818577163</v>
       </c>
       <c r="Q63">
-        <v>-162.4033581765</v>
+        <v>-166.018577163</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.3152804517881891</v>
+        <v>0.3223720426247204</v>
       </c>
       <c r="T63">
-        <v>2.60608192795693</v>
+        <v>2.674663031324218</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.02984310069878946</v>
+        <v>0.02936176036493802</v>
       </c>
       <c r="W63">
-        <v>0.2287629968552254</v>
+        <v>0.2288764969059476</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.1193724027951579</v>
+        <v>0.1174470414597522</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2644048042790813</v>
+        <v>0.2663048042790813</v>
       </c>
       <c r="C64">
-        <v>-249.1556876967244</v>
+        <v>-278.0807223765586</v>
       </c>
       <c r="D64">
-        <v>984.4662923032757</v>
+        <v>975.9835476234415</v>
       </c>
       <c r="E64">
-        <v>1267.19298</v>
+        <v>1287.63527</v>
       </c>
       <c r="F64">
-        <v>1267.42198</v>
+        <v>1287.86427</v>
       </c>
       <c r="G64">
         <v>33.8</v>
@@ -6535,37 +6535,37 @@
         <v>35.1</v>
       </c>
       <c r="M64">
-        <v>298.858102884</v>
+        <v>303.678394866</v>
       </c>
       <c r="N64">
-        <v>-263.758102884</v>
+        <v>-268.578394866</v>
       </c>
       <c r="O64">
-        <v>-65.939525721</v>
+        <v>-67.1445987165</v>
       </c>
       <c r="P64">
-        <v>-197.818577163</v>
+        <v>-201.4337961495</v>
       </c>
       <c r="Q64">
-        <v>-166.018577163</v>
+        <v>-169.6337961495</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.3223720426247204</v>
+        <v>0.3298469626956588</v>
       </c>
       <c r="T64">
-        <v>2.674663031324218</v>
+        <v>2.746951221360008</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.02936176036493802</v>
+        <v>0.02889570067660567</v>
       </c>
       <c r="W64">
-        <v>0.2288764969059476</v>
+        <v>0.2289863937804564</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.1174470414597522</v>
+        <v>0.1155828027064227</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2663048042790813</v>
+        <v>0.2682048042790813</v>
       </c>
       <c r="C65">
-        <v>-278.0807223765586</v>
+        <v>-306.8608212044539</v>
       </c>
       <c r="D65">
-        <v>975.9835476234415</v>
+        <v>967.6457387955461</v>
       </c>
       <c r="E65">
-        <v>1287.63527</v>
+        <v>1308.07756</v>
       </c>
       <c r="F65">
-        <v>1287.86427</v>
+        <v>1308.30656</v>
       </c>
       <c r="G65">
         <v>33.8</v>
@@ -6617,37 +6617,37 @@
         <v>35.1</v>
       </c>
       <c r="M65">
-        <v>303.678394866</v>
+        <v>308.498686848</v>
       </c>
       <c r="N65">
-        <v>-268.578394866</v>
+        <v>-273.398686848</v>
       </c>
       <c r="O65">
-        <v>-67.1445987165</v>
+        <v>-68.349671712</v>
       </c>
       <c r="P65">
-        <v>-201.4337961495</v>
+        <v>-205.049015136</v>
       </c>
       <c r="Q65">
-        <v>-169.6337961495</v>
+        <v>-173.249015136</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3298469626956588</v>
+        <v>0.3377371561038716</v>
       </c>
       <c r="T65">
-        <v>2.746951221360008</v>
+        <v>2.823255421953341</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.02889570067660567</v>
+        <v>0.02844420535353371</v>
       </c>
       <c r="W65">
-        <v>0.2289863937804564</v>
+        <v>0.2290928563776367</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.1155828027064227</v>
+        <v>0.1137768214141349</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2682048042790813</v>
+        <v>0.2701048042790813</v>
       </c>
       <c r="C66">
-        <v>-306.8608212044539</v>
+        <v>-335.4996672685144</v>
       </c>
       <c r="D66">
-        <v>967.6457387955461</v>
+        <v>959.4491827314858</v>
       </c>
       <c r="E66">
-        <v>1308.07756</v>
+        <v>1328.51985</v>
       </c>
       <c r="F66">
-        <v>1308.30656</v>
+        <v>1328.74885</v>
       </c>
       <c r="G66">
         <v>33.8</v>
@@ -6699,37 +6699,37 @@
         <v>35.1</v>
       </c>
       <c r="M66">
-        <v>308.498686848</v>
+        <v>313.31897883</v>
       </c>
       <c r="N66">
-        <v>-273.398686848</v>
+        <v>-278.21897883</v>
       </c>
       <c r="O66">
-        <v>-68.349671712</v>
+        <v>-69.55474470750001</v>
       </c>
       <c r="P66">
-        <v>-205.049015136</v>
+        <v>-208.6642341225</v>
       </c>
       <c r="Q66">
-        <v>-173.249015136</v>
+        <v>-176.8642341225</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3377371561038716</v>
+        <v>0.3460782177068393</v>
       </c>
       <c r="T66">
-        <v>2.823255421953341</v>
+        <v>2.90391986258058</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.02844420535353371</v>
+        <v>0.02800660219424857</v>
       </c>
       <c r="W66">
-        <v>0.2290928563776367</v>
+        <v>0.2291960432025962</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.1137768214141349</v>
+        <v>0.1120264087769943</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2701048042790813</v>
+        <v>0.2720048042790812</v>
       </c>
       <c r="C67">
-        <v>-335.4996672685144</v>
+        <v>-364.00081991292</v>
       </c>
       <c r="D67">
-        <v>959.4491827314858</v>
+        <v>951.3903200870802</v>
       </c>
       <c r="E67">
-        <v>1328.51985</v>
+        <v>1348.96214</v>
       </c>
       <c r="F67">
-        <v>1328.74885</v>
+        <v>1349.19114</v>
       </c>
       <c r="G67">
         <v>33.8</v>
@@ -6781,37 +6781,37 @@
         <v>35.1</v>
       </c>
       <c r="M67">
-        <v>313.31897883</v>
+        <v>318.1392708120001</v>
       </c>
       <c r="N67">
-        <v>-278.21897883</v>
+        <v>-283.039270812</v>
       </c>
       <c r="O67">
-        <v>-69.55474470750001</v>
+        <v>-70.75981770300001</v>
       </c>
       <c r="P67">
-        <v>-208.6642341225</v>
+        <v>-212.279453109</v>
       </c>
       <c r="Q67">
-        <v>-176.8642341225</v>
+        <v>-180.479453109</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.3460782177068393</v>
+        <v>0.3549099299923346</v>
       </c>
       <c r="T67">
-        <v>2.90391986258058</v>
+        <v>2.989329270303537</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.02800660219424857</v>
+        <v>0.02758225973675995</v>
       </c>
       <c r="W67">
-        <v>0.2291960432025962</v>
+        <v>0.229296103154072</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.1120264087769943</v>
+        <v>0.1103290389470398</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2720048042790812</v>
+        <v>0.2739048042790813</v>
       </c>
       <c r="C68">
-        <v>-364.00081991292</v>
+        <v>-392.3677198915589</v>
       </c>
       <c r="D68">
-        <v>951.3903200870802</v>
+        <v>943.4657101084413</v>
       </c>
       <c r="E68">
-        <v>1348.96214</v>
+        <v>1369.40443</v>
       </c>
       <c r="F68">
-        <v>1349.19114</v>
+        <v>1369.63343</v>
       </c>
       <c r="G68">
         <v>33.8</v>
@@ -6863,37 +6863,37 @@
         <v>35.1</v>
       </c>
       <c r="M68">
-        <v>318.1392708120001</v>
+        <v>322.959562794</v>
       </c>
       <c r="N68">
-        <v>-283.039270812</v>
+        <v>-287.859562794</v>
       </c>
       <c r="O68">
-        <v>-70.75981770300001</v>
+        <v>-71.9648906985</v>
       </c>
       <c r="P68">
-        <v>-212.279453109</v>
+        <v>-215.8946720955</v>
       </c>
       <c r="Q68">
-        <v>-180.479453109</v>
+        <v>-184.0946720955</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3549099299923346</v>
+        <v>0.3642768975678599</v>
       </c>
       <c r="T68">
-        <v>2.989329270303537</v>
+        <v>3.079915005767281</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.02758225973675995</v>
+        <v>0.02717058421830085</v>
       </c>
       <c r="W68">
-        <v>0.229296103154072</v>
+        <v>0.2293931762413247</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.1103290389470398</v>
+        <v>0.1086823368732035</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2739048042790813</v>
+        <v>0.2758048042790813</v>
       </c>
       <c r="C69">
-        <v>-392.3677198915589</v>
+        <v>-420.6036942662164</v>
       </c>
       <c r="D69">
-        <v>943.4657101084413</v>
+        <v>935.6720257337837</v>
       </c>
       <c r="E69">
-        <v>1369.40443</v>
+        <v>1389.84672</v>
       </c>
       <c r="F69">
-        <v>1369.63343</v>
+        <v>1390.07572</v>
       </c>
       <c r="G69">
         <v>33.8</v>
@@ -6945,37 +6945,37 @@
         <v>35.1</v>
       </c>
       <c r="M69">
-        <v>322.959562794</v>
+        <v>327.779854776</v>
       </c>
       <c r="N69">
-        <v>-287.859562794</v>
+        <v>-292.679854776</v>
       </c>
       <c r="O69">
-        <v>-71.9648906985</v>
+        <v>-73.169963694</v>
       </c>
       <c r="P69">
-        <v>-215.8946720955</v>
+        <v>-219.509891082</v>
       </c>
       <c r="Q69">
-        <v>-184.0946720955</v>
+        <v>-187.709891082</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3642768975678599</v>
+        <v>0.3742293006168556</v>
       </c>
       <c r="T69">
-        <v>3.079915005767281</v>
+        <v>3.176162349697509</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.02717058421830085</v>
+        <v>0.02677101680332584</v>
       </c>
       <c r="W69">
-        <v>0.2293931762413247</v>
+        <v>0.2294873942377758</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.1086823368732035</v>
+        <v>0.1070840672133034</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2758048042790813</v>
+        <v>0.2777048042790813</v>
       </c>
       <c r="C70">
-        <v>-420.6036942662164</v>
+        <v>-448.7119610639837</v>
       </c>
       <c r="D70">
-        <v>935.6720257337837</v>
+        <v>928.0060489360166</v>
       </c>
       <c r="E70">
-        <v>1389.84672</v>
+        <v>1410.28901</v>
       </c>
       <c r="F70">
-        <v>1390.07572</v>
+        <v>1410.51801</v>
       </c>
       <c r="G70">
         <v>33.8</v>
@@ -7027,37 +7027,37 @@
         <v>35.1</v>
       </c>
       <c r="M70">
-        <v>327.779854776</v>
+        <v>332.6001467580001</v>
       </c>
       <c r="N70">
-        <v>-292.679854776</v>
+        <v>-297.500146758</v>
       </c>
       <c r="O70">
-        <v>-73.169963694</v>
+        <v>-74.37503668950001</v>
       </c>
       <c r="P70">
-        <v>-219.509891082</v>
+        <v>-223.1251100685</v>
       </c>
       <c r="Q70">
-        <v>-187.709891082</v>
+        <v>-191.3251100685</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3742293006168556</v>
+        <v>0.3848237941851412</v>
       </c>
       <c r="T70">
-        <v>3.176162349697509</v>
+        <v>3.278619199687752</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.02677101680332584</v>
+        <v>0.026383031052553</v>
       </c>
       <c r="W70">
-        <v>0.2294873942377758</v>
+        <v>0.229578881277808</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.1070840672133034</v>
+        <v>0.1055321242102121</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2777048042790813</v>
+        <v>0.2796048042790813</v>
       </c>
       <c r="C71">
-        <v>-448.7119610639837</v>
+        <v>-476.6956337075749</v>
       </c>
       <c r="D71">
-        <v>928.0060489360166</v>
+        <v>920.4646662924254</v>
       </c>
       <c r="E71">
-        <v>1410.28901</v>
+        <v>1430.7313</v>
       </c>
       <c r="F71">
-        <v>1410.51801</v>
+        <v>1430.9603</v>
       </c>
       <c r="G71">
         <v>33.8</v>
@@ -7109,37 +7109,37 @@
         <v>35.1</v>
       </c>
       <c r="M71">
-        <v>332.6001467580001</v>
+        <v>337.4204387400001</v>
       </c>
       <c r="N71">
-        <v>-297.500146758</v>
+        <v>-302.32043874</v>
       </c>
       <c r="O71">
-        <v>-74.37503668950001</v>
+        <v>-75.58010968500001</v>
       </c>
       <c r="P71">
-        <v>-223.1251100685</v>
+        <v>-226.740329055</v>
       </c>
       <c r="Q71">
-        <v>-191.3251100685</v>
+        <v>-194.940329055</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3848237941851412</v>
+        <v>0.3961245873246459</v>
       </c>
       <c r="T71">
-        <v>3.278619199687752</v>
+        <v>3.38790650634401</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.026383031052553</v>
+        <v>0.0260061306089451</v>
       </c>
       <c r="W71">
-        <v>0.229578881277808</v>
+        <v>0.2296677544024108</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.1055321242102121</v>
+        <v>0.1040245224357804</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2796048042790813</v>
+        <v>0.2815048042790813</v>
       </c>
       <c r="C72">
-        <v>-476.6956337075749</v>
+        <v>-504.5577252313692</v>
       </c>
       <c r="D72">
-        <v>920.4646662924254</v>
+        <v>913.044864768631</v>
       </c>
       <c r="E72">
-        <v>1430.7313</v>
+        <v>1451.17359</v>
       </c>
       <c r="F72">
-        <v>1430.9603</v>
+        <v>1451.40259</v>
       </c>
       <c r="G72">
         <v>33.8</v>
@@ -7191,37 +7191,37 @@
         <v>35.1</v>
       </c>
       <c r="M72">
-        <v>337.4204387400001</v>
+        <v>342.240730722</v>
       </c>
       <c r="N72">
-        <v>-302.32043874</v>
+        <v>-307.140730722</v>
       </c>
       <c r="O72">
-        <v>-75.58010968500001</v>
+        <v>-76.7851826805</v>
       </c>
       <c r="P72">
-        <v>-226.740329055</v>
+        <v>-230.3555480415</v>
       </c>
       <c r="Q72">
-        <v>-194.940329055</v>
+        <v>-198.5555480415</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3961245873246459</v>
+        <v>0.4082047455082545</v>
       </c>
       <c r="T72">
-        <v>3.38790650634401</v>
+        <v>3.504730868631735</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.0260061306089451</v>
+        <v>0.02563984707924165</v>
       </c>
       <c r="W72">
-        <v>0.2296677544024108</v>
+        <v>0.2297541240587148</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.1040245224357804</v>
+        <v>0.1025593883169666</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2815048042790813</v>
+        <v>0.2834048042790813</v>
       </c>
       <c r="C73">
-        <v>-504.557725231369</v>
+        <v>-532.301152295175</v>
       </c>
       <c r="D73">
-        <v>913.044864768631</v>
+        <v>905.7437277048249</v>
       </c>
       <c r="E73">
-        <v>1451.17359</v>
+        <v>1471.61588</v>
       </c>
       <c r="F73">
-        <v>1451.40259</v>
+        <v>1471.84488</v>
       </c>
       <c r="G73">
         <v>33.8</v>
@@ -7273,37 +7273,37 @@
         <v>35.1</v>
       </c>
       <c r="M73">
-        <v>342.240730722</v>
+        <v>347.061022704</v>
       </c>
       <c r="N73">
-        <v>-307.1407307219999</v>
+        <v>-311.961022704</v>
       </c>
       <c r="O73">
-        <v>-76.78518268049999</v>
+        <v>-77.99025567599999</v>
       </c>
       <c r="P73">
-        <v>-230.3555480415</v>
+        <v>-233.970767028</v>
       </c>
       <c r="Q73">
-        <v>-198.5555480414999</v>
+        <v>-202.1707670279999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.4082047455082543</v>
+        <v>0.4211477721335491</v>
       </c>
       <c r="T73">
-        <v>3.504730868631734</v>
+        <v>3.629899828225724</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.02563984707924166</v>
+        <v>0.02528373809202996</v>
       </c>
       <c r="W73">
-        <v>0.2297541240587148</v>
+        <v>0.2298380945578993</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.1025593883169666</v>
+        <v>0.1011349523681199</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2834048042790813</v>
+        <v>0.2853048042790813</v>
       </c>
       <c r="C74">
-        <v>-532.301152295175</v>
+        <v>-559.9287390069434</v>
       </c>
       <c r="D74">
-        <v>905.7437277048249</v>
+        <v>898.5584309930567</v>
       </c>
       <c r="E74">
-        <v>1471.61588</v>
+        <v>1492.05817</v>
       </c>
       <c r="F74">
-        <v>1471.84488</v>
+        <v>1492.28717</v>
       </c>
       <c r="G74">
         <v>33.8</v>
@@ -7355,37 +7355,37 @@
         <v>35.1</v>
       </c>
       <c r="M74">
-        <v>347.061022704</v>
+        <v>351.8813146860001</v>
       </c>
       <c r="N74">
-        <v>-311.961022704</v>
+        <v>-316.781314686</v>
       </c>
       <c r="O74">
-        <v>-77.99025567599999</v>
+        <v>-79.19532867150001</v>
       </c>
       <c r="P74">
-        <v>-233.970767028</v>
+        <v>-237.5859860145</v>
       </c>
       <c r="Q74">
-        <v>-202.1707670279999</v>
+        <v>-205.7859860145</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.4211477721335491</v>
+        <v>0.4350495414718287</v>
       </c>
       <c r="T74">
-        <v>3.629899828225724</v>
+        <v>3.764340562604454</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.02528373809202996</v>
+        <v>0.02493738551542681</v>
       </c>
       <c r="W74">
-        <v>0.2298380945578993</v>
+        <v>0.2299197644954624</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.1011349523681199</v>
+        <v>0.09974954206170727</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2853048042790813</v>
+        <v>0.2872048042790813</v>
       </c>
       <c r="C75">
-        <v>-559.9287390069434</v>
+        <v>-587.4432205649586</v>
       </c>
       <c r="D75">
-        <v>898.5584309930567</v>
+        <v>891.4862394350415</v>
       </c>
       <c r="E75">
-        <v>1492.05817</v>
+        <v>1512.50046</v>
       </c>
       <c r="F75">
-        <v>1492.28717</v>
+        <v>1512.72946</v>
       </c>
       <c r="G75">
         <v>33.8</v>
@@ -7437,37 +7437,37 @@
         <v>35.1</v>
       </c>
       <c r="M75">
-        <v>351.8813146860001</v>
+        <v>356.701606668</v>
       </c>
       <c r="N75">
-        <v>-316.781314686</v>
+        <v>-321.601606668</v>
       </c>
       <c r="O75">
-        <v>-79.19532867150001</v>
+        <v>-80.400401667</v>
       </c>
       <c r="P75">
-        <v>-237.5859860145</v>
+        <v>-241.201205001</v>
       </c>
       <c r="Q75">
-        <v>-205.7859860145</v>
+        <v>-209.401205001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.4350495414718287</v>
+        <v>0.4500206776822837</v>
       </c>
       <c r="T75">
-        <v>3.764340562604454</v>
+        <v>3.909122891935395</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.02493738551542681</v>
+        <v>0.02460039381927239</v>
       </c>
       <c r="W75">
-        <v>0.2299197644954624</v>
+        <v>0.2299992271374156</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.09974954206170727</v>
+        <v>0.09840157527708959</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2872048042790813</v>
+        <v>0.2891048042790813</v>
       </c>
       <c r="C76">
-        <v>-587.4432205649586</v>
+        <v>-614.8472467293773</v>
       </c>
       <c r="D76">
-        <v>891.4862394350415</v>
+        <v>884.5245032706227</v>
       </c>
       <c r="E76">
-        <v>1512.50046</v>
+        <v>1532.94275</v>
       </c>
       <c r="F76">
-        <v>1512.72946</v>
+        <v>1533.17175</v>
       </c>
       <c r="G76">
         <v>33.8</v>
@@ -7519,37 +7519,37 @@
         <v>35.1</v>
       </c>
       <c r="M76">
-        <v>356.701606668</v>
+        <v>361.52189865</v>
       </c>
       <c r="N76">
-        <v>-321.601606668</v>
+        <v>-326.42189865</v>
       </c>
       <c r="O76">
-        <v>-80.400401667</v>
+        <v>-81.6054746625</v>
       </c>
       <c r="P76">
-        <v>-241.201205001</v>
+        <v>-244.8164239875</v>
       </c>
       <c r="Q76">
-        <v>-209.401205001</v>
+        <v>-213.0164239875</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.4500206776822837</v>
+        <v>0.466189504789575</v>
       </c>
       <c r="T76">
-        <v>3.909122891935395</v>
+        <v>4.065487807612811</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.02460039381927239</v>
+        <v>0.02427238856834876</v>
       </c>
       <c r="W76">
-        <v>0.2299992271374156</v>
+        <v>0.2300765707755834</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.09840157527708959</v>
+        <v>0.09708955427339516</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2891048042790813</v>
+        <v>0.2910048042790813</v>
       </c>
       <c r="C77">
-        <v>-614.8472467293773</v>
+        <v>-642.1433851323699</v>
       </c>
       <c r="D77">
-        <v>884.5245032706227</v>
+        <v>877.6706548676303</v>
       </c>
       <c r="E77">
-        <v>1532.94275</v>
+        <v>1553.38504</v>
       </c>
       <c r="F77">
-        <v>1533.17175</v>
+        <v>1553.61404</v>
       </c>
       <c r="G77">
         <v>33.8</v>
@@ -7601,37 +7601,37 @@
         <v>35.1</v>
       </c>
       <c r="M77">
-        <v>361.52189865</v>
+        <v>366.342190632</v>
       </c>
       <c r="N77">
-        <v>-326.42189865</v>
+        <v>-331.242190632</v>
       </c>
       <c r="O77">
-        <v>-81.6054746625</v>
+        <v>-82.810547658</v>
       </c>
       <c r="P77">
-        <v>-244.8164239875</v>
+        <v>-248.431642974</v>
       </c>
       <c r="Q77">
-        <v>-213.0164239875</v>
+        <v>-216.631642974</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.466189504789575</v>
+        <v>0.4837057341558074</v>
       </c>
       <c r="T77">
-        <v>4.065487807612811</v>
+        <v>4.234883132930013</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.02427238856834876</v>
+        <v>0.0239530150345547</v>
       </c>
       <c r="W77">
-        <v>0.2300765707755834</v>
+        <v>0.230151879054852</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.09708955427339516</v>
+        <v>0.09581206013821886</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2910048042790813</v>
+        <v>0.2929048042790813</v>
       </c>
       <c r="C78">
-        <v>-642.1433851323699</v>
+        <v>-669.3341244355452</v>
       </c>
       <c r="D78">
-        <v>877.6706548676303</v>
+        <v>870.922205564455</v>
       </c>
       <c r="E78">
-        <v>1553.38504</v>
+        <v>1573.82733</v>
       </c>
       <c r="F78">
-        <v>1553.61404</v>
+        <v>1574.05633</v>
       </c>
       <c r="G78">
         <v>33.8</v>
@@ -7683,37 +7683,37 @@
         <v>35.1</v>
       </c>
       <c r="M78">
-        <v>366.342190632</v>
+        <v>371.1624826140001</v>
       </c>
       <c r="N78">
-        <v>-331.242190632</v>
+        <v>-336.062482614</v>
       </c>
       <c r="O78">
-        <v>-82.810547658</v>
+        <v>-84.01562065350001</v>
       </c>
       <c r="P78">
-        <v>-248.431642974</v>
+        <v>-252.0468619605</v>
       </c>
       <c r="Q78">
-        <v>-216.631642974</v>
+        <v>-220.2468619605</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.4837057341558074</v>
+        <v>0.5027451139017119</v>
       </c>
       <c r="T78">
-        <v>4.234883132930013</v>
+        <v>4.419008486535664</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.0239530150345547</v>
+        <v>0.02364193691722282</v>
       </c>
       <c r="W78">
-        <v>0.230151879054852</v>
+        <v>0.2302252312749189</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.09581206013821886</v>
+        <v>0.09456774766889131</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2929048042790813</v>
+        <v>0.2948048042790813</v>
       </c>
       <c r="C79">
-        <v>-669.3341244355452</v>
+        <v>-696.4218773428306</v>
       </c>
       <c r="D79">
-        <v>870.922205564455</v>
+        <v>864.2767426571695</v>
       </c>
       <c r="E79">
-        <v>1573.82733</v>
+        <v>1594.26962</v>
       </c>
       <c r="F79">
-        <v>1574.05633</v>
+        <v>1594.49862</v>
       </c>
       <c r="G79">
         <v>33.8</v>
@@ -7765,37 +7765,37 @@
         <v>35.1</v>
       </c>
       <c r="M79">
-        <v>371.1624826140001</v>
+        <v>375.982774596</v>
       </c>
       <c r="N79">
-        <v>-336.062482614</v>
+        <v>-340.882774596</v>
       </c>
       <c r="O79">
-        <v>-84.01562065350001</v>
+        <v>-85.220693649</v>
       </c>
       <c r="P79">
-        <v>-252.0468619605</v>
+        <v>-255.662080947</v>
       </c>
       <c r="Q79">
-        <v>-220.2468619605</v>
+        <v>-223.862080947</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.5027451139017119</v>
+        <v>0.5235153463517898</v>
       </c>
       <c r="T79">
-        <v>4.419008486535664</v>
+        <v>4.619872508650922</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.02364193691722282</v>
+        <v>0.02333883516187381</v>
       </c>
       <c r="W79">
-        <v>0.2302252312749189</v>
+        <v>0.2302967026688301</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.09456774766889131</v>
+        <v>0.09335534064749529</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2948048042790813</v>
+        <v>0.2967048042790813</v>
       </c>
       <c r="C80">
-        <v>-696.4218773428306</v>
+        <v>-723.408983476451</v>
       </c>
       <c r="D80">
-        <v>864.2767426571695</v>
+        <v>857.7319265235491</v>
       </c>
       <c r="E80">
-        <v>1594.26962</v>
+        <v>1614.71191</v>
       </c>
       <c r="F80">
-        <v>1594.49862</v>
+        <v>1614.94091</v>
       </c>
       <c r="G80">
         <v>33.8</v>
@@ -7847,37 +7847,37 @@
         <v>35.1</v>
       </c>
       <c r="M80">
-        <v>375.982774596</v>
+        <v>380.803066578</v>
       </c>
       <c r="N80">
-        <v>-340.882774596</v>
+        <v>-345.703066578</v>
       </c>
       <c r="O80">
-        <v>-85.220693649</v>
+        <v>-86.4257666445</v>
       </c>
       <c r="P80">
-        <v>-255.662080947</v>
+        <v>-259.2772999335</v>
       </c>
       <c r="Q80">
-        <v>-223.862080947</v>
+        <v>-227.4772999335</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.5235153463517898</v>
+        <v>0.5462636961780656</v>
       </c>
       <c r="T80">
-        <v>4.619872508650922</v>
+        <v>4.8398664376343</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.02333883516187381</v>
+        <v>0.02304340686868553</v>
       </c>
       <c r="W80">
-        <v>0.2302967026688301</v>
+        <v>0.2303663646603639</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.09335534064749529</v>
+        <v>0.09217362747474223</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2967048042790813</v>
+        <v>0.2986048042790813</v>
       </c>
       <c r="C81">
-        <v>-723.408983476451</v>
+        <v>-750.2977121232249</v>
       </c>
       <c r="D81">
-        <v>857.7319265235491</v>
+        <v>851.2854878767754</v>
       </c>
       <c r="E81">
-        <v>1614.71191</v>
+        <v>1635.1542</v>
       </c>
       <c r="F81">
-        <v>1614.94091</v>
+        <v>1635.3832</v>
       </c>
       <c r="G81">
         <v>33.8</v>
@@ -7929,37 +7929,37 @@
         <v>35.1</v>
       </c>
       <c r="M81">
-        <v>380.803066578</v>
+        <v>385.62335856</v>
       </c>
       <c r="N81">
-        <v>-345.703066578</v>
+        <v>-350.52335856</v>
       </c>
       <c r="O81">
-        <v>-86.4257666445</v>
+        <v>-87.63083964</v>
       </c>
       <c r="P81">
-        <v>-259.2772999335</v>
+        <v>-262.89251892</v>
       </c>
       <c r="Q81">
-        <v>-227.4772999335</v>
+        <v>-231.09251892</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.5462636961780656</v>
+        <v>0.5712868809869688</v>
       </c>
       <c r="T81">
-        <v>4.8398664376343</v>
+        <v>5.081859759516015</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.02304340686868553</v>
+        <v>0.02275536428282696</v>
       </c>
       <c r="W81">
-        <v>0.2303663646603639</v>
+        <v>0.2304342851021094</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.09217362747474223</v>
+        <v>0.09102145713130794</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2986048042790813</v>
+        <v>0.3005048042790813</v>
       </c>
       <c r="C82">
-        <v>-750.2977121232249</v>
+        <v>-777.090264857938</v>
       </c>
       <c r="D82">
-        <v>851.2854878767754</v>
+        <v>844.9352251420622</v>
       </c>
       <c r="E82">
-        <v>1635.1542</v>
+        <v>1655.59649</v>
       </c>
       <c r="F82">
-        <v>1635.3832</v>
+        <v>1655.82549</v>
       </c>
       <c r="G82">
         <v>33.8</v>
@@ -8011,37 +8011,37 @@
         <v>35.1</v>
       </c>
       <c r="M82">
-        <v>385.62335856</v>
+        <v>390.4436505420001</v>
       </c>
       <c r="N82">
-        <v>-350.52335856</v>
+        <v>-355.343650542</v>
       </c>
       <c r="O82">
-        <v>-87.63083964</v>
+        <v>-88.83591263550001</v>
       </c>
       <c r="P82">
-        <v>-262.89251892</v>
+        <v>-266.5077379065</v>
       </c>
       <c r="Q82">
-        <v>-231.09251892</v>
+        <v>-234.7077379065</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.5712868809869688</v>
+        <v>0.5989440852494409</v>
       </c>
       <c r="T82">
-        <v>5.081859759516015</v>
+        <v>5.349326062648437</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.02275536428282696</v>
+        <v>0.02247443385958219</v>
       </c>
       <c r="W82">
-        <v>0.2304342851021094</v>
+        <v>0.2305005284959105</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.09102145713130794</v>
+        <v>0.0898977354383288</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.3005048042790813</v>
+        <v>0.3024048042790812</v>
       </c>
       <c r="C83">
-        <v>-777.090264857938</v>
+        <v>-803.7887780501736</v>
       </c>
       <c r="D83">
-        <v>844.9352251420622</v>
+        <v>838.6790019498266</v>
       </c>
       <c r="E83">
-        <v>1655.59649</v>
+        <v>1676.03878</v>
       </c>
       <c r="F83">
-        <v>1655.82549</v>
+        <v>1676.26778</v>
       </c>
       <c r="G83">
         <v>33.8</v>
@@ -8093,37 +8093,37 @@
         <v>35.1</v>
       </c>
       <c r="M83">
-        <v>390.4436505420001</v>
+        <v>395.2639425240001</v>
       </c>
       <c r="N83">
-        <v>-355.343650542</v>
+        <v>-360.163942524</v>
       </c>
       <c r="O83">
-        <v>-88.83591263550001</v>
+        <v>-90.04098563100001</v>
       </c>
       <c r="P83">
-        <v>-266.5077379065</v>
+        <v>-270.122956893</v>
       </c>
       <c r="Q83">
-        <v>-234.7077379065</v>
+        <v>-238.322956893</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.5989440852494409</v>
+        <v>0.6296743122077432</v>
       </c>
       <c r="T83">
-        <v>5.349326062648437</v>
+        <v>5.646510843906683</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.02247443385958219</v>
+        <v>0.02220035539787996</v>
       </c>
       <c r="W83">
-        <v>0.2305005284959105</v>
+        <v>0.2305651561971799</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.0898977354383288</v>
+        <v>0.08880142159151994</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.3024048042790812</v>
+        <v>0.3043048042790812</v>
       </c>
       <c r="C84">
-        <v>-803.7887780501736</v>
+        <v>-830.3953252605902</v>
       </c>
       <c r="D84">
-        <v>838.6790019498266</v>
+        <v>832.5147447394099</v>
       </c>
       <c r="E84">
-        <v>1676.03878</v>
+        <v>1696.48107</v>
       </c>
       <c r="F84">
-        <v>1676.26778</v>
+        <v>1696.71007</v>
       </c>
       <c r="G84">
         <v>33.8</v>
@@ -8175,37 +8175,37 @@
         <v>35.1</v>
       </c>
       <c r="M84">
-        <v>395.2639425240001</v>
+        <v>400.084234506</v>
       </c>
       <c r="N84">
-        <v>-360.163942524</v>
+        <v>-364.984234506</v>
       </c>
       <c r="O84">
-        <v>-90.04098563100001</v>
+        <v>-91.2460586265</v>
       </c>
       <c r="P84">
-        <v>-270.122956893</v>
+        <v>-273.7381758795</v>
       </c>
       <c r="Q84">
-        <v>-238.322956893</v>
+        <v>-241.9381758795</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.6296743122077432</v>
+        <v>0.6640198599846692</v>
       </c>
       <c r="T84">
-        <v>5.646510843906683</v>
+        <v>5.978658540607077</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.02220035539787996</v>
+        <v>0.02193288123645972</v>
       </c>
       <c r="W84">
-        <v>0.2305651561971799</v>
+        <v>0.2306282266044428</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.08880142159151994</v>
+        <v>0.08773152494583891</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.3043048042790812</v>
+        <v>0.3062048042790813</v>
       </c>
       <c r="C85">
-        <v>-830.3953252605902</v>
+        <v>-856.9119195322957</v>
       </c>
       <c r="D85">
-        <v>832.5147447394099</v>
+        <v>826.4404404677047</v>
       </c>
       <c r="E85">
-        <v>1696.48107</v>
+        <v>1716.92336</v>
       </c>
       <c r="F85">
-        <v>1696.71007</v>
+        <v>1717.15236</v>
       </c>
       <c r="G85">
         <v>33.8</v>
@@ -8257,37 +8257,37 @@
         <v>35.1</v>
       </c>
       <c r="M85">
-        <v>400.084234506</v>
+        <v>404.9045264880001</v>
       </c>
       <c r="N85">
-        <v>-364.984234506</v>
+        <v>-369.8045264880001</v>
       </c>
       <c r="O85">
-        <v>-91.2460586265</v>
+        <v>-92.45113162200002</v>
       </c>
       <c r="P85">
-        <v>-273.7381758795</v>
+        <v>-277.353394866</v>
       </c>
       <c r="Q85">
-        <v>-241.9381758795</v>
+        <v>-245.553394866</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.6640198599846692</v>
+        <v>0.7026586012337113</v>
       </c>
       <c r="T85">
-        <v>5.978658540607077</v>
+        <v>6.352324699395021</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.02193288123645972</v>
+        <v>0.02167177550745425</v>
       </c>
       <c r="W85">
-        <v>0.2306282266044428</v>
+        <v>0.2306897953353423</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.08773152494583891</v>
+        <v>0.086687102029817</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.3062048042790813</v>
+        <v>0.3081048042790813</v>
       </c>
       <c r="C86">
-        <v>-856.9119195322952</v>
+        <v>-883.3405155826333</v>
       </c>
       <c r="D86">
-        <v>826.4404404677049</v>
+        <v>820.4541344173667</v>
       </c>
       <c r="E86">
-        <v>1716.92336</v>
+        <v>1737.36565</v>
       </c>
       <c r="F86">
-        <v>1717.15236</v>
+        <v>1737.59465</v>
       </c>
       <c r="G86">
         <v>33.8</v>
@@ -8339,37 +8339,37 @@
         <v>35.1</v>
       </c>
       <c r="M86">
-        <v>404.904526488</v>
+        <v>409.72481847</v>
       </c>
       <c r="N86">
-        <v>-369.804526488</v>
+        <v>-374.62481847</v>
       </c>
       <c r="O86">
-        <v>-92.45113162200001</v>
+        <v>-93.65620461749999</v>
       </c>
       <c r="P86">
-        <v>-277.353394866</v>
+        <v>-280.9686138525</v>
       </c>
       <c r="Q86">
-        <v>-245.553394866</v>
+        <v>-249.1686138525</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.7026586012337108</v>
+        <v>0.7464491746492915</v>
       </c>
       <c r="T86">
-        <v>6.352324699395017</v>
+        <v>6.775813012688018</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.02167177550745425</v>
+        <v>0.02141681344266068</v>
       </c>
       <c r="W86">
-        <v>0.2306897953353423</v>
+        <v>0.2307499153902206</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.08668710202981711</v>
+        <v>0.08566725377064277</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.3081048042790813</v>
+        <v>0.3100048042790813</v>
       </c>
       <c r="C87">
-        <v>-883.3405155826333</v>
+        <v>-909.6830119004047</v>
       </c>
       <c r="D87">
-        <v>820.4541344173667</v>
+        <v>814.5539280995953</v>
       </c>
       <c r="E87">
-        <v>1737.36565</v>
+        <v>1757.80794</v>
       </c>
       <c r="F87">
-        <v>1737.59465</v>
+        <v>1758.03694</v>
       </c>
       <c r="G87">
         <v>33.8</v>
@@ -8421,37 +8421,37 @@
         <v>35.1</v>
       </c>
       <c r="M87">
-        <v>409.72481847</v>
+        <v>414.545110452</v>
       </c>
       <c r="N87">
-        <v>-374.62481847</v>
+        <v>-379.445110452</v>
       </c>
       <c r="O87">
-        <v>-93.65620461749999</v>
+        <v>-94.861277613</v>
       </c>
       <c r="P87">
-        <v>-280.9686138525</v>
+        <v>-284.583832839</v>
       </c>
       <c r="Q87">
-        <v>-249.1686138525</v>
+        <v>-252.783832839</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.7464491746492915</v>
+        <v>0.7964955442670981</v>
       </c>
       <c r="T87">
-        <v>6.775813012688018</v>
+        <v>7.259799656451448</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.02141681344266068</v>
+        <v>0.02116778072821113</v>
       </c>
       <c r="W87">
-        <v>0.2307499153902206</v>
+        <v>0.2308086373042878</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.08566725377064277</v>
+        <v>0.08467112291284462</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.3100048042790813</v>
+        <v>0.3119048042790812</v>
       </c>
       <c r="C88">
-        <v>-909.6830119004047</v>
+        <v>-935.9412527532351</v>
       </c>
       <c r="D88">
-        <v>814.5539280995953</v>
+        <v>808.7379772467649</v>
       </c>
       <c r="E88">
-        <v>1757.80794</v>
+        <v>1778.25023</v>
       </c>
       <c r="F88">
-        <v>1758.03694</v>
+        <v>1778.47923</v>
       </c>
       <c r="G88">
         <v>33.8</v>
@@ -8503,37 +8503,37 @@
         <v>35.1</v>
       </c>
       <c r="M88">
-        <v>414.545110452</v>
+        <v>419.365402434</v>
       </c>
       <c r="N88">
-        <v>-379.445110452</v>
+        <v>-384.265402434</v>
       </c>
       <c r="O88">
-        <v>-94.861277613</v>
+        <v>-96.06635060849999</v>
       </c>
       <c r="P88">
-        <v>-284.583832839</v>
+        <v>-288.1990518255</v>
       </c>
       <c r="Q88">
-        <v>-252.783832839</v>
+        <v>-256.3990518255</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.7964955442670981</v>
+        <v>0.8542413553645671</v>
       </c>
       <c r="T88">
-        <v>7.259799656451448</v>
+        <v>7.81824578387079</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.02116778072821113</v>
+        <v>0.02092447290374894</v>
       </c>
       <c r="W88">
-        <v>0.2308086373042878</v>
+        <v>0.230866009289296</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.08467112291284462</v>
+        <v>0.08369789161499575</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.3119048042790812</v>
+        <v>0.3138048042790813</v>
       </c>
       <c r="C89">
-        <v>-935.9412527532351</v>
+        <v>-962.1170301095619</v>
       </c>
       <c r="D89">
-        <v>808.7379772467649</v>
+        <v>803.0044898904382</v>
       </c>
       <c r="E89">
-        <v>1778.25023</v>
+        <v>1798.69252</v>
       </c>
       <c r="F89">
-        <v>1778.47923</v>
+        <v>1798.92152</v>
       </c>
       <c r="G89">
         <v>33.8</v>
@@ -8585,37 +8585,37 @@
         <v>35.1</v>
       </c>
       <c r="M89">
-        <v>419.365402434</v>
+        <v>424.185694416</v>
       </c>
       <c r="N89">
-        <v>-384.265402434</v>
+        <v>-389.085694416</v>
       </c>
       <c r="O89">
-        <v>-96.06635060849999</v>
+        <v>-97.27142360400001</v>
       </c>
       <c r="P89">
-        <v>-288.1990518255</v>
+        <v>-291.814270812</v>
       </c>
       <c r="Q89">
-        <v>-256.3990518255</v>
+        <v>-260.014270812</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.8542413553645671</v>
+        <v>0.9216114683116148</v>
       </c>
       <c r="T89">
-        <v>7.81824578387079</v>
+        <v>8.469766265860025</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.02092447290374894</v>
+        <v>0.02068669480256997</v>
       </c>
       <c r="W89">
-        <v>0.230866009289296</v>
+        <v>0.230922077365554</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.08369789161499575</v>
+        <v>0.08274677921027995</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.3138048042790813</v>
+        <v>0.3157048042790813</v>
       </c>
       <c r="C90">
-        <v>-962.1170301095619</v>
+        <v>-988.2120854794375</v>
       </c>
       <c r="D90">
-        <v>803.0044898904382</v>
+        <v>797.3517245205626</v>
       </c>
       <c r="E90">
-        <v>1798.69252</v>
+        <v>1819.13481</v>
       </c>
       <c r="F90">
-        <v>1798.92152</v>
+        <v>1819.36381</v>
       </c>
       <c r="G90">
         <v>33.8</v>
@@ -8667,37 +8667,37 @@
         <v>35.1</v>
       </c>
       <c r="M90">
-        <v>424.185694416</v>
+        <v>429.005986398</v>
       </c>
       <c r="N90">
-        <v>-389.085694416</v>
+        <v>-393.905986398</v>
       </c>
       <c r="O90">
-        <v>-97.27142360400001</v>
+        <v>-98.4764965995</v>
       </c>
       <c r="P90">
-        <v>-291.814270812</v>
+        <v>-295.4294897985</v>
       </c>
       <c r="Q90">
-        <v>-260.014270812</v>
+        <v>-263.6294897984999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.9216114683116148</v>
+        <v>1.00123069270358</v>
       </c>
       <c r="T90">
-        <v>8.469766265860025</v>
+        <v>9.239745017301844</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.02068669480256997</v>
+        <v>0.02045426002950738</v>
       </c>
       <c r="W90">
-        <v>0.230922077365554</v>
+        <v>0.2309768854850422</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.08274677921027995</v>
+        <v>0.08181704011802959</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.3157048042790813</v>
+        <v>0.3176048042790813</v>
       </c>
       <c r="C91">
-        <v>-988.2120854794375</v>
+        <v>-1014.228111678131</v>
       </c>
       <c r="D91">
-        <v>797.3517245205626</v>
+        <v>791.7779883218694</v>
       </c>
       <c r="E91">
-        <v>1819.13481</v>
+        <v>1839.5771</v>
       </c>
       <c r="F91">
-        <v>1819.36381</v>
+        <v>1839.8061</v>
       </c>
       <c r="G91">
         <v>33.8</v>
@@ -8749,37 +8749,37 @@
         <v>35.1</v>
       </c>
       <c r="M91">
-        <v>429.005986398</v>
+        <v>433.82627838</v>
       </c>
       <c r="N91">
-        <v>-393.905986398</v>
+        <v>-398.72627838</v>
       </c>
       <c r="O91">
-        <v>-98.4764965995</v>
+        <v>-99.681569595</v>
       </c>
       <c r="P91">
-        <v>-295.4294897985</v>
+        <v>-299.044708785</v>
       </c>
       <c r="Q91">
-        <v>-263.6294897984999</v>
+        <v>-267.244708785</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>1.00123069270358</v>
+        <v>1.096773761973938</v>
       </c>
       <c r="T91">
-        <v>9.239745017301844</v>
+        <v>10.16371951903203</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.02045426002950738</v>
+        <v>0.02022699047362397</v>
       </c>
       <c r="W91">
-        <v>0.2309768854850422</v>
+        <v>0.2310304756463195</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.08181704011802959</v>
+        <v>0.08090796189449589</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.3176048042790813</v>
+        <v>0.3195048042790813</v>
       </c>
       <c r="C92">
-        <v>-1014.228111678131</v>
+        <v>-1040.16675451627</v>
       </c>
       <c r="D92">
-        <v>791.7779883218694</v>
+        <v>786.2816354837305</v>
       </c>
       <c r="E92">
-        <v>1839.5771</v>
+        <v>1860.01939</v>
       </c>
       <c r="F92">
-        <v>1839.8061</v>
+        <v>1860.24839</v>
       </c>
       <c r="G92">
         <v>33.8</v>
@@ -8831,37 +8831,37 @@
         <v>35.1</v>
       </c>
       <c r="M92">
-        <v>433.82627838</v>
+        <v>438.6465703620001</v>
       </c>
       <c r="N92">
-        <v>-398.72627838</v>
+        <v>-403.5465703620001</v>
       </c>
       <c r="O92">
-        <v>-99.681569595</v>
+        <v>-100.8866425905</v>
       </c>
       <c r="P92">
-        <v>-299.044708785</v>
+        <v>-302.6599277715001</v>
       </c>
       <c r="Q92">
-        <v>-267.244708785</v>
+        <v>-270.8599277715001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.096773761973938</v>
+        <v>1.213548624415486</v>
       </c>
       <c r="T92">
-        <v>10.16371951903203</v>
+        <v>11.29302168781337</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.02022699047362397</v>
+        <v>0.02000471585303469</v>
       </c>
       <c r="W92">
-        <v>0.2310304756463195</v>
+        <v>0.2310828880018544</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.08090796189449589</v>
+        <v>0.08001886341213882</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.3195048042790813</v>
+        <v>0.3214048042790813</v>
       </c>
       <c r="C93">
-        <v>-1040.16675451627</v>
+        <v>-1066.029614420074</v>
       </c>
       <c r="D93">
-        <v>786.2816354837305</v>
+        <v>780.861065579926</v>
       </c>
       <c r="E93">
-        <v>1860.01939</v>
+        <v>1880.46168</v>
       </c>
       <c r="F93">
-        <v>1860.24839</v>
+        <v>1880.69068</v>
       </c>
       <c r="G93">
         <v>33.8</v>
@@ -8913,37 +8913,37 @@
         <v>35.1</v>
       </c>
       <c r="M93">
-        <v>438.6465703620001</v>
+        <v>443.466862344</v>
       </c>
       <c r="N93">
-        <v>-403.5465703620001</v>
+        <v>-408.366862344</v>
       </c>
       <c r="O93">
-        <v>-100.8866425905</v>
+        <v>-102.091715586</v>
       </c>
       <c r="P93">
-        <v>-302.6599277715001</v>
+        <v>-306.275146758</v>
       </c>
       <c r="Q93">
-        <v>-270.8599277715001</v>
+        <v>-274.475146758</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.213548624415486</v>
+        <v>1.359517202467423</v>
       </c>
       <c r="T93">
-        <v>11.29302168781337</v>
+        <v>12.70464939879004</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.02000471585303469</v>
+        <v>0.01978727328941475</v>
       </c>
       <c r="W93">
-        <v>0.2310828880018544</v>
+        <v>0.231134160958356</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.08001886341213882</v>
+        <v>0.07914909315765906</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.3214048042790813</v>
+        <v>0.3233048042790813</v>
       </c>
       <c r="C94">
-        <v>-1066.029614420074</v>
+        <v>-1091.81824798503</v>
       </c>
       <c r="D94">
-        <v>780.861065579926</v>
+        <v>775.5147220149703</v>
       </c>
       <c r="E94">
-        <v>1880.46168</v>
+        <v>1900.90397</v>
       </c>
       <c r="F94">
-        <v>1880.69068</v>
+        <v>1901.13297</v>
       </c>
       <c r="G94">
         <v>33.8</v>
@@ -8995,37 +8995,37 @@
         <v>35.1</v>
       </c>
       <c r="M94">
-        <v>443.466862344</v>
+        <v>448.2871543260001</v>
       </c>
       <c r="N94">
-        <v>-408.366862344</v>
+        <v>-413.187154326</v>
       </c>
       <c r="O94">
-        <v>-102.091715586</v>
+        <v>-103.2967885815</v>
       </c>
       <c r="P94">
-        <v>-306.275146758</v>
+        <v>-309.8903657445001</v>
       </c>
       <c r="Q94">
-        <v>-274.475146758</v>
+        <v>-278.0903657445</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.359517202467423</v>
+        <v>1.547191088534198</v>
       </c>
       <c r="T94">
-        <v>12.70464939879004</v>
+        <v>14.51959931290291</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.01978727328941475</v>
+        <v>0.01957450690995868</v>
       </c>
       <c r="W94">
-        <v>0.231134160958356</v>
+        <v>0.2311843312706318</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.07914909315765906</v>
+        <v>0.07829802763983473</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.3233048042790813</v>
+        <v>0.3252048042790813</v>
       </c>
       <c r="C95">
-        <v>-1091.81824798503</v>
+        <v>-1117.534169466172</v>
       </c>
       <c r="D95">
-        <v>775.5147220149703</v>
+        <v>770.2410905338282</v>
       </c>
       <c r="E95">
-        <v>1900.90397</v>
+        <v>1921.34626</v>
       </c>
       <c r="F95">
-        <v>1901.13297</v>
+        <v>1921.57526</v>
       </c>
       <c r="G95">
         <v>33.8</v>
@@ -9077,37 +9077,37 @@
         <v>35.1</v>
       </c>
       <c r="M95">
-        <v>448.2871543260001</v>
+        <v>453.107446308</v>
       </c>
       <c r="N95">
-        <v>-413.187154326</v>
+        <v>-418.007446308</v>
       </c>
       <c r="O95">
-        <v>-103.2967885815</v>
+        <v>-104.501861577</v>
       </c>
       <c r="P95">
-        <v>-309.8903657445001</v>
+        <v>-313.505584731</v>
       </c>
       <c r="Q95">
-        <v>-278.0903657445</v>
+        <v>-281.705584731</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.547191088534198</v>
+        <v>1.797422936623231</v>
       </c>
       <c r="T95">
-        <v>14.51959931290291</v>
+        <v>16.93953253172007</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.01957450690995868</v>
+        <v>0.01936626747474635</v>
       </c>
       <c r="W95">
-        <v>0.2311843312706318</v>
+        <v>0.2312334341294548</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.07829802763983473</v>
+        <v>0.07746506989898549</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.3252048042790813</v>
+        <v>0.3271048042790813</v>
       </c>
       <c r="C96">
-        <v>-1117.534169466172</v>
+        <v>-1143.17885220797</v>
       </c>
       <c r="D96">
-        <v>770.2410905338282</v>
+        <v>765.0386977920308</v>
       </c>
       <c r="E96">
-        <v>1921.34626</v>
+        <v>1941.78855</v>
       </c>
       <c r="F96">
-        <v>1921.57526</v>
+        <v>1942.01755</v>
       </c>
       <c r="G96">
         <v>33.8</v>
@@ -9159,37 +9159,37 @@
         <v>35.1</v>
       </c>
       <c r="M96">
-        <v>453.107446308</v>
+        <v>457.9277382900001</v>
       </c>
       <c r="N96">
-        <v>-418.007446308</v>
+        <v>-422.8277382900001</v>
       </c>
       <c r="O96">
-        <v>-104.501861577</v>
+        <v>-105.7069345725</v>
       </c>
       <c r="P96">
-        <v>-313.505584731</v>
+        <v>-317.1208037175001</v>
       </c>
       <c r="Q96">
-        <v>-281.705584731</v>
+        <v>-285.3208037175</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.797422936623231</v>
+        <v>2.147747523947877</v>
       </c>
       <c r="T96">
-        <v>16.93953253172007</v>
+        <v>20.32743903806408</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.01936626747474635</v>
+        <v>0.01916241202764376</v>
       </c>
       <c r="W96">
-        <v>0.2312334341294548</v>
+        <v>0.2312815032438816</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.07746506989898549</v>
+        <v>0.07664964811057506</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3271048042790813</v>
+        <v>0.3290048042790813</v>
       </c>
       <c r="C97">
-        <v>-1143.17885220797</v>
+        <v>-1168.753730016658</v>
       </c>
       <c r="D97">
-        <v>765.0386977920308</v>
+        <v>759.9061099833419</v>
       </c>
       <c r="E97">
-        <v>1941.78855</v>
+        <v>1962.23084</v>
       </c>
       <c r="F97">
-        <v>1942.01755</v>
+        <v>1962.45984</v>
       </c>
       <c r="G97">
         <v>33.8</v>
@@ -9241,37 +9241,37 @@
         <v>35.1</v>
       </c>
       <c r="M97">
-        <v>457.9277382900001</v>
+        <v>462.7480302720001</v>
       </c>
       <c r="N97">
-        <v>-422.8277382900001</v>
+        <v>-427.648030272</v>
       </c>
       <c r="O97">
-        <v>-105.7069345725</v>
+        <v>-106.912007568</v>
       </c>
       <c r="P97">
-        <v>-317.1208037175001</v>
+        <v>-320.736022704</v>
       </c>
       <c r="Q97">
-        <v>-285.3208037175</v>
+        <v>-288.936022704</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>2.147747523947877</v>
+        <v>2.673234404934849</v>
       </c>
       <c r="T97">
-        <v>20.32743903806408</v>
+        <v>25.40929879758012</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.01916241202764376</v>
+        <v>0.01896280356902247</v>
       </c>
       <c r="W97">
-        <v>0.2312815032438816</v>
+        <v>0.2313285709184245</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.07664964811057506</v>
+        <v>0.07585121427608987</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.3290048042790813</v>
+        <v>0.3309048042790813</v>
       </c>
       <c r="C98">
-        <v>-1168.753730016658</v>
+        <v>-1194.260198477695</v>
       </c>
       <c r="D98">
-        <v>759.9061099833419</v>
+        <v>754.8419315223049</v>
       </c>
       <c r="E98">
-        <v>1962.23084</v>
+        <v>1982.67313</v>
       </c>
       <c r="F98">
-        <v>1962.45984</v>
+        <v>1982.90213</v>
       </c>
       <c r="G98">
         <v>33.8</v>
@@ -9323,37 +9323,37 @@
         <v>35.1</v>
       </c>
       <c r="M98">
-        <v>462.748030272</v>
+        <v>467.568322254</v>
       </c>
       <c r="N98">
-        <v>-427.648030272</v>
+        <v>-432.468322254</v>
       </c>
       <c r="O98">
-        <v>-106.912007568</v>
+        <v>-108.1170805635</v>
       </c>
       <c r="P98">
-        <v>-320.736022704</v>
+        <v>-324.3512416905</v>
       </c>
       <c r="Q98">
-        <v>-288.936022704</v>
+        <v>-292.5512416905</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.673234404934842</v>
+        <v>3.549045873246455</v>
       </c>
       <c r="T98">
-        <v>25.40929879758005</v>
+        <v>33.87906506344007</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.01896280356902247</v>
+        <v>0.01876731074872327</v>
       </c>
       <c r="W98">
-        <v>0.2313285709184245</v>
+        <v>0.2313746681254511</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.07585121427608998</v>
+        <v>0.07506924299489315</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.3309048042790813</v>
+        <v>0.3328048042790813</v>
       </c>
       <c r="C99">
-        <v>-1194.260198477695</v>
+        <v>-1219.699616220887</v>
       </c>
       <c r="D99">
-        <v>754.8419315223049</v>
+        <v>749.844803779113</v>
       </c>
       <c r="E99">
-        <v>1982.67313</v>
+        <v>2003.11542</v>
       </c>
       <c r="F99">
-        <v>1982.90213</v>
+        <v>2003.34442</v>
       </c>
       <c r="G99">
         <v>33.8</v>
@@ -9405,37 +9405,37 @@
         <v>35.1</v>
       </c>
       <c r="M99">
-        <v>467.568322254</v>
+        <v>472.388614236</v>
       </c>
       <c r="N99">
-        <v>-432.468322254</v>
+        <v>-437.288614236</v>
       </c>
       <c r="O99">
-        <v>-108.1170805635</v>
+        <v>-109.322153559</v>
       </c>
       <c r="P99">
-        <v>-324.3512416905</v>
+        <v>-327.966460677</v>
       </c>
       <c r="Q99">
-        <v>-292.5512416905</v>
+        <v>-296.166460677</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.549045873246455</v>
+        <v>5.300668809869683</v>
       </c>
       <c r="T99">
-        <v>33.87906506344007</v>
+        <v>50.8185975951601</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.01876731074872327</v>
+        <v>0.01857580757781793</v>
       </c>
       <c r="W99">
-        <v>0.2313746681254511</v>
+        <v>0.2314198245731505</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.07506924299489315</v>
+        <v>0.07430323031127173</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3328048042790813</v>
+        <v>0.3347048042790813</v>
       </c>
       <c r="C100">
-        <v>-1219.699616220887</v>
+        <v>-1245.073306135594</v>
       </c>
       <c r="D100">
-        <v>749.844803779113</v>
+        <v>744.913403864406</v>
       </c>
       <c r="E100">
-        <v>2003.11542</v>
+        <v>2023.55771</v>
       </c>
       <c r="F100">
-        <v>2003.34442</v>
+        <v>2023.78671</v>
       </c>
       <c r="G100">
         <v>33.8</v>
@@ -9487,37 +9487,37 @@
         <v>35.1</v>
       </c>
       <c r="M100">
-        <v>472.388614236</v>
+        <v>477.208906218</v>
       </c>
       <c r="N100">
-        <v>-437.288614236</v>
+        <v>-442.108906218</v>
       </c>
       <c r="O100">
-        <v>-109.322153559</v>
+        <v>-110.5272265545</v>
       </c>
       <c r="P100">
-        <v>-327.966460677</v>
+        <v>-331.5816796635</v>
       </c>
       <c r="Q100">
-        <v>-296.166460677</v>
+        <v>-299.7816796635</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>5.300668809869683</v>
+        <v>10.55553761973937</v>
       </c>
       <c r="T100">
-        <v>50.8185975951601</v>
+        <v>101.6371951903202</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.01857580757781793</v>
+        <v>0.01838817315783997</v>
       </c>
       <c r="W100">
-        <v>0.2314198245731505</v>
+        <v>0.2314640687693814</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.07430323031127173</v>
+        <v>0.07355269263135988</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3347048042790813</v>
-      </c>
-      <c r="C101">
-        <v>-1245.073306135594</v>
-      </c>
-      <c r="D101">
-        <v>744.913403864406</v>
-      </c>
-      <c r="E101">
-        <v>2023.55771</v>
-      </c>
-      <c r="F101">
-        <v>2023.78671</v>
-      </c>
-      <c r="G101">
-        <v>33.8</v>
-      </c>
-      <c r="H101">
-        <v>2044</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>66.90000000000001</v>
-      </c>
-      <c r="K101">
-        <v>31.8</v>
-      </c>
-      <c r="L101">
-        <v>35.1</v>
-      </c>
-      <c r="M101">
-        <v>477.208906218</v>
-      </c>
-      <c r="N101">
-        <v>-442.108906218</v>
-      </c>
-      <c r="O101">
-        <v>-110.5272265545</v>
-      </c>
-      <c r="P101">
-        <v>-331.5816796635</v>
-      </c>
-      <c r="Q101">
-        <v>-299.7816796635</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>10.55553761973937</v>
-      </c>
-      <c r="T101">
-        <v>101.6371951903202</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.01838817315783997</v>
-      </c>
-      <c r="W101">
-        <v>0.2314640687693814</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.07355269263135988</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
